--- a/progression_odds_only_pdl1.xlsx
+++ b/progression_odds_only_pdl1.xlsx
@@ -14469,22 +14469,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="25">
-        <v>1.8712610000000001</v>
+        <v>1.934885</v>
       </c>
       <c r="C2" s="26">
-        <v>0.51000449999999997</v>
+        <v>0.53398469999999998</v>
       </c>
       <c r="D2" s="27">
-        <v>2.2999999999999998</v>
+        <v>2.3900000000000001</v>
       </c>
       <c r="E2" s="28">
-        <v>0.021000000000000001</v>
+        <v>0.017000000000000001</v>
       </c>
       <c r="F2" s="29">
-        <v>1.0968389999999999</v>
+        <v>1.12653</v>
       </c>
       <c r="G2" s="30">
-        <v>3.1924630000000001</v>
+        <v>3.3232849999999998</v>
       </c>
     </row>
     <row r="3">
@@ -14492,22 +14492,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="33">
-        <v>1.3989309999999999</v>
+        <v>1.407216</v>
       </c>
       <c r="C3" s="34">
-        <v>0.3676333</v>
+        <v>0.3736334</v>
       </c>
       <c r="D3" s="35">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="E3" s="36">
-        <v>0.20100000000000001</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="F3" s="37">
-        <v>0.83580310000000002</v>
+        <v>0.83628820000000004</v>
       </c>
       <c r="G3" s="38">
-        <v>2.3414700000000002</v>
+        <v>2.3679109999999999</v>
       </c>
     </row>
     <row r="4">
@@ -14515,22 +14515,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="41">
-        <v>2.1029019999999998</v>
+        <v>2.0618050000000001</v>
       </c>
       <c r="C4" s="42">
-        <v>0.68250869999999997</v>
+        <v>0.67837959999999997</v>
       </c>
       <c r="D4" s="43">
-        <v>2.29</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E4" s="44">
-        <v>0.021999999999999999</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="F4" s="45">
-        <v>1.1131580000000001</v>
+        <v>1.0818909999999999</v>
       </c>
       <c r="G4" s="46">
-        <v>3.9726590000000002</v>
+        <v>3.9292690000000001</v>
       </c>
     </row>
     <row r="5">
@@ -14538,22 +14538,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="49">
-        <v>1.3622669999999999</v>
+        <v>1.280019</v>
       </c>
       <c r="C5" s="50">
-        <v>0.3436128</v>
+        <v>0.32608179999999998</v>
       </c>
       <c r="D5" s="51">
-        <v>1.23</v>
+        <v>0.96999999999999997</v>
       </c>
       <c r="E5" s="52">
-        <v>0.22</v>
+        <v>0.33200000000000002</v>
       </c>
       <c r="F5" s="53">
-        <v>0.83091870000000001</v>
+        <v>0.77691779999999999</v>
       </c>
       <c r="G5" s="54">
-        <v>2.2333970000000001</v>
+        <v>2.1089099999999999</v>
       </c>
     </row>
     <row r="6">
@@ -14561,22 +14561,22 @@
         <v>11</v>
       </c>
       <c r="B6" s="57">
-        <v>1.2912159999999999</v>
+        <v>1.303709</v>
       </c>
       <c r="C6" s="58">
-        <v>0.34155679999999999</v>
+        <v>0.34851330000000003</v>
       </c>
       <c r="D6" s="59">
-        <v>0.96999999999999997</v>
+        <v>0.98999999999999999</v>
       </c>
       <c r="E6" s="60">
-        <v>0.33400000000000002</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="F6" s="61">
-        <v>0.76884050000000004</v>
+        <v>0.77202899999999997</v>
       </c>
       <c r="G6" s="62">
-        <v>2.1685110000000001</v>
+        <v>2.2015449999999999</v>
       </c>
     </row>
     <row r="7">
@@ -14584,22 +14584,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="65">
-        <v>1.55429</v>
+        <v>1.6077239999999999</v>
       </c>
       <c r="C7" s="66">
-        <v>0.83140910000000001</v>
+        <v>0.86188299999999996</v>
       </c>
       <c r="D7" s="67">
-        <v>0.81999999999999995</v>
+        <v>0.89000000000000001</v>
       </c>
       <c r="E7" s="68">
-        <v>0.40999999999999998</v>
+        <v>0.376</v>
       </c>
       <c r="F7" s="69">
-        <v>0.54477050000000005</v>
+        <v>0.56220130000000001</v>
       </c>
       <c r="G7" s="70">
-        <v>4.434558</v>
+        <v>4.5975999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -14630,22 +14630,22 @@
         <v>15</v>
       </c>
       <c r="B9" s="81">
-        <v>0.39781450000000002</v>
+        <v>0.3937138</v>
       </c>
       <c r="C9" s="82">
-        <v>0.41761369999999998</v>
+        <v>0.41456219999999999</v>
       </c>
       <c r="D9" s="83">
-        <v>-0.88</v>
+        <v>-0.89000000000000001</v>
       </c>
       <c r="E9" s="84">
-        <v>0.38</v>
+        <v>0.376</v>
       </c>
       <c r="F9" s="85">
-        <v>0.050829399999999997</v>
+        <v>0.049992500000000002</v>
       </c>
       <c r="G9" s="86">
-        <v>3.113483</v>
+        <v>3.1006740000000002</v>
       </c>
     </row>
     <row r="10">
@@ -14653,22 +14653,22 @@
         <v>16</v>
       </c>
       <c r="B10" s="89">
-        <v>2.0533899999999998</v>
+        <v>1.741339</v>
       </c>
       <c r="C10" s="90">
-        <v>1.157548</v>
+        <v>1.0147679999999999</v>
       </c>
       <c r="D10" s="91">
-        <v>1.28</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="E10" s="92">
-        <v>0.20200000000000001</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="F10" s="93">
-        <v>0.68018619999999996</v>
+        <v>0.55570520000000001</v>
       </c>
       <c r="G10" s="94">
-        <v>6.1989089999999996</v>
+        <v>5.456601</v>
       </c>
     </row>
     <row r="11">
@@ -14676,22 +14676,22 @@
         <v>17</v>
       </c>
       <c r="B11" s="97">
-        <v>0.58366580000000001</v>
+        <v>0.63587870000000002</v>
       </c>
       <c r="C11" s="98">
-        <v>0.61705949999999998</v>
+        <v>0.67476349999999996</v>
       </c>
       <c r="D11" s="99">
-        <v>-0.51000000000000001</v>
+        <v>-0.42999999999999999</v>
       </c>
       <c r="E11" s="100">
-        <v>0.61099999999999999</v>
+        <v>0.67000000000000004</v>
       </c>
       <c r="F11" s="101">
-        <v>0.0734958</v>
+        <v>0.079454899999999995</v>
       </c>
       <c r="G11" s="102">
-        <v>4.6351760000000004</v>
+        <v>5.088946</v>
       </c>
     </row>
     <row r="12">
@@ -14745,22 +14745,22 @@
         <v>1</v>
       </c>
       <c r="B14" s="121">
-        <v>0.74682040000000005</v>
+        <v>0.68444340000000004</v>
       </c>
       <c r="C14" s="122">
-        <v>0.18143999999999999</v>
+        <v>0.17098830000000001</v>
       </c>
       <c r="D14" s="123">
-        <v>-1.2</v>
+        <v>-1.52</v>
       </c>
       <c r="E14" s="124">
-        <v>0.23000000000000001</v>
+        <v>0.129</v>
       </c>
       <c r="F14" s="125">
-        <v>0.46389190000000002</v>
+        <v>0.41945900000000003</v>
       </c>
       <c r="G14" s="126">
-        <v>1.202307</v>
+        <v>1.1168260000000001</v>
       </c>
     </row>
     <row r="15">
@@ -14814,22 +14814,22 @@
         <v>1</v>
       </c>
       <c r="B17" s="145">
-        <v>5.0370330000000001</v>
+        <v>5.9011680000000002</v>
       </c>
       <c r="C17" s="146">
-        <v>3.8609990000000001</v>
+        <v>4.8360700000000003</v>
       </c>
       <c r="D17" s="147">
-        <v>2.1099999999999999</v>
+        <v>2.1699999999999999</v>
       </c>
       <c r="E17" s="148">
-        <v>0.035000000000000003</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="F17" s="149">
-        <v>1.1212690000000001</v>
+        <v>1.184048</v>
       </c>
       <c r="G17" s="150">
-        <v>22.627669999999998</v>
+        <v>29.410789999999999</v>
       </c>
     </row>
     <row r="18">
@@ -14883,22 +14883,22 @@
         <v>1</v>
       </c>
       <c r="B20" s="169">
-        <v>0.88689030000000002</v>
+        <v>0.83580339999999998</v>
       </c>
       <c r="C20" s="170">
-        <v>0.21148520000000001</v>
+        <v>0.20441809999999999</v>
       </c>
       <c r="D20" s="171">
-        <v>-0.5</v>
+        <v>-0.72999999999999998</v>
       </c>
       <c r="E20" s="172">
-        <v>0.61499999999999999</v>
+        <v>0.46300000000000002</v>
       </c>
       <c r="F20" s="173">
-        <v>0.55576979999999998</v>
+        <v>0.51751150000000001</v>
       </c>
       <c r="G20" s="174">
-        <v>1.4152880000000001</v>
+        <v>1.3498589999999999</v>
       </c>
     </row>
     <row r="21">
@@ -14952,22 +14952,22 @@
         <v>1</v>
       </c>
       <c r="B23" s="193">
-        <v>1.626641</v>
+        <v>1.5305740000000001</v>
       </c>
       <c r="C23" s="194">
-        <v>0.37549500000000002</v>
+        <v>0.36296830000000002</v>
       </c>
       <c r="D23" s="195">
-        <v>2.1099999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="E23" s="196">
-        <v>0.035000000000000003</v>
+        <v>0.072999999999999996</v>
       </c>
       <c r="F23" s="197">
-        <v>1.034665</v>
+        <v>0.9616036</v>
       </c>
       <c r="G23" s="198">
-        <v>2.557312</v>
+        <v>2.4361989999999998</v>
       </c>
     </row>
     <row r="24">
@@ -15021,22 +15021,22 @@
         <v>1</v>
       </c>
       <c r="B26" s="217">
-        <v>1.9747650000000001</v>
+        <v>1.8738760000000001</v>
       </c>
       <c r="C26" s="218">
-        <v>1.0055210000000001</v>
+        <v>0.96325939999999999</v>
       </c>
       <c r="D26" s="219">
-        <v>1.3400000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="E26" s="220">
-        <v>0.181</v>
+        <v>0.222</v>
       </c>
       <c r="F26" s="221">
-        <v>0.72794159999999997</v>
+        <v>0.68420060000000005</v>
       </c>
       <c r="G26" s="222">
-        <v>5.357157</v>
+        <v>5.1321339999999998</v>
       </c>
     </row>
     <row r="27">
@@ -15090,22 +15090,22 @@
         <v>1</v>
       </c>
       <c r="B29" s="241">
-        <v>3.7612040000000002</v>
+        <v>3.6828590000000001</v>
       </c>
       <c r="C29" s="242">
-        <v>1.0811360000000001</v>
+        <v>1.0825990000000001</v>
       </c>
       <c r="D29" s="243">
-        <v>4.6100000000000003</v>
+        <v>4.4299999999999997</v>
       </c>
       <c r="E29" s="244">
         <v>0</v>
       </c>
       <c r="F29" s="245">
-        <v>2.141184</v>
+        <v>2.069995</v>
       </c>
       <c r="G29" s="246">
-        <v>6.6069300000000002</v>
+        <v>6.5524079999999998</v>
       </c>
     </row>
     <row r="30">
@@ -15159,22 +15159,22 @@
         <v>1</v>
       </c>
       <c r="B32" s="265">
-        <v>2.7399420000000001</v>
+        <v>2.2883079999999998</v>
       </c>
       <c r="C32" s="266">
-        <v>1.478945</v>
+        <v>1.2416940000000001</v>
       </c>
       <c r="D32" s="267">
-        <v>1.8700000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="E32" s="268">
-        <v>0.062</v>
+        <v>0.127</v>
       </c>
       <c r="F32" s="269">
-        <v>0.95123179999999996</v>
+        <v>0.79000680000000001</v>
       </c>
       <c r="G32" s="270">
-        <v>7.8921700000000001</v>
+        <v>6.6282360000000002</v>
       </c>
     </row>
     <row r="33">
@@ -15228,22 +15228,22 @@
         <v>1</v>
       </c>
       <c r="B35" s="289">
-        <v>1.3599669999999999</v>
+        <v>1.3219860000000001</v>
       </c>
       <c r="C35" s="290">
-        <v>1.3041780000000001</v>
+        <v>1.2698989999999999</v>
       </c>
       <c r="D35" s="291">
-        <v>0.32000000000000001</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="E35" s="292">
-        <v>0.749</v>
+        <v>0.77100000000000002</v>
       </c>
       <c r="F35" s="293">
-        <v>0.2076086</v>
+        <v>0.20116999999999999</v>
       </c>
       <c r="G35" s="294">
-        <v>8.9086429999999997</v>
+        <v>8.6874110000000009</v>
       </c>
     </row>
     <row r="36">
@@ -15366,22 +15366,22 @@
         <v>1</v>
       </c>
       <c r="B41" s="337">
-        <v>17.253990000000002</v>
+        <v>16.773689999999999</v>
       </c>
       <c r="C41" s="338">
-        <v>29.132940000000001</v>
+        <v>28.334150000000001</v>
       </c>
       <c r="D41" s="339">
-        <v>1.69</v>
+        <v>1.6699999999999999</v>
       </c>
       <c r="E41" s="340">
-        <v>0.091999999999999999</v>
+        <v>0.095000000000000001</v>
       </c>
       <c r="F41" s="341">
-        <v>0.6304592</v>
+        <v>0.61203620000000003</v>
       </c>
       <c r="G41" s="342">
-        <v>472.1959</v>
+        <v>459.70600000000002</v>
       </c>
     </row>
     <row r="42">
@@ -15435,22 +15435,22 @@
         <v>1</v>
       </c>
       <c r="B44" s="361">
-        <v>0.37243209999999999</v>
+        <v>0.35458699999999999</v>
       </c>
       <c r="C44" s="362">
-        <v>0.39219389999999999</v>
+        <v>0.39412000000000003</v>
       </c>
       <c r="D44" s="363">
-        <v>-0.93999999999999995</v>
+        <v>-0.93000000000000005</v>
       </c>
       <c r="E44" s="364">
-        <v>0.34799999999999998</v>
+        <v>0.35099999999999998</v>
       </c>
       <c r="F44" s="365">
-        <v>0.047280200000000001</v>
+        <v>0.040143999999999999</v>
       </c>
       <c r="G44" s="366">
-        <v>2.9336929999999999</v>
+        <v>3.1320229999999998</v>
       </c>
     </row>
     <row r="45">
@@ -15504,22 +15504,22 @@
         <v>1</v>
       </c>
       <c r="B47" s="385">
-        <v>0.45476929999999999</v>
+        <v>0.3424371</v>
       </c>
       <c r="C47" s="386">
-        <v>1.73519</v>
+        <v>1.330891</v>
       </c>
       <c r="D47" s="387">
-        <v>-0.20999999999999999</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="E47" s="388">
-        <v>0.83599999999999997</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="F47" s="389">
-        <v>0.00025700000000000001</v>
+        <v>0.0001684</v>
       </c>
       <c r="G47" s="390">
-        <v>804.60609999999997</v>
+        <v>696.30280000000005</v>
       </c>
     </row>
     <row r="48">
@@ -15573,22 +15573,22 @@
         <v>32</v>
       </c>
       <c r="B50" s="409">
-        <v>0.53939040000000005</v>
+        <v>0.54502519999999999</v>
       </c>
       <c r="C50" s="410">
-        <v>0.098581299999999997</v>
+        <v>0.1008645</v>
       </c>
       <c r="D50" s="411">
-        <v>-3.3799999999999999</v>
+        <v>-3.2799999999999998</v>
       </c>
       <c r="E50" s="412">
         <v>0.001</v>
       </c>
       <c r="F50" s="413">
-        <v>0.37699349999999998</v>
+        <v>0.37921890000000003</v>
       </c>
       <c r="G50" s="414">
-        <v>0.7717427</v>
+        <v>0.78332740000000001</v>
       </c>
     </row>
     <row r="51">
@@ -15596,22 +15596,22 @@
         <v>33</v>
       </c>
       <c r="B51" s="417">
-        <v>2.6355279999999999</v>
+        <v>2.765965</v>
       </c>
       <c r="C51" s="418">
-        <v>3.1489370000000001</v>
+        <v>3.3051360000000001</v>
       </c>
       <c r="D51" s="419">
-        <v>0.81000000000000005</v>
+        <v>0.84999999999999998</v>
       </c>
       <c r="E51" s="420">
-        <v>0.41699999999999998</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="F51" s="421">
-        <v>0.25342500000000001</v>
+        <v>0.2659011</v>
       </c>
       <c r="G51" s="422">
-        <v>27.408539999999999</v>
+        <v>28.772220000000001</v>
       </c>
     </row>
     <row r="52">
@@ -15619,22 +15619,22 @@
         <v>34</v>
       </c>
       <c r="B52" s="425">
-        <v>0.39524730000000002</v>
+        <v>0.38835429999999999</v>
       </c>
       <c r="C52" s="426">
-        <v>0.13291629999999999</v>
+        <v>0.13184589999999999</v>
       </c>
       <c r="D52" s="427">
-        <v>-2.7599999999999998</v>
+        <v>-2.79</v>
       </c>
       <c r="E52" s="428">
-        <v>0.0060000000000000001</v>
+        <v>0.0050000000000000001</v>
       </c>
       <c r="F52" s="429">
-        <v>0.20446619999999999</v>
+        <v>0.19963919999999999</v>
       </c>
       <c r="G52" s="430">
-        <v>0.76404039999999995</v>
+        <v>0.75545790000000002</v>
       </c>
     </row>
     <row r="53">
@@ -15688,22 +15688,22 @@
         <v>32</v>
       </c>
       <c r="B55" s="449">
-        <v>0.9353108</v>
+        <v>0.92250730000000003</v>
       </c>
       <c r="C55" s="450">
-        <v>0.0879992</v>
+        <v>0.0876884</v>
       </c>
       <c r="D55" s="451">
-        <v>-0.70999999999999997</v>
+        <v>-0.84999999999999998</v>
       </c>
       <c r="E55" s="452">
-        <v>0.47699999999999998</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="F55" s="453">
-        <v>0.7778041</v>
+        <v>0.76570119999999997</v>
       </c>
       <c r="G55" s="454">
-        <v>1.1247130000000001</v>
+        <v>1.1114250000000001</v>
       </c>
     </row>
     <row r="56">
@@ -15711,22 +15711,22 @@
         <v>33</v>
       </c>
       <c r="B56" s="457">
-        <v>2.123621</v>
+        <v>2.374797</v>
       </c>
       <c r="C56" s="458">
-        <v>0.84742200000000001</v>
+        <v>0.96980049999999996</v>
       </c>
       <c r="D56" s="459">
-        <v>1.8899999999999999</v>
+        <v>2.1200000000000001</v>
       </c>
       <c r="E56" s="460">
-        <v>0.058999999999999997</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="F56" s="461">
-        <v>0.97142360000000005</v>
+        <v>1.0666450000000001</v>
       </c>
       <c r="G56" s="462">
-        <v>4.6424310000000002</v>
+        <v>5.287293</v>
       </c>
     </row>
     <row r="57">
@@ -15734,22 +15734,22 @@
         <v>34</v>
       </c>
       <c r="B57" s="465">
-        <v>0.54879860000000003</v>
+        <v>0.53307249999999995</v>
       </c>
       <c r="C57" s="466">
-        <v>0.1438643</v>
+        <v>0.14150689999999999</v>
       </c>
       <c r="D57" s="467">
-        <v>-2.29</v>
+        <v>-2.3700000000000001</v>
       </c>
       <c r="E57" s="468">
-        <v>0.021999999999999999</v>
+        <v>0.017999999999999999</v>
       </c>
       <c r="F57" s="469">
-        <v>0.32830350000000003</v>
+        <v>0.31683299999999998</v>
       </c>
       <c r="G57" s="470">
-        <v>0.91738240000000004</v>
+        <v>0.89689620000000003</v>
       </c>
     </row>
     <row r="58">
@@ -15803,22 +15803,22 @@
         <v>32</v>
       </c>
       <c r="B60" s="489">
-        <v>1.0314049999999999</v>
+        <v>0.98508379999999995</v>
       </c>
       <c r="C60" s="490">
-        <v>0.28750110000000001</v>
+        <v>0.27645700000000001</v>
       </c>
       <c r="D60" s="491">
-        <v>0.11</v>
+        <v>-0.050000000000000003</v>
       </c>
       <c r="E60" s="492">
-        <v>0.91200000000000003</v>
+        <v>0.95699999999999996</v>
       </c>
       <c r="F60" s="493">
-        <v>0.59725399999999995</v>
+        <v>0.56831529999999997</v>
       </c>
       <c r="G60" s="494">
-        <v>1.7811440000000001</v>
+        <v>1.7074849999999999</v>
       </c>
     </row>
     <row r="61">
@@ -15826,22 +15826,22 @@
         <v>33</v>
       </c>
       <c r="B61" s="497">
-        <v>1.8793260000000001</v>
+        <v>1.8339399999999999</v>
       </c>
       <c r="C61" s="498">
-        <v>0.74010690000000001</v>
+        <v>0.73414429999999997</v>
       </c>
       <c r="D61" s="499">
-        <v>1.6000000000000001</v>
+        <v>1.51</v>
       </c>
       <c r="E61" s="500">
-        <v>0.109</v>
+        <v>0.13</v>
       </c>
       <c r="F61" s="501">
-        <v>0.86853239999999998</v>
+        <v>0.83683700000000005</v>
       </c>
       <c r="G61" s="502">
-        <v>4.0664749999999996</v>
+        <v>4.019107</v>
       </c>
     </row>
     <row r="62">
@@ -15849,22 +15849,22 @@
         <v>34</v>
       </c>
       <c r="B62" s="505">
-        <v>0.8010216</v>
+        <v>0.84180639999999996</v>
       </c>
       <c r="C62" s="506">
-        <v>0.35892930000000001</v>
+        <v>0.37931219999999999</v>
       </c>
       <c r="D62" s="507">
-        <v>-0.5</v>
+        <v>-0.38</v>
       </c>
       <c r="E62" s="508">
-        <v>0.621</v>
+        <v>0.70199999999999996</v>
       </c>
       <c r="F62" s="509">
-        <v>0.33283560000000001</v>
+        <v>0.34806999999999999</v>
       </c>
       <c r="G62" s="510">
-        <v>1.9277850000000001</v>
+        <v>2.0359060000000002</v>
       </c>
     </row>
     <row r="63">
@@ -15895,22 +15895,22 @@
         <v>37</v>
       </c>
       <c r="B64" s="521">
-        <v>0.92959619999999998</v>
+        <v>0.9258748</v>
       </c>
       <c r="C64" s="522">
-        <v>0.091474600000000003</v>
+        <v>0.091593999999999995</v>
       </c>
       <c r="D64" s="523">
-        <v>-0.73999999999999999</v>
+        <v>-0.78000000000000003</v>
       </c>
       <c r="E64" s="524">
-        <v>0.45800000000000002</v>
+        <v>0.436</v>
       </c>
       <c r="F64" s="525">
-        <v>0.76653850000000001</v>
+        <v>0.76268550000000002</v>
       </c>
       <c r="G64" s="526">
-        <v>1.12734</v>
+        <v>1.1239809999999999</v>
       </c>
     </row>
     <row r="65">
@@ -15918,22 +15918,22 @@
         <v>38</v>
       </c>
       <c r="B65" s="529">
-        <v>1.132592</v>
+        <v>1.1170009999999999</v>
       </c>
       <c r="C65" s="530">
-        <v>0.059741900000000001</v>
+        <v>0.0594084</v>
       </c>
       <c r="D65" s="531">
-        <v>2.3599999999999999</v>
+        <v>2.0800000000000001</v>
       </c>
       <c r="E65" s="532">
-        <v>0.017999999999999999</v>
+        <v>0.036999999999999998</v>
       </c>
       <c r="F65" s="533">
-        <v>1.0213490000000001</v>
+        <v>1.006426</v>
       </c>
       <c r="G65" s="534">
-        <v>1.2559499999999999</v>
+        <v>1.239725</v>
       </c>
     </row>
     <row r="66">
@@ -15941,22 +15941,22 @@
         <v>39</v>
       </c>
       <c r="B66" s="537">
-        <v>0.55392509999999995</v>
+        <v>0.55401979999999995</v>
       </c>
       <c r="C66" s="538">
-        <v>0.039825399999999997</v>
+        <v>0.040144300000000001</v>
       </c>
       <c r="D66" s="539">
-        <v>-8.2200000000000006</v>
+        <v>-8.1500000000000004</v>
       </c>
       <c r="E66" s="540">
         <v>0</v>
       </c>
       <c r="F66" s="541">
-        <v>0.48111890000000002</v>
+        <v>0.48067019999999999</v>
       </c>
       <c r="G66" s="542">
-        <v>0.63774889999999995</v>
+        <v>0.63856250000000003</v>
       </c>
     </row>
     <row r="67">
@@ -15964,22 +15964,22 @@
         <v>40</v>
       </c>
       <c r="B67" s="545">
-        <v>0.82387730000000003</v>
+        <v>0.82982259999999997</v>
       </c>
       <c r="C67" s="546">
-        <v>0.053929400000000002</v>
+        <v>0.054772399999999999</v>
       </c>
       <c r="D67" s="547">
-        <v>-2.96</v>
+        <v>-2.8300000000000001</v>
       </c>
       <c r="E67" s="548">
-        <v>0.0030000000000000001</v>
+        <v>0.0050000000000000001</v>
       </c>
       <c r="F67" s="549">
-        <v>0.72467709999999996</v>
+        <v>0.72912460000000001</v>
       </c>
       <c r="G67" s="550">
-        <v>0.93665690000000001</v>
+        <v>0.94442780000000004</v>
       </c>
     </row>
     <row r="68">
@@ -15987,22 +15987,22 @@
         <v>41</v>
       </c>
       <c r="B68" s="553">
-        <v>1.246191</v>
+        <v>1.2453879999999999</v>
       </c>
       <c r="C68" s="554">
-        <v>0.0896087</v>
+        <v>0.090245599999999995</v>
       </c>
       <c r="D68" s="555">
-        <v>3.0600000000000001</v>
+        <v>3.0299999999999998</v>
       </c>
       <c r="E68" s="556">
         <v>0.002</v>
       </c>
       <c r="F68" s="557">
-        <v>1.082376</v>
+        <v>1.0804959999999999</v>
       </c>
       <c r="G68" s="558">
-        <v>1.4348000000000001</v>
+        <v>1.435443</v>
       </c>
     </row>
     <row r="69">
@@ -16010,22 +16010,22 @@
         <v>42</v>
       </c>
       <c r="B69" s="561">
-        <v>1.749809</v>
+        <v>1.7690079999999999</v>
       </c>
       <c r="C69" s="562">
-        <v>0.1459211</v>
+        <v>0.14878530000000001</v>
       </c>
       <c r="D69" s="563">
-        <v>6.71</v>
+        <v>6.7800000000000002</v>
       </c>
       <c r="E69" s="564">
         <v>0</v>
       </c>
       <c r="F69" s="565">
-        <v>1.485959</v>
+        <v>1.500162</v>
       </c>
       <c r="G69" s="566">
-        <v>2.0605090000000001</v>
+        <v>2.0860340000000002</v>
       </c>
     </row>
     <row r="70">
@@ -16033,10 +16033,10 @@
         <v>43</v>
       </c>
       <c r="B70" s="569">
-        <v>2.0242689999999999</v>
+        <v>2.025455</v>
       </c>
       <c r="C70" s="570">
-        <v>0.37233070000000001</v>
+        <v>0.3731467</v>
       </c>
       <c r="D70" s="571">
         <v>3.8300000000000001</v>
@@ -16045,10 +16045,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="573">
-        <v>1.411575</v>
+        <v>1.4115850000000001</v>
       </c>
       <c r="G70" s="574">
-        <v>2.9029039999999999</v>
+        <v>2.906285</v>
       </c>
     </row>
     <row r="71">
@@ -16056,22 +16056,22 @@
         <v>44</v>
       </c>
       <c r="B71" s="577">
-        <v>0.94920110000000002</v>
+        <v>0.92609660000000005</v>
       </c>
       <c r="C71" s="578">
-        <v>0.1073214</v>
+        <v>0.1061122</v>
       </c>
       <c r="D71" s="579">
-        <v>-0.46000000000000002</v>
+        <v>-0.67000000000000004</v>
       </c>
       <c r="E71" s="580">
-        <v>0.64500000000000002</v>
+        <v>0.503</v>
       </c>
       <c r="F71" s="581">
-        <v>0.76053139999999997</v>
+        <v>0.73981909999999995</v>
       </c>
       <c r="G71" s="582">
-        <v>1.1846749999999999</v>
+        <v>1.159276</v>
       </c>
     </row>
     <row r="72">
@@ -16079,22 +16079,22 @@
         <v>45</v>
       </c>
       <c r="B72" s="585">
-        <v>0.7531833</v>
+        <v>0.74355090000000001</v>
       </c>
       <c r="C72" s="586">
-        <v>0.080729599999999999</v>
+        <v>0.080754699999999999</v>
       </c>
       <c r="D72" s="587">
-        <v>-2.6400000000000001</v>
+        <v>-2.73</v>
       </c>
       <c r="E72" s="588">
-        <v>0.0080000000000000002</v>
+        <v>0.0060000000000000001</v>
       </c>
       <c r="F72" s="589">
-        <v>0.61047099999999999</v>
+        <v>0.60098609999999997</v>
       </c>
       <c r="G72" s="590">
-        <v>0.92925789999999997</v>
+        <v>0.9199347</v>
       </c>
     </row>
     <row r="73">
@@ -16102,22 +16102,22 @@
         <v>46</v>
       </c>
       <c r="B73" s="593">
-        <v>0.43815799999999999</v>
+        <v>0.4609858</v>
       </c>
       <c r="C73" s="594">
-        <v>0.092071700000000006</v>
+        <v>0.1000303</v>
       </c>
       <c r="D73" s="595">
-        <v>-3.9300000000000002</v>
+        <v>-3.5699999999999999</v>
       </c>
       <c r="E73" s="596">
         <v>0</v>
       </c>
       <c r="F73" s="597">
-        <v>0.29024499999999998</v>
+        <v>0.30128919999999998</v>
       </c>
       <c r="G73" s="598">
-        <v>0.66144950000000002</v>
+        <v>0.70532870000000003</v>
       </c>
     </row>
     <row r="74">
@@ -16125,22 +16125,22 @@
         <v>47</v>
       </c>
       <c r="B74" s="601">
-        <v>0.83370889999999998</v>
+        <v>0.86585610000000002</v>
       </c>
       <c r="C74" s="602">
-        <v>0.089246900000000004</v>
+        <v>0.093958899999999998</v>
       </c>
       <c r="D74" s="603">
-        <v>-1.7</v>
+        <v>-1.3300000000000001</v>
       </c>
       <c r="E74" s="604">
-        <v>0.088999999999999996</v>
+        <v>0.184</v>
       </c>
       <c r="F74" s="605">
-        <v>0.67591950000000001</v>
+        <v>0.69996610000000004</v>
       </c>
       <c r="G74" s="606">
-        <v>1.028333</v>
+        <v>1.071061</v>
       </c>
     </row>
     <row r="75">
@@ -16148,22 +16148,22 @@
         <v>48</v>
       </c>
       <c r="B75" s="609">
-        <v>1.1558600000000001</v>
+        <v>0.8717049</v>
       </c>
       <c r="C75" s="610">
-        <v>0.0146988</v>
+        <v>0.0111366</v>
       </c>
       <c r="D75" s="611">
-        <v>11.390000000000001</v>
+        <v>-10.75</v>
       </c>
       <c r="E75" s="612">
         <v>0</v>
       </c>
       <c r="F75" s="613">
-        <v>1.127407</v>
+        <v>0.85014849999999997</v>
       </c>
       <c r="G75" s="614">
-        <v>1.185031</v>
+        <v>0.89380780000000004</v>
       </c>
     </row>
     <row r="76">
@@ -16171,22 +16171,22 @@
         <v>49</v>
       </c>
       <c r="B76" s="617">
-        <v>0.98925529999999995</v>
+        <v>0.496083</v>
       </c>
       <c r="C76" s="618">
-        <v>0.0021779</v>
+        <v>0.069649199999999995</v>
       </c>
       <c r="D76" s="619">
-        <v>-4.9100000000000001</v>
+        <v>-4.9900000000000002</v>
       </c>
       <c r="E76" s="620">
         <v>0</v>
       </c>
       <c r="F76" s="621">
-        <v>0.98499579999999998</v>
+        <v>0.37674469999999999</v>
       </c>
       <c r="G76" s="622">
-        <v>0.99353320000000001</v>
+        <v>0.6532232</v>
       </c>
     </row>
     <row r="77">
@@ -16194,22 +16194,22 @@
         <v>50</v>
       </c>
       <c r="B77" s="625">
-        <v>0.84810379999999996</v>
+        <v>0.83397880000000002</v>
       </c>
       <c r="C77" s="626">
-        <v>0.0587501</v>
+        <v>0.058173999999999997</v>
       </c>
       <c r="D77" s="627">
-        <v>-2.3799999999999999</v>
+        <v>-2.6000000000000001</v>
       </c>
       <c r="E77" s="628">
-        <v>0.017000000000000001</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="F77" s="629">
-        <v>0.74043060000000005</v>
+        <v>0.72741069999999997</v>
       </c>
       <c r="G77" s="630">
-        <v>0.97143489999999999</v>
+        <v>0.95615950000000005</v>
       </c>
     </row>
     <row r="78">
@@ -16217,22 +16217,22 @@
         <v>51</v>
       </c>
       <c r="B78" s="633">
-        <v>0.79476409999999997</v>
+        <v>0.79178479999999996</v>
       </c>
       <c r="C78" s="634">
-        <v>0.099931300000000001</v>
+        <v>0.1003208</v>
       </c>
       <c r="D78" s="635">
-        <v>-1.8300000000000001</v>
+        <v>-1.8400000000000001</v>
       </c>
       <c r="E78" s="636">
-        <v>0.068000000000000005</v>
+        <v>0.065000000000000002</v>
       </c>
       <c r="F78" s="637">
-        <v>0.62117020000000001</v>
+        <v>0.61767240000000001</v>
       </c>
       <c r="G78" s="638">
-        <v>1.0168710000000001</v>
+        <v>1.014977</v>
       </c>
     </row>
     <row r="79">
@@ -16240,22 +16240,22 @@
         <v>52</v>
       </c>
       <c r="B79" s="641">
-        <v>0.74427109999999996</v>
+        <v>0.73503300000000005</v>
       </c>
       <c r="C79" s="642">
-        <v>0.067731399999999997</v>
+        <v>0.067431400000000002</v>
       </c>
       <c r="D79" s="643">
-        <v>-3.25</v>
+        <v>-3.3599999999999999</v>
       </c>
       <c r="E79" s="644">
         <v>0.001</v>
       </c>
       <c r="F79" s="645">
-        <v>0.62268539999999995</v>
+        <v>0.61407049999999996</v>
       </c>
       <c r="G79" s="646">
-        <v>0.88959759999999999</v>
+        <v>0.87982329999999998</v>
       </c>
     </row>
     <row r="80">
@@ -16263,22 +16263,22 @@
         <v>53</v>
       </c>
       <c r="B80" s="649">
-        <v>0.98685630000000002</v>
+        <v>0.9719489</v>
       </c>
       <c r="C80" s="650">
-        <v>0.088574100000000003</v>
+        <v>0.087948100000000001</v>
       </c>
       <c r="D80" s="651">
-        <v>-0.15</v>
+        <v>-0.31</v>
       </c>
       <c r="E80" s="652">
-        <v>0.88300000000000001</v>
+        <v>0.753</v>
       </c>
       <c r="F80" s="653">
-        <v>0.82766649999999997</v>
+        <v>0.81399429999999995</v>
       </c>
       <c r="G80" s="654">
-        <v>1.1766639999999999</v>
+        <v>1.1605540000000001</v>
       </c>
     </row>
     <row r="81">
@@ -16286,22 +16286,22 @@
         <v>54</v>
       </c>
       <c r="B81" s="657">
-        <v>0.98304250000000004</v>
+        <v>0.92573309999999998</v>
       </c>
       <c r="C81" s="658">
-        <v>0.56989699999999999</v>
+        <v>0.53796909999999998</v>
       </c>
       <c r="D81" s="659">
-        <v>-0.029999999999999999</v>
+        <v>-0.13</v>
       </c>
       <c r="E81" s="660">
-        <v>0.97599999999999998</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="F81" s="661">
-        <v>0.31557829999999998</v>
+        <v>0.29636649999999998</v>
       </c>
       <c r="G81" s="662">
-        <v>3.062227</v>
+        <v>2.891629</v>
       </c>
     </row>
     <row r="82">
@@ -16309,22 +16309,22 @@
         <v>55</v>
       </c>
       <c r="B82" s="665">
-        <v>1.107918</v>
+        <v>1.100746</v>
       </c>
       <c r="C82" s="666">
-        <v>0.043362600000000001</v>
+        <v>0.0434188</v>
       </c>
       <c r="D82" s="667">
-        <v>2.6200000000000001</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="E82" s="668">
-        <v>0.0089999999999999993</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="F82" s="669">
-        <v>1.0261070000000001</v>
+        <v>1.018853</v>
       </c>
       <c r="G82" s="670">
-        <v>1.1962520000000001</v>
+        <v>1.1892210000000001</v>
       </c>
     </row>
     <row r="83">
@@ -16332,22 +16332,22 @@
         <v>56</v>
       </c>
       <c r="B83" s="673">
-        <v>1.0007079999999999</v>
+        <v>0.95042260000000001</v>
       </c>
       <c r="C83" s="674">
-        <v>0.00042920000000000002</v>
+        <v>0.024829</v>
       </c>
       <c r="D83" s="675">
-        <v>1.6499999999999999</v>
+        <v>-1.95</v>
       </c>
       <c r="E83" s="676">
-        <v>0.099000000000000005</v>
+        <v>0.051999999999999998</v>
       </c>
       <c r="F83" s="677">
-        <v>0.99986730000000001</v>
+        <v>0.9029836</v>
       </c>
       <c r="G83" s="678">
-        <v>1.00155</v>
+        <v>1.000354</v>
       </c>
     </row>
     <row r="84">
@@ -16355,22 +16355,22 @@
         <v>57</v>
       </c>
       <c r="B84" s="681">
-        <v>0.81167319999999998</v>
+        <v>0.80393870000000001</v>
       </c>
       <c r="C84" s="682">
-        <v>0.045144799999999999</v>
+        <v>0.045161899999999998</v>
       </c>
       <c r="D84" s="683">
-        <v>-3.75</v>
+        <v>-3.8799999999999999</v>
       </c>
       <c r="E84" s="684">
         <v>0</v>
       </c>
       <c r="F84" s="685">
-        <v>0.72784329999999997</v>
+        <v>0.72012189999999998</v>
       </c>
       <c r="G84" s="686">
-        <v>0.90515840000000003</v>
+        <v>0.89751119999999995</v>
       </c>
     </row>
     <row r="85">
@@ -16378,22 +16378,22 @@
         <v>58</v>
       </c>
       <c r="B85" s="689">
-        <v>0.92627060000000006</v>
+        <v>0.9276721</v>
       </c>
       <c r="C85" s="690">
-        <v>0.074018200000000006</v>
+        <v>0.074581300000000003</v>
       </c>
       <c r="D85" s="691">
-        <v>-0.95999999999999997</v>
+        <v>-0.93000000000000005</v>
       </c>
       <c r="E85" s="692">
-        <v>0.33800000000000002</v>
+        <v>0.34999999999999998</v>
       </c>
       <c r="F85" s="693">
-        <v>0.79198769999999996</v>
+        <v>0.79243050000000004</v>
       </c>
       <c r="G85" s="694">
-        <v>1.083321</v>
+        <v>1.085995</v>
       </c>
     </row>
     <row r="86">
@@ -16401,22 +16401,22 @@
         <v>59</v>
       </c>
       <c r="B86" s="697">
-        <v>0.90384710000000001</v>
+        <v>0.89644170000000001</v>
       </c>
       <c r="C86" s="698">
-        <v>0.037866999999999998</v>
+        <v>0.037862</v>
       </c>
       <c r="D86" s="699">
-        <v>-2.4100000000000001</v>
+        <v>-2.5899999999999999</v>
       </c>
       <c r="E86" s="700">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="F86" s="701">
-        <v>0.83259450000000002</v>
+        <v>0.82522200000000001</v>
       </c>
       <c r="G86" s="702">
-        <v>0.9811974</v>
+        <v>0.97380789999999995</v>
       </c>
     </row>
     <row r="87">
@@ -16424,22 +16424,22 @@
         <v>60</v>
       </c>
       <c r="B87" s="705">
-        <v>0.89171529999999999</v>
+        <v>0.8901675</v>
       </c>
       <c r="C87" s="706">
-        <v>0.084216600000000003</v>
+        <v>0.084538699999999995</v>
       </c>
       <c r="D87" s="707">
-        <v>-1.21</v>
+        <v>-1.23</v>
       </c>
       <c r="E87" s="708">
-        <v>0.22500000000000001</v>
+        <v>0.221</v>
       </c>
       <c r="F87" s="709">
-        <v>0.74103019999999997</v>
+        <v>0.73898149999999996</v>
       </c>
       <c r="G87" s="710">
-        <v>1.0730409999999999</v>
+        <v>1.072284</v>
       </c>
     </row>
     <row r="88">
@@ -16447,22 +16447,22 @@
         <v>61</v>
       </c>
       <c r="B88" s="713">
-        <v>0.8535604</v>
+        <v>0.86292570000000002</v>
       </c>
       <c r="C88" s="714">
-        <v>0.065852099999999997</v>
+        <v>0.0672185</v>
       </c>
       <c r="D88" s="715">
-        <v>-2.0499999999999998</v>
+        <v>-1.8899999999999999</v>
       </c>
       <c r="E88" s="716">
-        <v>0.040000000000000001</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="F88" s="717">
-        <v>0.73377720000000002</v>
+        <v>0.74074399999999996</v>
       </c>
       <c r="G88" s="718">
-        <v>0.99289729999999998</v>
+        <v>1.005261</v>
       </c>
     </row>
     <row r="89">
@@ -16470,22 +16470,22 @@
         <v>62</v>
       </c>
       <c r="B89" s="721">
-        <v>0.95844810000000003</v>
+        <v>0.95887739999999999</v>
       </c>
       <c r="C89" s="722">
-        <v>0.038092599999999997</v>
+        <v>0.038415499999999998</v>
       </c>
       <c r="D89" s="723">
-        <v>-1.0700000000000001</v>
+        <v>-1.05</v>
       </c>
       <c r="E89" s="724">
-        <v>0.28599999999999998</v>
+        <v>0.29499999999999999</v>
       </c>
       <c r="F89" s="725">
-        <v>0.88662189999999996</v>
+        <v>0.8864647</v>
       </c>
       <c r="G89" s="726">
-        <v>1.0360929999999999</v>
+        <v>1.0372049999999999</v>
       </c>
     </row>
     <row r="90">
@@ -16493,22 +16493,22 @@
         <v>63</v>
       </c>
       <c r="B90" s="729">
-        <v>0.87342750000000002</v>
+        <v>0.86736639999999998</v>
       </c>
       <c r="C90" s="730">
-        <v>0.0359738</v>
+        <v>0.036023899999999998</v>
       </c>
       <c r="D90" s="731">
-        <v>-3.29</v>
+        <v>-3.4300000000000002</v>
       </c>
       <c r="E90" s="732">
         <v>0.001</v>
       </c>
       <c r="F90" s="733">
-        <v>0.80569089999999999</v>
+        <v>0.7995582</v>
       </c>
       <c r="G90" s="734">
-        <v>0.9468588</v>
+        <v>0.94092520000000002</v>
       </c>
     </row>
     <row r="91">
@@ -16539,22 +16539,22 @@
         <v>65</v>
       </c>
       <c r="B92" s="745">
-        <v>0.68675419999999998</v>
+        <v>0.70652539999999997</v>
       </c>
       <c r="C92" s="746">
-        <v>0.11198660000000001</v>
+        <v>0.1207949</v>
       </c>
       <c r="D92" s="747">
-        <v>-2.2999999999999998</v>
+        <v>-2.0299999999999998</v>
       </c>
       <c r="E92" s="748">
-        <v>0.021000000000000001</v>
+        <v>0.042000000000000003</v>
       </c>
       <c r="F92" s="749">
-        <v>0.49888320000000003</v>
+        <v>0.50535620000000003</v>
       </c>
       <c r="G92" s="750">
-        <v>0.9453743</v>
+        <v>0.98777490000000001</v>
       </c>
     </row>
     <row r="93">
@@ -16562,22 +16562,22 @@
         <v>66</v>
       </c>
       <c r="B93" s="753">
-        <v>0.89083939999999995</v>
+        <v>0.89903529999999998</v>
       </c>
       <c r="C93" s="754">
-        <v>0.1531508</v>
+        <v>0.1618087</v>
       </c>
       <c r="D93" s="755">
-        <v>-0.67000000000000004</v>
+        <v>-0.58999999999999997</v>
       </c>
       <c r="E93" s="756">
-        <v>0.501</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="F93" s="757">
-        <v>0.63600880000000004</v>
+        <v>0.63179640000000004</v>
       </c>
       <c r="G93" s="758">
-        <v>1.247773</v>
+        <v>1.279312</v>
       </c>
     </row>
     <row r="94">
@@ -16585,22 +16585,22 @@
         <v>67</v>
       </c>
       <c r="B94" s="761">
-        <v>0.72419359999999999</v>
+        <v>0.7210126</v>
       </c>
       <c r="C94" s="762">
-        <v>0.1133002</v>
+        <v>0.1187839</v>
       </c>
       <c r="D94" s="763">
-        <v>-2.0600000000000001</v>
+        <v>-1.99</v>
       </c>
       <c r="E94" s="764">
-        <v>0.039</v>
+        <v>0.047</v>
       </c>
       <c r="F94" s="765">
-        <v>0.53294699999999995</v>
+        <v>0.52204850000000003</v>
       </c>
       <c r="G94" s="766">
-        <v>0.98406850000000001</v>
+        <v>0.99580630000000003</v>
       </c>
     </row>
     <row r="95">
@@ -16608,22 +16608,22 @@
         <v>68</v>
       </c>
       <c r="B95" s="769">
-        <v>1.1007769999999999</v>
+        <v>1.131802</v>
       </c>
       <c r="C95" s="770">
-        <v>0.1683605</v>
+        <v>0.1823563</v>
       </c>
       <c r="D95" s="771">
-        <v>0.63</v>
+        <v>0.77000000000000002</v>
       </c>
       <c r="E95" s="772">
-        <v>0.53000000000000003</v>
+        <v>0.442</v>
       </c>
       <c r="F95" s="773">
-        <v>0.81566280000000002</v>
+        <v>0.8253239</v>
       </c>
       <c r="G95" s="774">
-        <v>1.4855529999999999</v>
+        <v>1.552087</v>
       </c>
     </row>
     <row r="96">
@@ -16654,22 +16654,22 @@
         <v>70</v>
       </c>
       <c r="B97" s="785">
-        <v>0.95832810000000002</v>
+        <v>0.95155540000000005</v>
       </c>
       <c r="C97" s="786">
-        <v>0.057861999999999997</v>
+        <v>0.057977000000000001</v>
       </c>
       <c r="D97" s="787">
-        <v>-0.69999999999999996</v>
+        <v>-0.81999999999999995</v>
       </c>
       <c r="E97" s="788">
-        <v>0.48099999999999998</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="F97" s="789">
-        <v>0.85137390000000002</v>
+        <v>0.84444520000000001</v>
       </c>
       <c r="G97" s="790">
-        <v>1.0787180000000001</v>
+        <v>1.072252</v>
       </c>
     </row>
     <row r="98">
@@ -16677,22 +16677,22 @@
         <v>71</v>
       </c>
       <c r="B98" s="793">
-        <v>1.0142770000000001</v>
+        <v>1.033034</v>
       </c>
       <c r="C98" s="794">
-        <v>0.076773099999999997</v>
+        <v>0.078872899999999996</v>
       </c>
       <c r="D98" s="795">
-        <v>0.19</v>
+        <v>0.42999999999999999</v>
       </c>
       <c r="E98" s="796">
-        <v>0.85099999999999998</v>
+        <v>0.67000000000000004</v>
       </c>
       <c r="F98" s="797">
-        <v>0.8744343</v>
+        <v>0.88945629999999998</v>
       </c>
       <c r="G98" s="798">
-        <v>1.176485</v>
+        <v>1.1997880000000001</v>
       </c>
     </row>
     <row r="99">
@@ -16700,22 +16700,22 @@
         <v>72</v>
       </c>
       <c r="B99" s="801">
-        <v>0.94270109999999996</v>
+        <v>0.903806</v>
       </c>
       <c r="C99" s="802">
-        <v>0.1198224</v>
+        <v>0.116607</v>
       </c>
       <c r="D99" s="803">
-        <v>-0.46000000000000002</v>
+        <v>-0.78000000000000003</v>
       </c>
       <c r="E99" s="804">
-        <v>0.64200000000000002</v>
+        <v>0.433</v>
       </c>
       <c r="F99" s="805">
-        <v>0.73482119999999995</v>
+        <v>0.70186760000000004</v>
       </c>
       <c r="G99" s="806">
-        <v>1.20939</v>
+        <v>1.163845</v>
       </c>
     </row>
     <row r="100">
@@ -16723,22 +16723,22 @@
         <v>73</v>
       </c>
       <c r="B100" s="809">
-        <v>0.83651089999999995</v>
+        <v>0.84343500000000005</v>
       </c>
       <c r="C100" s="810">
-        <v>0.1943754</v>
+        <v>0.19894990000000001</v>
       </c>
       <c r="D100" s="811">
-        <v>-0.77000000000000002</v>
+        <v>-0.71999999999999997</v>
       </c>
       <c r="E100" s="812">
-        <v>0.442</v>
+        <v>0.46999999999999997</v>
       </c>
       <c r="F100" s="813">
-        <v>0.53049670000000004</v>
+        <v>0.53121430000000003</v>
       </c>
       <c r="G100" s="814">
-        <v>1.319048</v>
+        <v>1.3391630000000001</v>
       </c>
     </row>
     <row r="101">
@@ -16746,22 +16746,22 @@
         <v>74</v>
       </c>
       <c r="B101" s="817">
-        <v>1.5718669999999999</v>
+        <v>1.552759</v>
       </c>
       <c r="C101" s="818">
-        <v>0.33219650000000001</v>
+        <v>0.32955980000000001</v>
       </c>
       <c r="D101" s="819">
-        <v>2.1400000000000001</v>
+        <v>2.0699999999999999</v>
       </c>
       <c r="E101" s="820">
-        <v>0.032000000000000001</v>
+        <v>0.037999999999999999</v>
       </c>
       <c r="F101" s="821">
-        <v>1.038781</v>
+        <v>1.0243390000000001</v>
       </c>
       <c r="G101" s="822">
-        <v>2.3785249999999998</v>
+        <v>2.3537710000000001</v>
       </c>
     </row>
     <row r="102">
@@ -16769,22 +16769,22 @@
         <v>75</v>
       </c>
       <c r="B102" s="825">
-        <v>0.47692600000000002</v>
+        <v>0.45819100000000001</v>
       </c>
       <c r="C102" s="826">
-        <v>0.70169110000000001</v>
+        <v>0.67507430000000002</v>
       </c>
       <c r="D102" s="827">
-        <v>-0.5</v>
+        <v>-0.53000000000000003</v>
       </c>
       <c r="E102" s="828">
-        <v>0.61499999999999999</v>
+        <v>0.59599999999999998</v>
       </c>
       <c r="F102" s="829">
-        <v>0.0266745</v>
+        <v>0.025523000000000001</v>
       </c>
       <c r="G102" s="830">
-        <v>8.5271889999999999</v>
+        <v>8.2254869999999993</v>
       </c>
     </row>
     <row r="103">
@@ -16792,22 +16792,22 @@
         <v>76</v>
       </c>
       <c r="B103" s="833">
-        <v>1.046832</v>
+        <v>1.0109870000000001</v>
       </c>
       <c r="C103" s="834">
-        <v>0.089726</v>
+        <v>0.088125800000000004</v>
       </c>
       <c r="D103" s="835">
-        <v>0.53000000000000003</v>
+        <v>0.13</v>
       </c>
       <c r="E103" s="836">
-        <v>0.59299999999999997</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="F103" s="837">
-        <v>0.88495060000000003</v>
+        <v>0.85221239999999998</v>
       </c>
       <c r="G103" s="838">
-        <v>1.238327</v>
+        <v>1.1993419999999999</v>
       </c>
     </row>
     <row r="104">
@@ -16815,22 +16815,22 @@
         <v>77</v>
       </c>
       <c r="B104" s="841">
-        <v>1.2516149999999999</v>
+        <v>1.2168159999999999</v>
       </c>
       <c r="C104" s="842">
-        <v>0.12363739999999999</v>
+        <v>0.1218915</v>
       </c>
       <c r="D104" s="843">
-        <v>2.27</v>
+        <v>1.96</v>
       </c>
       <c r="E104" s="844">
-        <v>0.023</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F104" s="845">
-        <v>1.0313049999999999</v>
+        <v>0.99990310000000004</v>
       </c>
       <c r="G104" s="846">
-        <v>1.518988</v>
+        <v>1.4807840000000001</v>
       </c>
     </row>
     <row r="105">
@@ -16838,22 +16838,22 @@
         <v>78</v>
       </c>
       <c r="B105" s="849">
-        <v>1.2847170000000001</v>
+        <v>1.290392</v>
       </c>
       <c r="C105" s="850">
-        <v>0.16573479999999999</v>
+        <v>0.16810249999999999</v>
       </c>
       <c r="D105" s="851">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="E105" s="852">
-        <v>0.051999999999999998</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="F105" s="853">
-        <v>0.99769629999999998</v>
+        <v>0.99961690000000003</v>
       </c>
       <c r="G105" s="854">
-        <v>1.654309</v>
+        <v>1.6657500000000001</v>
       </c>
     </row>
     <row r="106">
@@ -16861,22 +16861,22 @@
         <v>79</v>
       </c>
       <c r="B106" s="857">
-        <v>0.48221199999999997</v>
+        <v>0.4782998</v>
       </c>
       <c r="C106" s="858">
-        <v>0.32106839999999998</v>
+        <v>0.31967430000000002</v>
       </c>
       <c r="D106" s="859">
         <v>-1.1000000000000001</v>
       </c>
       <c r="E106" s="860">
-        <v>0.27300000000000002</v>
+        <v>0.27000000000000002</v>
       </c>
       <c r="F106" s="861">
-        <v>0.13076380000000001</v>
+        <v>0.12906100000000001</v>
       </c>
       <c r="G106" s="862">
-        <v>1.778232</v>
+        <v>1.772578</v>
       </c>
     </row>
     <row r="107">
@@ -16884,22 +16884,22 @@
         <v>80</v>
       </c>
       <c r="B107" s="865">
-        <v>1.7058739999999999</v>
+        <v>1.6867700000000001</v>
       </c>
       <c r="C107" s="866">
-        <v>0.31533899999999998</v>
+        <v>0.32011099999999998</v>
       </c>
       <c r="D107" s="867">
-        <v>2.8900000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="E107" s="868">
-        <v>0.0040000000000000001</v>
+        <v>0.0060000000000000001</v>
       </c>
       <c r="F107" s="869">
-        <v>1.1874039999999999</v>
+        <v>1.1628320000000001</v>
       </c>
       <c r="G107" s="870">
-        <v>2.4507310000000002</v>
+        <v>2.4467789999999998</v>
       </c>
     </row>
     <row r="108">
@@ -16907,22 +16907,22 @@
         <v>81</v>
       </c>
       <c r="B108" s="873">
-        <v>0.95581210000000005</v>
+        <v>0.93534439999999997</v>
       </c>
       <c r="C108" s="874">
-        <v>0.25414979999999998</v>
+        <v>0.2500503</v>
       </c>
       <c r="D108" s="875">
-        <v>-0.17000000000000001</v>
+        <v>-0.25</v>
       </c>
       <c r="E108" s="876">
-        <v>0.86499999999999999</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="F108" s="877">
-        <v>0.56759510000000002</v>
+        <v>0.55387980000000003</v>
       </c>
       <c r="G108" s="878">
-        <v>1.6095569999999999</v>
+        <v>1.579529</v>
       </c>
     </row>
     <row r="109">
@@ -16930,22 +16930,22 @@
         <v>82</v>
       </c>
       <c r="B109" s="881">
-        <v>0.96167159999999996</v>
+        <v>0.94769669999999995</v>
       </c>
       <c r="C109" s="882">
-        <v>0.1121625</v>
+        <v>0.1125345</v>
       </c>
       <c r="D109" s="883">
-        <v>-0.34000000000000002</v>
+        <v>-0.45000000000000001</v>
       </c>
       <c r="E109" s="884">
-        <v>0.73799999999999999</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="F109" s="885">
-        <v>0.76515370000000005</v>
+        <v>0.75091920000000001</v>
       </c>
       <c r="G109" s="886">
-        <v>1.2086619999999999</v>
+        <v>1.1960390000000001</v>
       </c>
     </row>
     <row r="110">
@@ -16953,22 +16953,22 @@
         <v>83</v>
       </c>
       <c r="B110" s="889">
-        <v>1.0845769999999999</v>
+        <v>1.0970610000000001</v>
       </c>
       <c r="C110" s="890">
-        <v>0.1804064</v>
+        <v>0.18436849999999999</v>
       </c>
       <c r="D110" s="891">
-        <v>0.48999999999999999</v>
+        <v>0.55000000000000005</v>
       </c>
       <c r="E110" s="892">
-        <v>0.625</v>
+        <v>0.58099999999999996</v>
       </c>
       <c r="F110" s="893">
-        <v>0.78284010000000004</v>
+        <v>0.7891878</v>
       </c>
       <c r="G110" s="894">
-        <v>1.5026139999999999</v>
+        <v>1.525039</v>
       </c>
     </row>
     <row r="111">
@@ -16976,22 +16976,22 @@
         <v>84</v>
       </c>
       <c r="B111" s="897">
-        <v>0.97182049999999998</v>
+        <v>0.96180670000000001</v>
       </c>
       <c r="C111" s="898">
-        <v>0.056768600000000002</v>
+        <v>0.0569519</v>
       </c>
       <c r="D111" s="899">
-        <v>-0.48999999999999999</v>
+        <v>-0.66000000000000003</v>
       </c>
       <c r="E111" s="900">
-        <v>0.625</v>
+        <v>0.51100000000000001</v>
       </c>
       <c r="F111" s="901">
-        <v>0.86668920000000005</v>
+        <v>0.85641690000000004</v>
       </c>
       <c r="G111" s="902">
-        <v>1.089704</v>
+        <v>1.080166</v>
       </c>
     </row>
     <row r="112">
@@ -16999,22 +16999,22 @@
         <v>85</v>
       </c>
       <c r="B112" s="905">
-        <v>1.411476</v>
+        <v>1.5117529999999999</v>
       </c>
       <c r="C112" s="906">
-        <v>0.21836430000000001</v>
+        <v>0.24035809999999999</v>
       </c>
       <c r="D112" s="907">
-        <v>2.23</v>
+        <v>2.6000000000000001</v>
       </c>
       <c r="E112" s="908">
-        <v>0.025999999999999999</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="F112" s="909">
-        <v>1.042287</v>
+        <v>1.1069960000000001</v>
       </c>
       <c r="G112" s="910">
-        <v>1.9114359999999999</v>
+        <v>2.064505</v>
       </c>
     </row>
     <row r="113">
@@ -17022,22 +17022,22 @@
         <v>86</v>
       </c>
       <c r="B113" s="913">
-        <v>1.113626</v>
+        <v>1.110541</v>
       </c>
       <c r="C113" s="914">
-        <v>0.089819399999999994</v>
+        <v>0.089934100000000003</v>
       </c>
       <c r="D113" s="915">
-        <v>1.3300000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="E113" s="916">
-        <v>0.182</v>
+        <v>0.19500000000000001</v>
       </c>
       <c r="F113" s="917">
-        <v>0.95079309999999995</v>
+        <v>0.94755060000000002</v>
       </c>
       <c r="G113" s="918">
-        <v>1.3043469999999999</v>
+        <v>1.3015680000000001</v>
       </c>
     </row>
     <row r="114">
@@ -17045,22 +17045,22 @@
         <v>87</v>
       </c>
       <c r="B114" s="921">
-        <v>1.385051</v>
+        <v>1.4293039999999999</v>
       </c>
       <c r="C114" s="922">
-        <v>0.35508820000000002</v>
+        <v>0.37258340000000001</v>
       </c>
       <c r="D114" s="923">
-        <v>1.27</v>
+        <v>1.3700000000000001</v>
       </c>
       <c r="E114" s="924">
-        <v>0.20399999999999999</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="F114" s="925">
-        <v>0.83799480000000004</v>
+        <v>0.85750789999999999</v>
       </c>
       <c r="G114" s="926">
-        <v>2.2892320000000002</v>
+        <v>2.3823820000000002</v>
       </c>
     </row>
     <row r="115">
@@ -17068,22 +17068,22 @@
         <v>88</v>
       </c>
       <c r="B115" s="936">
-        <v>6.9000000000000002e-127</v>
+        <v>120.6125</v>
       </c>
       <c r="C115" s="937">
-        <v>1.8000000000000001e-125</v>
+        <v>83.814819999999998</v>
       </c>
       <c r="D115" s="938">
-        <v>-11.33</v>
+        <v>6.9000000000000004</v>
       </c>
       <c r="E115" s="939">
         <v>0</v>
       </c>
       <c r="F115" s="940">
-        <v>9.9999999999999994e-149</v>
+        <v>30.894680000000001</v>
       </c>
       <c r="G115" s="941">
-        <v>4.6999999999999999e-105</v>
+        <v>470.86970000000002</v>
       </c>
     </row>
   </sheetData>

--- a/progression_odds_only_pdl1.xlsx
+++ b/progression_odds_only_pdl1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="322" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="357" uniqueCount="90">
   <si>
     <t>progression_outcome</t>
   </si>
@@ -39,16 +39,16 @@
     <t>io_mono</t>
   </si>
   <si>
-    <t>firstlinechemotherapy</t>
+    <t>firstlinechemothe~y</t>
   </si>
   <si>
-    <t>nonfirstlinechemotherapy</t>
+    <t>nonfirstlinechemo~y</t>
   </si>
   <si>
-    <t>otherfirstlinetherapy</t>
+    <t>otherfirstlinethe~y</t>
   </si>
   <si>
-    <t>firstlinecombinationtherapy</t>
+    <t>firstlinecombinat~y</t>
   </si>
   <si>
     <t>antibrafdrug</t>
@@ -63,10 +63,10 @@
     <t>metinhibitor</t>
   </si>
   <si>
-    <t>carboplatinmonotherapy</t>
+    <t>carboplatinmonoth~y</t>
   </si>
   <si>
-    <t>cisplatinmonotherapy</t>
+    <t>cisplatinmonother~y</t>
   </si>
   <si>
     <t>antialkdrug#alk</t>
@@ -108,10 +108,10 @@
     <t>ecog4</t>
   </si>
   <si>
-    <t>squamouscellcarcinoma</t>
+    <t>squamouscellcarci~a</t>
   </si>
   <si>
-    <t>nonsquamouscellcarcinoma</t>
+    <t>nonsquamouscellca~a</t>
   </si>
   <si>
     <t>pdl1</t>
@@ -144,13 +144,13 @@
     <t>male</t>
   </si>
   <si>
-    <t>daysfromadvanceddiagnosistotreat</t>
+    <t>daysfromadvancedd~t</t>
   </si>
   <si>
-    <t>patientassistanceprogram</t>
+    <t>patientassistance~m</t>
   </si>
   <si>
-    <t>othergovernmentalinsurance</t>
+    <t>othergovernmental~e</t>
   </si>
   <si>
     <t>medicare</t>
@@ -162,7 +162,7 @@
     <t>medicaid</t>
   </si>
   <si>
-    <t>commercialhealthplan</t>
+    <t>commercialhealthp~n</t>
   </si>
   <si>
     <t>noinsurance</t>
@@ -189,7 +189,7 @@
     <t>neversmoker</t>
   </si>
   <si>
-    <t>academicmedicalcenter</t>
+    <t>academicmedicalce~r</t>
   </si>
   <si>
     <t>kidney_bool</t>
@@ -198,10 +198,10 @@
     <t>liver_bool</t>
   </si>
   <si>
-    <t>connective_tissue_bool</t>
+    <t>connective_tissue~l</t>
   </si>
   <si>
-    <t>interstitiallungdisease</t>
+    <t>interstitiallungd~e</t>
   </si>
   <si>
     <t>diabetes</t>
@@ -216,40 +216,43 @@
     <t>othercnsmetastases</t>
   </si>
   <si>
-    <t>digestivesystemmetastases</t>
+    <t>digestivesystemme~s</t>
   </si>
   <si>
     <t>adrenalmetastases</t>
   </si>
   <si>
-    <t>unspecifiedmetastases</t>
+    <t>unspecifiedmetast~s</t>
   </si>
   <si>
-    <t>antiinfectiveusepriortotreatment</t>
+    <t>antiinfectiveusep~t</t>
   </si>
   <si>
-    <t>glucocorticoidusepriortotreatmen</t>
+    <t>glucocorticoiduse~n</t>
   </si>
   <si>
-    <t>clinicalstudydrugused</t>
+    <t>clinicalstudydrug~d</t>
   </si>
   <si>
     <t>bevacizumabused</t>
   </si>
   <si>
-    <t>threeormorechemotherapydrugs</t>
+    <t>threeormorechemot~s</t>
   </si>
   <si>
     <t>io_mono#c.pdl1</t>
   </si>
   <si>
-    <t>nonfirstlinechemotherapy#c.pdl1</t>
+    <t>nonfirstlinechemo~y#</t>
   </si>
   <si>
-    <t>firstlinecombinationtherapy#c.pdl1</t>
+    <t>c.pdl1</t>
   </si>
   <si>
-    <t>firstlinechemotherapy#c.pdl1</t>
+    <t>firstlinecombinat~y#</t>
+  </si>
+  <si>
+    <t>firstlinechemothe~y#</t>
   </si>
   <si>
     <t>antialkdrug#c.pdl1</t>
@@ -273,10 +276,10 @@
     <t>metinhibitor#c.pdl1</t>
   </si>
   <si>
-    <t>carboplatinmonotherapy#c.pdl1</t>
+    <t>carboplatinmonoth~y#</t>
   </si>
   <si>
-    <t>cisplatinmonotherapy#c.pdl1</t>
+    <t>cisplatinmonother~y#</t>
   </si>
   <si>
     <t>_cons</t>
@@ -286,7 +289,167 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="950">
+  <fonts count="990">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -4096,7 +4259,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="950">
+  <borders count="990">
     <border>
       <left/>
       <right/>
@@ -10700,6 +10863,286 @@
     </border>
     <border>
       <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="thin"/>
@@ -10751,7 +11194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="950">
+  <cellXfs count="990">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -14546,6 +14989,166 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="949" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="950" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="951" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="952" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="953" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="954" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="955" fillId="0" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="956" fillId="0" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="957" fillId="0" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="958" fillId="0" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="959" fillId="0" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="960" fillId="0" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="961" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="962" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="963" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="964" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="965" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="966" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="967" fillId="0" borderId="967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="968" fillId="0" borderId="968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="969" fillId="0" borderId="969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="970" fillId="0" borderId="970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="971" fillId="0" borderId="971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="972" fillId="0" borderId="972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="973" fillId="0" borderId="973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="974" fillId="0" borderId="974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="975" fillId="0" borderId="975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="976" fillId="0" borderId="976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="977" fillId="0" borderId="977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="978" fillId="0" borderId="978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="979" fillId="0" borderId="979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="980" fillId="0" borderId="980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="981" fillId="0" borderId="981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="982" fillId="0" borderId="982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="983" fillId="0" borderId="983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="984" fillId="0" borderId="984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="985" fillId="0" borderId="985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="986" fillId="0" borderId="986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="987" fillId="0" borderId="987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="988" fillId="0" borderId="988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="989" fillId="0" borderId="989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -14558,7 +15161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16471,54 +17074,54 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="680">
-        <v>1</v>
-      </c>
-      <c r="B84" s="681">
-        <v>6.0548960000000003</v>
-      </c>
-      <c r="C84" s="682">
-        <v>4.9696559999999996</v>
-      </c>
-      <c r="D84" s="683">
-        <v>2.19</v>
-      </c>
-      <c r="E84" s="684">
-        <v>0.028000000000000001</v>
-      </c>
-      <c r="F84" s="685">
-        <v>1.2119059999999999</v>
-      </c>
-      <c r="G84" s="686">
-        <v>30.251329999999999</v>
+      <c r="A84" s="680" t="s">
+        <v>77</v>
+      </c>
+      <c r="B84" s="681" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="682" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="683" t="s">
+        <v>6</v>
+      </c>
+      <c r="E84" s="684" t="s">
+        <v>6</v>
+      </c>
+      <c r="F84" s="685" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="686" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="688" t="s">
-        <v>6</v>
-      </c>
-      <c r="B85" s="689" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="690" t="s">
-        <v>6</v>
-      </c>
-      <c r="D85" s="691" t="s">
-        <v>6</v>
-      </c>
-      <c r="E85" s="692" t="s">
-        <v>6</v>
-      </c>
-      <c r="F85" s="693" t="s">
-        <v>6</v>
-      </c>
-      <c r="G85" s="694" t="s">
-        <v>6</v>
+      <c r="A85" s="688">
+        <v>1</v>
+      </c>
+      <c r="B85" s="689">
+        <v>6.0548960000000003</v>
+      </c>
+      <c r="C85" s="690">
+        <v>4.9696559999999996</v>
+      </c>
+      <c r="D85" s="691">
+        <v>2.19</v>
+      </c>
+      <c r="E85" s="692">
+        <v>0.028000000000000001</v>
+      </c>
+      <c r="F85" s="693">
+        <v>1.2119059999999999</v>
+      </c>
+      <c r="G85" s="694">
+        <v>30.251329999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="696" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="B86" s="697" t="s">
         <v>6</v>
@@ -16540,31 +17143,31 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="704">
-        <v>1</v>
-      </c>
-      <c r="B87" s="705">
-        <v>0.82965630000000001</v>
-      </c>
-      <c r="C87" s="706">
-        <v>0.20293990000000001</v>
-      </c>
-      <c r="D87" s="707">
-        <v>-0.76000000000000001</v>
-      </c>
-      <c r="E87" s="708">
-        <v>0.44500000000000001</v>
-      </c>
-      <c r="F87" s="709">
-        <v>0.51367479999999999</v>
-      </c>
-      <c r="G87" s="710">
-        <v>1.3400099999999999</v>
+      <c r="A87" s="704" t="s">
+        <v>78</v>
+      </c>
+      <c r="B87" s="705" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="706" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="707" t="s">
+        <v>6</v>
+      </c>
+      <c r="E87" s="708" t="s">
+        <v>6</v>
+      </c>
+      <c r="F87" s="709" t="s">
+        <v>6</v>
+      </c>
+      <c r="G87" s="710" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="712" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B88" s="713" t="s">
         <v>6</v>
@@ -16586,54 +17189,54 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="720" t="s">
-        <v>78</v>
-      </c>
-      <c r="B89" s="721" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="722" t="s">
-        <v>6</v>
-      </c>
-      <c r="D89" s="723" t="s">
-        <v>6</v>
-      </c>
-      <c r="E89" s="724" t="s">
-        <v>6</v>
-      </c>
-      <c r="F89" s="725" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" s="726" t="s">
-        <v>6</v>
+      <c r="A89" s="720">
+        <v>1</v>
+      </c>
+      <c r="B89" s="721">
+        <v>0.82965630000000001</v>
+      </c>
+      <c r="C89" s="722">
+        <v>0.20293990000000001</v>
+      </c>
+      <c r="D89" s="723">
+        <v>-0.76000000000000001</v>
+      </c>
+      <c r="E89" s="724">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="F89" s="725">
+        <v>0.51367479999999999</v>
+      </c>
+      <c r="G89" s="726">
+        <v>1.3400099999999999</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="728">
-        <v>1</v>
-      </c>
-      <c r="B90" s="729">
-        <v>1.516319</v>
-      </c>
-      <c r="C90" s="730">
-        <v>0.35964249999999998</v>
-      </c>
-      <c r="D90" s="731">
-        <v>1.76</v>
-      </c>
-      <c r="E90" s="732">
-        <v>0.079000000000000001</v>
-      </c>
-      <c r="F90" s="733">
-        <v>0.95257999999999998</v>
-      </c>
-      <c r="G90" s="734">
-        <v>2.4136799999999998</v>
+      <c r="A90" s="728" t="s">
+        <v>6</v>
+      </c>
+      <c r="B90" s="729" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="730" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="731" t="s">
+        <v>6</v>
+      </c>
+      <c r="E90" s="732" t="s">
+        <v>6</v>
+      </c>
+      <c r="F90" s="733" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="734" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="736" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="B91" s="737" t="s">
         <v>6</v>
@@ -16656,7 +17259,7 @@
     </row>
     <row r="92">
       <c r="A92" s="744" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B92" s="745" t="s">
         <v>6</v>
@@ -16682,22 +17285,22 @@
         <v>1</v>
       </c>
       <c r="B93" s="753">
-        <v>1.8507450000000001</v>
+        <v>1.516319</v>
       </c>
       <c r="C93" s="754">
-        <v>0.95050809999999997</v>
+        <v>0.35964249999999998</v>
       </c>
       <c r="D93" s="755">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="E93" s="756">
-        <v>0.23100000000000001</v>
+        <v>0.079000000000000001</v>
       </c>
       <c r="F93" s="757">
-        <v>0.67637170000000002</v>
+        <v>0.95257999999999998</v>
       </c>
       <c r="G93" s="758">
-        <v>5.064165</v>
+        <v>2.4136799999999998</v>
       </c>
     </row>
     <row r="94">
@@ -16751,22 +17354,22 @@
         <v>1</v>
       </c>
       <c r="B96" s="777">
-        <v>3.670512</v>
+        <v>1.8507450000000001</v>
       </c>
       <c r="C96" s="778">
-        <v>1.078945</v>
+        <v>0.95050809999999997</v>
       </c>
       <c r="D96" s="779">
-        <v>4.4199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="E96" s="780">
-        <v>0</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F96" s="781">
-        <v>2.0630820000000001</v>
+        <v>0.67637170000000002</v>
       </c>
       <c r="G96" s="782">
-        <v>6.5303570000000004</v>
+        <v>5.064165</v>
       </c>
     </row>
     <row r="97">
@@ -16820,22 +17423,22 @@
         <v>1</v>
       </c>
       <c r="B99" s="801">
-        <v>2.2813940000000001</v>
+        <v>3.670512</v>
       </c>
       <c r="C99" s="802">
-        <v>1.2395259999999999</v>
+        <v>1.078945</v>
       </c>
       <c r="D99" s="803">
-        <v>1.52</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="E99" s="804">
-        <v>0.129</v>
+        <v>0</v>
       </c>
       <c r="F99" s="805">
-        <v>0.78654939999999996</v>
+        <v>2.0630820000000001</v>
       </c>
       <c r="G99" s="806">
-        <v>6.6172079999999998</v>
+        <v>6.5303570000000004</v>
       </c>
     </row>
     <row r="100">
@@ -16889,22 +17492,22 @@
         <v>1</v>
       </c>
       <c r="B102" s="825">
-        <v>1.305895</v>
+        <v>2.2813940000000001</v>
       </c>
       <c r="C102" s="826">
-        <v>1.25553</v>
+        <v>1.2395259999999999</v>
       </c>
       <c r="D102" s="827">
-        <v>0.28000000000000003</v>
+        <v>1.52</v>
       </c>
       <c r="E102" s="828">
-        <v>0.78100000000000003</v>
+        <v>0.129</v>
       </c>
       <c r="F102" s="829">
-        <v>0.1983972</v>
+        <v>0.78654939999999996</v>
       </c>
       <c r="G102" s="830">
-        <v>8.5956960000000002</v>
+        <v>6.6172079999999998</v>
       </c>
     </row>
     <row r="103">
@@ -16958,22 +17561,22 @@
         <v>1</v>
       </c>
       <c r="B105" s="849">
-        <v>1</v>
-      </c>
-      <c r="C105" s="850" t="s">
-        <v>84</v>
-      </c>
-      <c r="D105" s="851" t="s">
-        <v>6</v>
-      </c>
-      <c r="E105" s="852" t="s">
-        <v>6</v>
-      </c>
-      <c r="F105" s="853" t="s">
-        <v>6</v>
-      </c>
-      <c r="G105" s="854" t="s">
-        <v>6</v>
+        <v>1.305895</v>
+      </c>
+      <c r="C105" s="850">
+        <v>1.25553</v>
+      </c>
+      <c r="D105" s="851">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E105" s="852">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="F105" s="853">
+        <v>0.1983972</v>
+      </c>
+      <c r="G105" s="854">
+        <v>8.5956960000000002</v>
       </c>
     </row>
     <row r="106">
@@ -17001,7 +17604,7 @@
     </row>
     <row r="107">
       <c r="A107" s="864" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B107" s="865" t="s">
         <v>6</v>
@@ -17027,22 +17630,22 @@
         <v>1</v>
       </c>
       <c r="B108" s="873">
-        <v>15.3744</v>
-      </c>
-      <c r="C108" s="874">
-        <v>26.068850000000001</v>
-      </c>
-      <c r="D108" s="875">
-        <v>1.6100000000000001</v>
-      </c>
-      <c r="E108" s="876">
-        <v>0.107</v>
-      </c>
-      <c r="F108" s="877">
-        <v>0.55398749999999997</v>
-      </c>
-      <c r="G108" s="878">
-        <v>426.67419999999999</v>
+        <v>1</v>
+      </c>
+      <c r="C108" s="874" t="s">
+        <v>85</v>
+      </c>
+      <c r="D108" s="875" t="s">
+        <v>6</v>
+      </c>
+      <c r="E108" s="876" t="s">
+        <v>6</v>
+      </c>
+      <c r="F108" s="877" t="s">
+        <v>6</v>
+      </c>
+      <c r="G108" s="878" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="109">
@@ -17096,22 +17699,22 @@
         <v>1</v>
       </c>
       <c r="B111" s="897">
-        <v>0.3662707</v>
+        <v>15.3744</v>
       </c>
       <c r="C111" s="898">
-        <v>0.40698889999999999</v>
+        <v>26.068850000000001</v>
       </c>
       <c r="D111" s="899">
-        <v>-0.90000000000000002</v>
+        <v>1.6100000000000001</v>
       </c>
       <c r="E111" s="900">
-        <v>0.36599999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="F111" s="901">
-        <v>0.041492800000000003</v>
+        <v>0.55398749999999997</v>
       </c>
       <c r="G111" s="902">
-        <v>3.2331919999999999</v>
+        <v>426.67419999999999</v>
       </c>
     </row>
     <row r="112">
@@ -17161,71 +17764,186 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="920">
-        <v>1</v>
-      </c>
-      <c r="B114" s="921">
-        <v>0.3361133</v>
-      </c>
-      <c r="C114" s="922">
-        <v>1.3072429999999999</v>
-      </c>
-      <c r="D114" s="923">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="E114" s="924">
-        <v>0.77900000000000003</v>
-      </c>
-      <c r="F114" s="925">
-        <v>0.00016440000000000001</v>
-      </c>
-      <c r="G114" s="926">
-        <v>687.15769999999998</v>
+      <c r="A114" s="920" t="s">
+        <v>77</v>
+      </c>
+      <c r="B114" s="921" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="922" t="s">
+        <v>6</v>
+      </c>
+      <c r="D114" s="923" t="s">
+        <v>6</v>
+      </c>
+      <c r="E114" s="924" t="s">
+        <v>6</v>
+      </c>
+      <c r="F114" s="925" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" s="926" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="928" t="s">
-        <v>6</v>
-      </c>
-      <c r="B115" s="929" t="s">
-        <v>6</v>
-      </c>
-      <c r="C115" s="930" t="s">
-        <v>6</v>
-      </c>
-      <c r="D115" s="931" t="s">
-        <v>6</v>
-      </c>
-      <c r="E115" s="932" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" s="933" t="s">
-        <v>6</v>
-      </c>
-      <c r="G115" s="934" t="s">
-        <v>6</v>
+      <c r="A115" s="928">
+        <v>1</v>
+      </c>
+      <c r="B115" s="929">
+        <v>0.3662707</v>
+      </c>
+      <c r="C115" s="930">
+        <v>0.40698889999999999</v>
+      </c>
+      <c r="D115" s="931">
+        <v>-0.90000000000000002</v>
+      </c>
+      <c r="E115" s="932">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="F115" s="933">
+        <v>0.041492800000000003</v>
+      </c>
+      <c r="G115" s="934">
+        <v>3.2331919999999999</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="943" t="s">
+      <c r="A116" s="936" t="s">
+        <v>6</v>
+      </c>
+      <c r="B116" s="937" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="938" t="s">
+        <v>6</v>
+      </c>
+      <c r="D116" s="939" t="s">
+        <v>6</v>
+      </c>
+      <c r="E116" s="940" t="s">
+        <v>6</v>
+      </c>
+      <c r="F116" s="941" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="942" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="944" t="s">
         <v>88</v>
       </c>
-      <c r="B116" s="944">
+      <c r="B117" s="945" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="946" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117" s="947" t="s">
+        <v>6</v>
+      </c>
+      <c r="E117" s="948" t="s">
+        <v>6</v>
+      </c>
+      <c r="F117" s="949" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" s="950" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="952" t="s">
+        <v>77</v>
+      </c>
+      <c r="B118" s="953" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="954" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" s="955" t="s">
+        <v>6</v>
+      </c>
+      <c r="E118" s="956" t="s">
+        <v>6</v>
+      </c>
+      <c r="F118" s="957" t="s">
+        <v>6</v>
+      </c>
+      <c r="G118" s="958" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="960">
+        <v>1</v>
+      </c>
+      <c r="B119" s="961">
+        <v>0.3361133</v>
+      </c>
+      <c r="C119" s="962">
+        <v>1.3072429999999999</v>
+      </c>
+      <c r="D119" s="963">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="E119" s="964">
+        <v>0.77900000000000003</v>
+      </c>
+      <c r="F119" s="965">
+        <v>0.00016440000000000001</v>
+      </c>
+      <c r="G119" s="966">
+        <v>687.15769999999998</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="968" t="s">
+        <v>6</v>
+      </c>
+      <c r="B120" s="969" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="970" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" s="971" t="s">
+        <v>6</v>
+      </c>
+      <c r="E120" s="972" t="s">
+        <v>6</v>
+      </c>
+      <c r="F120" s="973" t="s">
+        <v>6</v>
+      </c>
+      <c r="G120" s="974" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="983" t="s">
+        <v>89</v>
+      </c>
+      <c r="B121" s="984">
         <v>96.123270000000005</v>
       </c>
-      <c r="C116" s="945">
+      <c r="C121" s="985">
         <v>67.488169999999997</v>
       </c>
-      <c r="D116" s="946">
+      <c r="D121" s="986">
         <v>6.5</v>
       </c>
-      <c r="E116" s="947">
+      <c r="E121" s="987">
         <v>0</v>
       </c>
-      <c r="F116" s="948">
+      <c r="F121" s="988">
         <v>24.277259999999998</v>
       </c>
-      <c r="G116" s="949">
+      <c r="G121" s="989">
         <v>380.58999999999998</v>
       </c>
     </row>

--- a/progression_odds_only_pdl1.xlsx
+++ b/progression_odds_only_pdl1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="357" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="322" uniqueCount="89">
   <si>
     <t>progression_outcome</t>
   </si>
@@ -39,16 +39,16 @@
     <t>io_mono</t>
   </si>
   <si>
-    <t>firstlinechemothe~y</t>
+    <t>firstlinechemotherapy</t>
   </si>
   <si>
-    <t>nonfirstlinechemo~y</t>
+    <t>nonfirstlinechemotherapy</t>
   </si>
   <si>
-    <t>otherfirstlinethe~y</t>
+    <t>otherfirstlinetherapy</t>
   </si>
   <si>
-    <t>firstlinecombinat~y</t>
+    <t>firstlinecombinationtherapy</t>
   </si>
   <si>
     <t>antibrafdrug</t>
@@ -63,10 +63,10 @@
     <t>metinhibitor</t>
   </si>
   <si>
-    <t>carboplatinmonoth~y</t>
+    <t>carboplatinmonotherapy</t>
   </si>
   <si>
-    <t>cisplatinmonother~y</t>
+    <t>cisplatinmonotherapy</t>
   </si>
   <si>
     <t>antialkdrug#alk</t>
@@ -108,10 +108,10 @@
     <t>ecog4</t>
   </si>
   <si>
-    <t>squamouscellcarci~a</t>
+    <t>squamouscellcarcinoma</t>
   </si>
   <si>
-    <t>nonsquamouscellca~a</t>
+    <t>nonsquamouscellcarcinoma</t>
   </si>
   <si>
     <t>pdl1</t>
@@ -144,13 +144,13 @@
     <t>male</t>
   </si>
   <si>
-    <t>daysfromadvancedd~t</t>
+    <t>daysfromadvanceddiagnosistotreat</t>
   </si>
   <si>
-    <t>patientassistance~m</t>
+    <t>patientassistanceprogram</t>
   </si>
   <si>
-    <t>othergovernmental~e</t>
+    <t>othergovernmentalinsurance</t>
   </si>
   <si>
     <t>medicare</t>
@@ -162,7 +162,7 @@
     <t>medicaid</t>
   </si>
   <si>
-    <t>commercialhealthp~n</t>
+    <t>commercialhealthplan</t>
   </si>
   <si>
     <t>noinsurance</t>
@@ -189,7 +189,7 @@
     <t>neversmoker</t>
   </si>
   <si>
-    <t>academicmedicalce~r</t>
+    <t>academicmedicalcenter</t>
   </si>
   <si>
     <t>kidney_bool</t>
@@ -198,10 +198,10 @@
     <t>liver_bool</t>
   </si>
   <si>
-    <t>connective_tissue~l</t>
+    <t>connective_tissue_bool</t>
   </si>
   <si>
-    <t>interstitiallungd~e</t>
+    <t>interstitiallungdisease</t>
   </si>
   <si>
     <t>diabetes</t>
@@ -216,43 +216,40 @@
     <t>othercnsmetastases</t>
   </si>
   <si>
-    <t>digestivesystemme~s</t>
+    <t>digestivesystemmetastases</t>
   </si>
   <si>
     <t>adrenalmetastases</t>
   </si>
   <si>
-    <t>unspecifiedmetast~s</t>
+    <t>unspecifiedmetastases</t>
   </si>
   <si>
-    <t>antiinfectiveusep~t</t>
+    <t>antiinfectiveusepriortotreatment</t>
   </si>
   <si>
-    <t>glucocorticoiduse~n</t>
+    <t>glucocorticoidusepriortotreatmen</t>
   </si>
   <si>
-    <t>clinicalstudydrug~d</t>
+    <t>clinicalstudydrugused</t>
   </si>
   <si>
     <t>bevacizumabused</t>
   </si>
   <si>
-    <t>threeormorechemot~s</t>
+    <t>threeormorechemotherapydrugs</t>
   </si>
   <si>
     <t>io_mono#c.pdl1</t>
   </si>
   <si>
-    <t>nonfirstlinechemo~y#</t>
+    <t>nonfirstlinechemotherapy#c.pdl1</t>
   </si>
   <si>
-    <t>c.pdl1</t>
+    <t>firstlinecombinationtherapy#c.pdl1</t>
   </si>
   <si>
-    <t>firstlinecombinat~y#</t>
-  </si>
-  <si>
-    <t>firstlinechemothe~y#</t>
+    <t>firstlinechemotherapy#c.pdl1</t>
   </si>
   <si>
     <t>antialkdrug#c.pdl1</t>
@@ -276,10 +273,10 @@
     <t>metinhibitor#c.pdl1</t>
   </si>
   <si>
-    <t>carboplatinmonoth~y#</t>
+    <t>carboplatinmonotherapy#c.pdl1</t>
   </si>
   <si>
-    <t>cisplatinmonother~y#</t>
+    <t>cisplatinmonotherapy#c.pdl1</t>
   </si>
   <si>
     <t>_cons</t>
@@ -289,167 +286,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="990">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
+  <fonts count="950">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -4259,7 +4096,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="990">
+  <borders count="950">
     <border>
       <left/>
       <right/>
@@ -10863,286 +10700,6 @@
     </border>
     <border>
       <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
       <right style="thin"/>
       <top style="none"/>
       <bottom style="thin"/>
@@ -11194,7 +10751,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="990">
+  <cellXfs count="950">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -14989,166 +14546,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="949" fillId="0" borderId="949" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="950" fillId="0" borderId="950" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="951" fillId="0" borderId="951" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="952" fillId="0" borderId="952" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="953" fillId="0" borderId="953" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="954" fillId="0" borderId="954" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="955" fillId="0" borderId="955" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="956" fillId="0" borderId="956" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="957" fillId="0" borderId="957" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="958" fillId="0" borderId="958" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="959" fillId="0" borderId="959" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="960" fillId="0" borderId="960" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="961" fillId="0" borderId="961" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="962" fillId="0" borderId="962" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="963" fillId="0" borderId="963" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="964" fillId="0" borderId="964" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="965" fillId="0" borderId="965" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="966" fillId="0" borderId="966" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="967" fillId="0" borderId="967" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="968" fillId="0" borderId="968" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="969" fillId="0" borderId="969" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="970" fillId="0" borderId="970" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="971" fillId="0" borderId="971" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="972" fillId="0" borderId="972" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="973" fillId="0" borderId="973" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="974" fillId="0" borderId="974" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="975" fillId="0" borderId="975" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="976" fillId="0" borderId="976" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="977" fillId="0" borderId="977" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="978" fillId="0" borderId="978" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="979" fillId="0" borderId="979" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="980" fillId="0" borderId="980" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="981" fillId="0" borderId="981" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="982" fillId="0" borderId="982" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="983" fillId="0" borderId="983" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="984" fillId="0" borderId="984" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="985" fillId="0" borderId="985" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="986" fillId="0" borderId="986" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="987" fillId="0" borderId="987" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="988" fillId="0" borderId="988" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="989" fillId="0" borderId="989" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -15161,7 +14558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17074,54 +16471,54 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="680" t="s">
-        <v>77</v>
-      </c>
-      <c r="B84" s="681" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="682" t="s">
-        <v>6</v>
-      </c>
-      <c r="D84" s="683" t="s">
-        <v>6</v>
-      </c>
-      <c r="E84" s="684" t="s">
-        <v>6</v>
-      </c>
-      <c r="F84" s="685" t="s">
-        <v>6</v>
-      </c>
-      <c r="G84" s="686" t="s">
-        <v>6</v>
+      <c r="A84" s="680">
+        <v>1</v>
+      </c>
+      <c r="B84" s="681">
+        <v>6.0548960000000003</v>
+      </c>
+      <c r="C84" s="682">
+        <v>4.9696559999999996</v>
+      </c>
+      <c r="D84" s="683">
+        <v>2.19</v>
+      </c>
+      <c r="E84" s="684">
+        <v>0.028000000000000001</v>
+      </c>
+      <c r="F84" s="685">
+        <v>1.2119059999999999</v>
+      </c>
+      <c r="G84" s="686">
+        <v>30.251329999999999</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="688">
-        <v>1</v>
-      </c>
-      <c r="B85" s="689">
-        <v>6.0548960000000003</v>
-      </c>
-      <c r="C85" s="690">
-        <v>4.9696559999999996</v>
-      </c>
-      <c r="D85" s="691">
-        <v>2.19</v>
-      </c>
-      <c r="E85" s="692">
-        <v>0.028000000000000001</v>
-      </c>
-      <c r="F85" s="693">
-        <v>1.2119059999999999</v>
-      </c>
-      <c r="G85" s="694">
-        <v>30.251329999999999</v>
+      <c r="A85" s="688" t="s">
+        <v>6</v>
+      </c>
+      <c r="B85" s="689" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="690" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="691" t="s">
+        <v>6</v>
+      </c>
+      <c r="E85" s="692" t="s">
+        <v>6</v>
+      </c>
+      <c r="F85" s="693" t="s">
+        <v>6</v>
+      </c>
+      <c r="G85" s="694" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="696" t="s">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="B86" s="697" t="s">
         <v>6</v>
@@ -17143,31 +16540,31 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="704" t="s">
-        <v>78</v>
-      </c>
-      <c r="B87" s="705" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="706" t="s">
-        <v>6</v>
-      </c>
-      <c r="D87" s="707" t="s">
-        <v>6</v>
-      </c>
-      <c r="E87" s="708" t="s">
-        <v>6</v>
-      </c>
-      <c r="F87" s="709" t="s">
-        <v>6</v>
-      </c>
-      <c r="G87" s="710" t="s">
-        <v>6</v>
+      <c r="A87" s="704">
+        <v>1</v>
+      </c>
+      <c r="B87" s="705">
+        <v>0.82965630000000001</v>
+      </c>
+      <c r="C87" s="706">
+        <v>0.20293990000000001</v>
+      </c>
+      <c r="D87" s="707">
+        <v>-0.76000000000000001</v>
+      </c>
+      <c r="E87" s="708">
+        <v>0.44500000000000001</v>
+      </c>
+      <c r="F87" s="709">
+        <v>0.51367479999999999</v>
+      </c>
+      <c r="G87" s="710">
+        <v>1.3400099999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="712" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="B88" s="713" t="s">
         <v>6</v>
@@ -17189,54 +16586,54 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="720">
-        <v>1</v>
-      </c>
-      <c r="B89" s="721">
-        <v>0.82965630000000001</v>
-      </c>
-      <c r="C89" s="722">
-        <v>0.20293990000000001</v>
-      </c>
-      <c r="D89" s="723">
-        <v>-0.76000000000000001</v>
-      </c>
-      <c r="E89" s="724">
-        <v>0.44500000000000001</v>
-      </c>
-      <c r="F89" s="725">
-        <v>0.51367479999999999</v>
-      </c>
-      <c r="G89" s="726">
-        <v>1.3400099999999999</v>
+      <c r="A89" s="720" t="s">
+        <v>78</v>
+      </c>
+      <c r="B89" s="721" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="722" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="723" t="s">
+        <v>6</v>
+      </c>
+      <c r="E89" s="724" t="s">
+        <v>6</v>
+      </c>
+      <c r="F89" s="725" t="s">
+        <v>6</v>
+      </c>
+      <c r="G89" s="726" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="728" t="s">
-        <v>6</v>
-      </c>
-      <c r="B90" s="729" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="730" t="s">
-        <v>6</v>
-      </c>
-      <c r="D90" s="731" t="s">
-        <v>6</v>
-      </c>
-      <c r="E90" s="732" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" s="733" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="734" t="s">
-        <v>6</v>
+      <c r="A90" s="728">
+        <v>1</v>
+      </c>
+      <c r="B90" s="729">
+        <v>1.516319</v>
+      </c>
+      <c r="C90" s="730">
+        <v>0.35964249999999998</v>
+      </c>
+      <c r="D90" s="731">
+        <v>1.76</v>
+      </c>
+      <c r="E90" s="732">
+        <v>0.079000000000000001</v>
+      </c>
+      <c r="F90" s="733">
+        <v>0.95257999999999998</v>
+      </c>
+      <c r="G90" s="734">
+        <v>2.4136799999999998</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="736" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="B91" s="737" t="s">
         <v>6</v>
@@ -17259,7 +16656,7 @@
     </row>
     <row r="92">
       <c r="A92" s="744" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B92" s="745" t="s">
         <v>6</v>
@@ -17285,22 +16682,22 @@
         <v>1</v>
       </c>
       <c r="B93" s="753">
-        <v>1.516319</v>
+        <v>1.8507450000000001</v>
       </c>
       <c r="C93" s="754">
-        <v>0.35964249999999998</v>
+        <v>0.95050809999999997</v>
       </c>
       <c r="D93" s="755">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="E93" s="756">
-        <v>0.079000000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F93" s="757">
-        <v>0.95257999999999998</v>
+        <v>0.67637170000000002</v>
       </c>
       <c r="G93" s="758">
-        <v>2.4136799999999998</v>
+        <v>5.064165</v>
       </c>
     </row>
     <row r="94">
@@ -17354,22 +16751,22 @@
         <v>1</v>
       </c>
       <c r="B96" s="777">
-        <v>1.8507450000000001</v>
+        <v>3.670512</v>
       </c>
       <c r="C96" s="778">
-        <v>0.95050809999999997</v>
+        <v>1.078945</v>
       </c>
       <c r="D96" s="779">
-        <v>1.2</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="E96" s="780">
-        <v>0.23100000000000001</v>
+        <v>0</v>
       </c>
       <c r="F96" s="781">
-        <v>0.67637170000000002</v>
+        <v>2.0630820000000001</v>
       </c>
       <c r="G96" s="782">
-        <v>5.064165</v>
+        <v>6.5303570000000004</v>
       </c>
     </row>
     <row r="97">
@@ -17423,22 +16820,22 @@
         <v>1</v>
       </c>
       <c r="B99" s="801">
-        <v>3.670512</v>
+        <v>2.2813940000000001</v>
       </c>
       <c r="C99" s="802">
-        <v>1.078945</v>
+        <v>1.2395259999999999</v>
       </c>
       <c r="D99" s="803">
-        <v>4.4199999999999999</v>
+        <v>1.52</v>
       </c>
       <c r="E99" s="804">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="F99" s="805">
-        <v>2.0630820000000001</v>
+        <v>0.78654939999999996</v>
       </c>
       <c r="G99" s="806">
-        <v>6.5303570000000004</v>
+        <v>6.6172079999999998</v>
       </c>
     </row>
     <row r="100">
@@ -17492,22 +16889,22 @@
         <v>1</v>
       </c>
       <c r="B102" s="825">
-        <v>2.2813940000000001</v>
+        <v>1.305895</v>
       </c>
       <c r="C102" s="826">
-        <v>1.2395259999999999</v>
+        <v>1.25553</v>
       </c>
       <c r="D102" s="827">
-        <v>1.52</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E102" s="828">
-        <v>0.129</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="F102" s="829">
-        <v>0.78654939999999996</v>
+        <v>0.1983972</v>
       </c>
       <c r="G102" s="830">
-        <v>6.6172079999999998</v>
+        <v>8.5956960000000002</v>
       </c>
     </row>
     <row r="103">
@@ -17561,22 +16958,22 @@
         <v>1</v>
       </c>
       <c r="B105" s="849">
-        <v>1.305895</v>
-      </c>
-      <c r="C105" s="850">
-        <v>1.25553</v>
-      </c>
-      <c r="D105" s="851">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="E105" s="852">
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="F105" s="853">
-        <v>0.1983972</v>
-      </c>
-      <c r="G105" s="854">
-        <v>8.5956960000000002</v>
+        <v>1</v>
+      </c>
+      <c r="C105" s="850" t="s">
+        <v>84</v>
+      </c>
+      <c r="D105" s="851" t="s">
+        <v>6</v>
+      </c>
+      <c r="E105" s="852" t="s">
+        <v>6</v>
+      </c>
+      <c r="F105" s="853" t="s">
+        <v>6</v>
+      </c>
+      <c r="G105" s="854" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="106">
@@ -17604,7 +17001,7 @@
     </row>
     <row r="107">
       <c r="A107" s="864" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B107" s="865" t="s">
         <v>6</v>
@@ -17630,22 +17027,22 @@
         <v>1</v>
       </c>
       <c r="B108" s="873">
-        <v>1</v>
-      </c>
-      <c r="C108" s="874" t="s">
-        <v>85</v>
-      </c>
-      <c r="D108" s="875" t="s">
-        <v>6</v>
-      </c>
-      <c r="E108" s="876" t="s">
-        <v>6</v>
-      </c>
-      <c r="F108" s="877" t="s">
-        <v>6</v>
-      </c>
-      <c r="G108" s="878" t="s">
-        <v>6</v>
+        <v>15.3744</v>
+      </c>
+      <c r="C108" s="874">
+        <v>26.068850000000001</v>
+      </c>
+      <c r="D108" s="875">
+        <v>1.6100000000000001</v>
+      </c>
+      <c r="E108" s="876">
+        <v>0.107</v>
+      </c>
+      <c r="F108" s="877">
+        <v>0.55398749999999997</v>
+      </c>
+      <c r="G108" s="878">
+        <v>426.67419999999999</v>
       </c>
     </row>
     <row r="109">
@@ -17699,22 +17096,22 @@
         <v>1</v>
       </c>
       <c r="B111" s="897">
-        <v>15.3744</v>
+        <v>0.3662707</v>
       </c>
       <c r="C111" s="898">
-        <v>26.068850000000001</v>
+        <v>0.40698889999999999</v>
       </c>
       <c r="D111" s="899">
-        <v>1.6100000000000001</v>
+        <v>-0.90000000000000002</v>
       </c>
       <c r="E111" s="900">
-        <v>0.107</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="F111" s="901">
-        <v>0.55398749999999997</v>
+        <v>0.041492800000000003</v>
       </c>
       <c r="G111" s="902">
-        <v>426.67419999999999</v>
+        <v>3.2331919999999999</v>
       </c>
     </row>
     <row r="112">
@@ -17764,186 +17161,71 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="920" t="s">
-        <v>77</v>
-      </c>
-      <c r="B114" s="921" t="s">
-        <v>6</v>
-      </c>
-      <c r="C114" s="922" t="s">
-        <v>6</v>
-      </c>
-      <c r="D114" s="923" t="s">
-        <v>6</v>
-      </c>
-      <c r="E114" s="924" t="s">
-        <v>6</v>
-      </c>
-      <c r="F114" s="925" t="s">
-        <v>6</v>
-      </c>
-      <c r="G114" s="926" t="s">
-        <v>6</v>
+      <c r="A114" s="920">
+        <v>1</v>
+      </c>
+      <c r="B114" s="921">
+        <v>0.3361133</v>
+      </c>
+      <c r="C114" s="922">
+        <v>1.3072429999999999</v>
+      </c>
+      <c r="D114" s="923">
+        <v>-0.28000000000000003</v>
+      </c>
+      <c r="E114" s="924">
+        <v>0.77900000000000003</v>
+      </c>
+      <c r="F114" s="925">
+        <v>0.00016440000000000001</v>
+      </c>
+      <c r="G114" s="926">
+        <v>687.15769999999998</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="928">
-        <v>1</v>
-      </c>
-      <c r="B115" s="929">
-        <v>0.3662707</v>
-      </c>
-      <c r="C115" s="930">
-        <v>0.40698889999999999</v>
-      </c>
-      <c r="D115" s="931">
-        <v>-0.90000000000000002</v>
-      </c>
-      <c r="E115" s="932">
-        <v>0.36599999999999999</v>
-      </c>
-      <c r="F115" s="933">
-        <v>0.041492800000000003</v>
-      </c>
-      <c r="G115" s="934">
-        <v>3.2331919999999999</v>
+      <c r="A115" s="928" t="s">
+        <v>6</v>
+      </c>
+      <c r="B115" s="929" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="930" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" s="931" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115" s="932" t="s">
+        <v>6</v>
+      </c>
+      <c r="F115" s="933" t="s">
+        <v>6</v>
+      </c>
+      <c r="G115" s="934" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="936" t="s">
-        <v>6</v>
-      </c>
-      <c r="B116" s="937" t="s">
-        <v>6</v>
-      </c>
-      <c r="C116" s="938" t="s">
-        <v>6</v>
-      </c>
-      <c r="D116" s="939" t="s">
-        <v>6</v>
-      </c>
-      <c r="E116" s="940" t="s">
-        <v>6</v>
-      </c>
-      <c r="F116" s="941" t="s">
-        <v>6</v>
-      </c>
-      <c r="G116" s="942" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="944" t="s">
+      <c r="A116" s="943" t="s">
         <v>88</v>
       </c>
-      <c r="B117" s="945" t="s">
-        <v>6</v>
-      </c>
-      <c r="C117" s="946" t="s">
-        <v>6</v>
-      </c>
-      <c r="D117" s="947" t="s">
-        <v>6</v>
-      </c>
-      <c r="E117" s="948" t="s">
-        <v>6</v>
-      </c>
-      <c r="F117" s="949" t="s">
-        <v>6</v>
-      </c>
-      <c r="G117" s="950" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="952" t="s">
-        <v>77</v>
-      </c>
-      <c r="B118" s="953" t="s">
-        <v>6</v>
-      </c>
-      <c r="C118" s="954" t="s">
-        <v>6</v>
-      </c>
-      <c r="D118" s="955" t="s">
-        <v>6</v>
-      </c>
-      <c r="E118" s="956" t="s">
-        <v>6</v>
-      </c>
-      <c r="F118" s="957" t="s">
-        <v>6</v>
-      </c>
-      <c r="G118" s="958" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="960">
-        <v>1</v>
-      </c>
-      <c r="B119" s="961">
-        <v>0.3361133</v>
-      </c>
-      <c r="C119" s="962">
-        <v>1.3072429999999999</v>
-      </c>
-      <c r="D119" s="963">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="E119" s="964">
-        <v>0.77900000000000003</v>
-      </c>
-      <c r="F119" s="965">
-        <v>0.00016440000000000001</v>
-      </c>
-      <c r="G119" s="966">
-        <v>687.15769999999998</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="968" t="s">
-        <v>6</v>
-      </c>
-      <c r="B120" s="969" t="s">
-        <v>6</v>
-      </c>
-      <c r="C120" s="970" t="s">
-        <v>6</v>
-      </c>
-      <c r="D120" s="971" t="s">
-        <v>6</v>
-      </c>
-      <c r="E120" s="972" t="s">
-        <v>6</v>
-      </c>
-      <c r="F120" s="973" t="s">
-        <v>6</v>
-      </c>
-      <c r="G120" s="974" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="983" t="s">
-        <v>89</v>
-      </c>
-      <c r="B121" s="984">
+      <c r="B116" s="944">
         <v>96.123270000000005</v>
       </c>
-      <c r="C121" s="985">
+      <c r="C116" s="945">
         <v>67.488169999999997</v>
       </c>
-      <c r="D121" s="986">
+      <c r="D116" s="946">
         <v>6.5</v>
       </c>
-      <c r="E121" s="987">
+      <c r="E116" s="947">
         <v>0</v>
       </c>
-      <c r="F121" s="988">
+      <c r="F116" s="948">
         <v>24.277259999999998</v>
       </c>
-      <c r="G121" s="989">
+      <c r="G116" s="949">
         <v>380.58999999999998</v>
       </c>
     </row>

--- a/progression_odds_only_pdl1.xlsx
+++ b/progression_odds_only_pdl1.xlsx
@@ -14589,22 +14589,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="25">
-        <v>1.95103</v>
+        <v>1.382166</v>
       </c>
       <c r="C2" s="26">
-        <v>0.53916050000000004</v>
+        <v>1.263261</v>
       </c>
       <c r="D2" s="27">
-        <v>2.4199999999999999</v>
+        <v>0.34999999999999998</v>
       </c>
       <c r="E2" s="28">
-        <v>0.016</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="F2" s="29">
-        <v>1.135108</v>
+        <v>0.23045499999999999</v>
       </c>
       <c r="G2" s="30">
-        <v>3.35344</v>
+        <v>8.2896180000000008</v>
       </c>
     </row>
     <row r="3">
@@ -14612,22 +14612,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="33">
-        <v>1.4164969999999999</v>
+        <v>0.80735849999999998</v>
       </c>
       <c r="C3" s="34">
-        <v>0.37657069999999998</v>
+        <v>0.078483899999999995</v>
       </c>
       <c r="D3" s="35">
-        <v>1.3100000000000001</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="E3" s="36">
-        <v>0.19</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="F3" s="37">
-        <v>0.84125360000000005</v>
+        <v>0.66729910000000003</v>
       </c>
       <c r="G3" s="38">
-        <v>2.3850889999999998</v>
+        <v>0.97681499999999999</v>
       </c>
     </row>
     <row r="4">
@@ -14635,22 +14635,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="41">
-        <v>2.0536750000000001</v>
+        <v>1.1661189999999999</v>
       </c>
       <c r="C4" s="42">
-        <v>0.6765622</v>
+        <v>0.25204680000000002</v>
       </c>
       <c r="D4" s="43">
-        <v>2.1800000000000002</v>
+        <v>0.70999999999999997</v>
       </c>
       <c r="E4" s="44">
-        <v>0.029000000000000001</v>
+        <v>0.47699999999999998</v>
       </c>
       <c r="F4" s="45">
-        <v>1.0767439999999999</v>
+        <v>0.76341870000000001</v>
       </c>
       <c r="G4" s="46">
-        <v>3.9169800000000001</v>
+        <v>1.781242</v>
       </c>
     </row>
     <row r="5">
@@ -14658,22 +14658,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="49">
-        <v>1.2889120000000001</v>
+        <v>0.81775690000000001</v>
       </c>
       <c r="C5" s="50">
-        <v>0.32879140000000001</v>
+        <v>0.093204899999999993</v>
       </c>
       <c r="D5" s="51">
-        <v>0.98999999999999999</v>
+        <v>-1.77</v>
       </c>
       <c r="E5" s="52">
-        <v>0.32000000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="F5" s="53">
-        <v>0.78178650000000005</v>
+        <v>0.65404459999999998</v>
       </c>
       <c r="G5" s="54">
-        <v>2.1249959999999999</v>
+        <v>1.0224470000000001</v>
       </c>
     </row>
     <row r="6">
@@ -14681,22 +14681,22 @@
         <v>11</v>
       </c>
       <c r="B6" s="57">
-        <v>1.3094539999999999</v>
+        <v>0.54097660000000003</v>
       </c>
       <c r="C6" s="58">
-        <v>0.35046290000000002</v>
+        <v>0.49216959999999999</v>
       </c>
       <c r="D6" s="59">
-        <v>1.01</v>
+        <v>-0.68000000000000005</v>
       </c>
       <c r="E6" s="60">
-        <v>0.314</v>
+        <v>0.499</v>
       </c>
       <c r="F6" s="61">
-        <v>0.77495099999999995</v>
+        <v>0.090943700000000002</v>
       </c>
       <c r="G6" s="62">
-        <v>2.2126169999999998</v>
+        <v>3.2179880000000001</v>
       </c>
     </row>
     <row r="7">
@@ -14704,22 +14704,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="65">
-        <v>1.6326989999999999</v>
+        <v>0.9453722</v>
       </c>
       <c r="C7" s="66">
-        <v>0.87593840000000001</v>
+        <v>0.45216279999999998</v>
       </c>
       <c r="D7" s="67">
-        <v>0.91000000000000003</v>
+        <v>-0.12</v>
       </c>
       <c r="E7" s="68">
-        <v>0.36099999999999999</v>
+        <v>0.90700000000000003</v>
       </c>
       <c r="F7" s="69">
-        <v>0.57047769999999998</v>
+        <v>0.37023800000000001</v>
       </c>
       <c r="G7" s="70">
-        <v>4.672758</v>
+        <v>2.4139300000000001</v>
       </c>
     </row>
     <row r="8">
@@ -14750,22 +14750,22 @@
         <v>15</v>
       </c>
       <c r="B9" s="81">
-        <v>0.4009491</v>
+        <v>0.2238726</v>
       </c>
       <c r="C9" s="82">
-        <v>0.4216895</v>
+        <v>0.22839609999999999</v>
       </c>
       <c r="D9" s="83">
-        <v>-0.87</v>
+        <v>-1.47</v>
       </c>
       <c r="E9" s="84">
-        <v>0.38500000000000001</v>
+        <v>0.14199999999999999</v>
       </c>
       <c r="F9" s="85">
-        <v>0.051033599999999999</v>
+        <v>0.030311000000000001</v>
       </c>
       <c r="G9" s="86">
-        <v>3.150083</v>
+        <v>1.6534899999999999</v>
       </c>
     </row>
     <row r="10">
@@ -14773,22 +14773,22 @@
         <v>16</v>
       </c>
       <c r="B10" s="89">
-        <v>1.739045</v>
+        <v>0.98913600000000002</v>
       </c>
       <c r="C10" s="90">
-        <v>1.013164</v>
+        <v>0.52160209999999996</v>
       </c>
       <c r="D10" s="91">
-        <v>0.94999999999999996</v>
+        <v>-0.02</v>
       </c>
       <c r="E10" s="92">
-        <v>0.34200000000000003</v>
+        <v>0.98299999999999999</v>
       </c>
       <c r="F10" s="93">
-        <v>0.55513999999999997</v>
+        <v>0.3518771</v>
       </c>
       <c r="G10" s="94">
-        <v>5.4477729999999998</v>
+        <v>2.7804880000000001</v>
       </c>
     </row>
     <row r="11">
@@ -14796,22 +14796,22 @@
         <v>17</v>
       </c>
       <c r="B11" s="97">
-        <v>0.63797990000000004</v>
+        <v>0.36105399999999999</v>
       </c>
       <c r="C11" s="98">
-        <v>0.67715590000000003</v>
+        <v>0.37251489999999998</v>
       </c>
       <c r="D11" s="99">
-        <v>-0.41999999999999999</v>
+        <v>-0.98999999999999999</v>
       </c>
       <c r="E11" s="100">
-        <v>0.67200000000000004</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="F11" s="101">
-        <v>0.079677600000000001</v>
+        <v>0.047791500000000001</v>
       </c>
       <c r="G11" s="102">
-        <v>5.1083160000000003</v>
+        <v>2.7276790000000002</v>
       </c>
     </row>
     <row r="12">
@@ -14865,22 +14865,22 @@
         <v>19</v>
       </c>
       <c r="B14" s="121">
-        <v>0.54199909999999996</v>
+        <v>0.54264800000000002</v>
       </c>
       <c r="C14" s="122">
-        <v>0.1003496</v>
+        <v>0.1005233</v>
       </c>
       <c r="D14" s="123">
-        <v>-3.3100000000000001</v>
+        <v>-3.2999999999999998</v>
       </c>
       <c r="E14" s="124">
         <v>0.001</v>
       </c>
       <c r="F14" s="125">
-        <v>0.37705169999999999</v>
+        <v>0.37743009999999999</v>
       </c>
       <c r="G14" s="126">
-        <v>0.7791053</v>
+        <v>0.78018900000000002</v>
       </c>
     </row>
     <row r="15">
@@ -14888,22 +14888,22 @@
         <v>20</v>
       </c>
       <c r="B15" s="129">
-        <v>2.7959610000000001</v>
+        <v>1.5850839999999999</v>
       </c>
       <c r="C15" s="130">
-        <v>3.3364910000000001</v>
+        <v>1.8509329999999999</v>
       </c>
       <c r="D15" s="131">
-        <v>0.85999999999999999</v>
+        <v>0.39000000000000001</v>
       </c>
       <c r="E15" s="132">
-        <v>0.38900000000000001</v>
+        <v>0.69299999999999995</v>
       </c>
       <c r="F15" s="133">
-        <v>0.26963179999999998</v>
+        <v>0.1607267</v>
       </c>
       <c r="G15" s="134">
-        <v>28.99287</v>
+        <v>15.63208</v>
       </c>
     </row>
     <row r="16">
@@ -14911,22 +14911,22 @@
         <v>21</v>
       </c>
       <c r="B16" s="137">
-        <v>0.39306029999999997</v>
+        <v>0.23096449999999999</v>
       </c>
       <c r="C16" s="138">
-        <v>0.13349440000000001</v>
+        <v>0.056233400000000003</v>
       </c>
       <c r="D16" s="139">
-        <v>-2.75</v>
+        <v>-6.0199999999999996</v>
       </c>
       <c r="E16" s="140">
-        <v>0.0060000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F16" s="141">
-        <v>0.2020073</v>
+        <v>0.14331830000000001</v>
       </c>
       <c r="G16" s="142">
-        <v>0.76480610000000004</v>
+        <v>0.37221080000000001</v>
       </c>
     </row>
     <row r="17">
@@ -14980,22 +14980,22 @@
         <v>19</v>
       </c>
       <c r="B19" s="161">
-        <v>0.92039289999999996</v>
+        <v>0.91699489999999995</v>
       </c>
       <c r="C19" s="162">
-        <v>0.0875388</v>
+        <v>0.087200299999999995</v>
       </c>
       <c r="D19" s="163">
-        <v>-0.87</v>
+        <v>-0.91000000000000003</v>
       </c>
       <c r="E19" s="164">
-        <v>0.38300000000000001</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="F19" s="165">
-        <v>0.76386259999999995</v>
+        <v>0.76106739999999995</v>
       </c>
       <c r="G19" s="166">
-        <v>1.1089990000000001</v>
+        <v>1.1048690000000001</v>
       </c>
     </row>
     <row r="20">
@@ -15003,22 +15003,22 @@
         <v>20</v>
       </c>
       <c r="B20" s="169">
-        <v>2.3840219999999999</v>
+        <v>1.3639600000000001</v>
       </c>
       <c r="C20" s="170">
-        <v>0.97508399999999995</v>
+        <v>0.4448011</v>
       </c>
       <c r="D20" s="171">
-        <v>2.1200000000000001</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="E20" s="172">
-        <v>0.034000000000000002</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="F20" s="173">
-        <v>1.0694539999999999</v>
+        <v>0.71980739999999999</v>
       </c>
       <c r="G20" s="174">
-        <v>5.3144520000000002</v>
+        <v>2.5845630000000002</v>
       </c>
     </row>
     <row r="21">
@@ -15026,22 +15026,22 @@
         <v>21</v>
       </c>
       <c r="B21" s="177">
-        <v>0.53668380000000005</v>
+        <v>0.3089806</v>
       </c>
       <c r="C21" s="178">
-        <v>0.14266029999999999</v>
+        <v>0.033144399999999998</v>
       </c>
       <c r="D21" s="179">
-        <v>-2.3399999999999999</v>
+        <v>-10.949999999999999</v>
       </c>
       <c r="E21" s="180">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F21" s="181">
-        <v>0.3187526</v>
+        <v>0.25039329999999999</v>
       </c>
       <c r="G21" s="182">
-        <v>0.90361469999999999</v>
+        <v>0.38127630000000001</v>
       </c>
     </row>
     <row r="22">
@@ -15095,22 +15095,22 @@
         <v>19</v>
       </c>
       <c r="B24" s="201">
-        <v>0.99318770000000001</v>
+        <v>0.98608200000000001</v>
       </c>
       <c r="C24" s="202">
-        <v>0.27861570000000002</v>
+        <v>0.2765571</v>
       </c>
       <c r="D24" s="203">
-        <v>-0.02</v>
+        <v>-0.050000000000000003</v>
       </c>
       <c r="E24" s="204">
-        <v>0.98099999999999998</v>
+        <v>0.95999999999999997</v>
       </c>
       <c r="F24" s="205">
-        <v>0.5731214</v>
+        <v>0.56909480000000001</v>
       </c>
       <c r="G24" s="206">
-        <v>1.7211399999999999</v>
+        <v>1.708604</v>
       </c>
     </row>
     <row r="25">
@@ -15118,22 +15118,22 @@
         <v>20</v>
       </c>
       <c r="B25" s="209">
-        <v>1.844848</v>
+        <v>1.0772200000000001</v>
       </c>
       <c r="C25" s="210">
-        <v>0.73904119999999995</v>
+        <v>0.34881190000000001</v>
       </c>
       <c r="D25" s="211">
-        <v>1.53</v>
+        <v>0.23000000000000001</v>
       </c>
       <c r="E25" s="212">
-        <v>0.126</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="F25" s="213">
-        <v>0.84134030000000004</v>
+        <v>0.57105680000000003</v>
       </c>
       <c r="G25" s="214">
-        <v>4.0452899999999996</v>
+        <v>2.0320290000000001</v>
       </c>
     </row>
     <row r="26">
@@ -15141,22 +15141,22 @@
         <v>21</v>
       </c>
       <c r="B26" s="217">
-        <v>0.85454399999999997</v>
+        <v>0.48528159999999998</v>
       </c>
       <c r="C26" s="218">
-        <v>0.3854108</v>
+        <v>0.18200669999999999</v>
       </c>
       <c r="D26" s="219">
-        <v>-0.34999999999999998</v>
+        <v>-1.9299999999999999</v>
       </c>
       <c r="E26" s="220">
-        <v>0.72699999999999998</v>
+        <v>0.053999999999999999</v>
       </c>
       <c r="F26" s="221">
-        <v>0.35304580000000002</v>
+        <v>0.23267379999999999</v>
       </c>
       <c r="G26" s="222">
-        <v>2.0684149999999999</v>
+        <v>1.0121389999999999</v>
       </c>
     </row>
     <row r="27">
@@ -15187,22 +15187,22 @@
         <v>24</v>
       </c>
       <c r="B28" s="233">
-        <v>0.92954309999999996</v>
+        <v>0.92869219999999997</v>
       </c>
       <c r="C28" s="234">
-        <v>0.091952099999999995</v>
+        <v>0.091844200000000001</v>
       </c>
       <c r="D28" s="235">
-        <v>-0.73999999999999999</v>
+        <v>-0.75</v>
       </c>
       <c r="E28" s="236">
-        <v>0.46000000000000002</v>
+        <v>0.45400000000000001</v>
       </c>
       <c r="F28" s="237">
-        <v>0.76571489999999998</v>
+        <v>0.76505230000000002</v>
       </c>
       <c r="G28" s="238">
-        <v>1.128423</v>
+        <v>1.1273340000000001</v>
       </c>
     </row>
     <row r="29">
@@ -15210,22 +15210,22 @@
         <v>25</v>
       </c>
       <c r="B29" s="241">
-        <v>1.120093</v>
+        <v>1.1205909999999999</v>
       </c>
       <c r="C29" s="242">
-        <v>0.059580500000000002</v>
+        <v>0.0595877</v>
       </c>
       <c r="D29" s="243">
-        <v>2.1299999999999999</v>
+        <v>2.1400000000000001</v>
       </c>
       <c r="E29" s="244">
-        <v>0.033000000000000002</v>
+        <v>0.032000000000000001</v>
       </c>
       <c r="F29" s="245">
-        <v>1.009199</v>
+        <v>1.009682</v>
       </c>
       <c r="G29" s="246">
-        <v>1.2431730000000001</v>
+        <v>1.243684</v>
       </c>
     </row>
     <row r="30">
@@ -15233,22 +15233,22 @@
         <v>26</v>
       </c>
       <c r="B30" s="249">
-        <v>0.55220499999999995</v>
+        <v>0.55215820000000004</v>
       </c>
       <c r="C30" s="250">
-        <v>0.040018499999999999</v>
+        <v>0.0399932</v>
       </c>
       <c r="D30" s="251">
-        <v>-8.1899999999999995</v>
+        <v>-8.1999999999999993</v>
       </c>
       <c r="E30" s="252">
         <v>0</v>
       </c>
       <c r="F30" s="253">
-        <v>0.47908590000000001</v>
+        <v>0.47908260000000003</v>
       </c>
       <c r="G30" s="254">
-        <v>0.63648369999999999</v>
+        <v>0.63638019999999995</v>
       </c>
     </row>
     <row r="31">
@@ -15256,22 +15256,22 @@
         <v>27</v>
       </c>
       <c r="B31" s="257">
-        <v>0.8283239</v>
+        <v>0.83079329999999996</v>
       </c>
       <c r="C31" s="258">
-        <v>0.054681899999999999</v>
+        <v>0.054820599999999997</v>
       </c>
       <c r="D31" s="259">
-        <v>-2.8500000000000001</v>
+        <v>-2.8100000000000001</v>
       </c>
       <c r="E31" s="260">
-        <v>0.0040000000000000001</v>
+        <v>0.0050000000000000001</v>
       </c>
       <c r="F31" s="261">
-        <v>0.72779320000000003</v>
+        <v>0.73000489999999996</v>
       </c>
       <c r="G31" s="262">
-        <v>0.9427411</v>
+        <v>0.94549720000000004</v>
       </c>
     </row>
     <row r="32">
@@ -15279,22 +15279,22 @@
         <v>28</v>
       </c>
       <c r="B32" s="265">
-        <v>1.2435970000000001</v>
+        <v>1.24654</v>
       </c>
       <c r="C32" s="266">
-        <v>0.090160000000000004</v>
+        <v>0.090324100000000004</v>
       </c>
       <c r="D32" s="267">
-        <v>3.0099999999999998</v>
+        <v>3.04</v>
       </c>
       <c r="E32" s="268">
-        <v>0.0030000000000000001</v>
+        <v>0.002</v>
       </c>
       <c r="F32" s="269">
-        <v>1.078867</v>
+        <v>1.081504</v>
       </c>
       <c r="G32" s="270">
-        <v>1.433478</v>
+        <v>1.4367589999999999</v>
       </c>
     </row>
     <row r="33">
@@ -15302,22 +15302,22 @@
         <v>29</v>
       </c>
       <c r="B33" s="273">
-        <v>1.7659419999999999</v>
+        <v>1.7720100000000001</v>
       </c>
       <c r="C33" s="274">
-        <v>0.1485541</v>
+        <v>0.14898049999999999</v>
       </c>
       <c r="D33" s="275">
-        <v>6.7599999999999998</v>
+        <v>6.7999999999999998</v>
       </c>
       <c r="E33" s="276">
         <v>0</v>
       </c>
       <c r="F33" s="277">
-        <v>1.4975179999999999</v>
+        <v>1.502802</v>
       </c>
       <c r="G33" s="278">
-        <v>2.082481</v>
+        <v>2.089442</v>
       </c>
     </row>
     <row r="34">
@@ -15325,22 +15325,22 @@
         <v>30</v>
       </c>
       <c r="B34" s="281">
-        <v>2.0145599999999999</v>
+        <v>2.0435569999999999</v>
       </c>
       <c r="C34" s="282">
-        <v>0.37138139999999997</v>
+        <v>0.37689070000000002</v>
       </c>
       <c r="D34" s="283">
-        <v>3.7999999999999998</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="E34" s="284">
         <v>0</v>
       </c>
       <c r="F34" s="285">
-        <v>1.403662</v>
+        <v>1.4236420000000001</v>
       </c>
       <c r="G34" s="286">
-        <v>2.8913329999999999</v>
+        <v>2.9334099999999999</v>
       </c>
     </row>
     <row r="35">
@@ -15348,22 +15348,22 @@
         <v>31</v>
       </c>
       <c r="B35" s="289">
-        <v>0.92437480000000005</v>
+        <v>0.92847939999999996</v>
       </c>
       <c r="C35" s="290">
-        <v>0.1059585</v>
+        <v>0.1064005</v>
       </c>
       <c r="D35" s="291">
-        <v>-0.68999999999999995</v>
+        <v>-0.65000000000000002</v>
       </c>
       <c r="E35" s="292">
-        <v>0.49299999999999999</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="F35" s="293">
-        <v>0.73837540000000002</v>
+        <v>0.74169879999999999</v>
       </c>
       <c r="G35" s="294">
-        <v>1.1572279999999999</v>
+        <v>1.1622969999999999</v>
       </c>
     </row>
     <row r="36">
@@ -15371,22 +15371,22 @@
         <v>32</v>
       </c>
       <c r="B36" s="297">
-        <v>0.74031279999999999</v>
+        <v>0.74097690000000005</v>
       </c>
       <c r="C36" s="298">
-        <v>0.080440999999999999</v>
+        <v>0.080496899999999996</v>
       </c>
       <c r="D36" s="299">
-        <v>-2.77</v>
+        <v>-2.7599999999999998</v>
       </c>
       <c r="E36" s="300">
         <v>0.0060000000000000001</v>
       </c>
       <c r="F36" s="301">
-        <v>0.59830859999999997</v>
+        <v>0.59887120000000005</v>
       </c>
       <c r="G36" s="302">
-        <v>0.91602059999999996</v>
+        <v>0.91680289999999998</v>
       </c>
     </row>
     <row r="37">
@@ -15394,22 +15394,22 @@
         <v>33</v>
       </c>
       <c r="B37" s="305">
-        <v>0.46468860000000001</v>
+        <v>0.3597784</v>
       </c>
       <c r="C37" s="306">
-        <v>0.1008443</v>
+        <v>0.038785800000000002</v>
       </c>
       <c r="D37" s="307">
-        <v>-3.5299999999999998</v>
+        <v>-9.4800000000000004</v>
       </c>
       <c r="E37" s="308">
         <v>0</v>
       </c>
       <c r="F37" s="309">
-        <v>0.30369570000000001</v>
+        <v>0.29125380000000001</v>
       </c>
       <c r="G37" s="310">
-        <v>0.71102569999999998</v>
+        <v>0.44442510000000002</v>
       </c>
     </row>
     <row r="38">
@@ -15417,22 +15417,22 @@
         <v>34</v>
       </c>
       <c r="B38" s="313">
-        <v>0.86745280000000002</v>
+        <v>0.86714659999999999</v>
       </c>
       <c r="C38" s="314">
-        <v>0.094178399999999996</v>
+        <v>0.094197199999999995</v>
       </c>
       <c r="D38" s="315">
         <v>-1.3100000000000001</v>
       </c>
       <c r="E38" s="316">
-        <v>0.19</v>
+        <v>0.189</v>
       </c>
       <c r="F38" s="317">
-        <v>0.70118369999999997</v>
+        <v>0.70085379999999997</v>
       </c>
       <c r="G38" s="318">
-        <v>1.0731489999999999</v>
+        <v>1.0728960000000001</v>
       </c>
     </row>
     <row r="39">
@@ -15440,22 +15440,22 @@
         <v>35</v>
       </c>
       <c r="B39" s="321">
-        <v>0.8724073</v>
+        <v>0.87149569999999999</v>
       </c>
       <c r="C39" s="322">
-        <v>0.011143399999999999</v>
+        <v>0.0111234</v>
       </c>
       <c r="D39" s="323">
-        <v>-10.69</v>
+        <v>-10.779999999999999</v>
       </c>
       <c r="E39" s="324">
         <v>0</v>
       </c>
       <c r="F39" s="325">
-        <v>0.85083759999999997</v>
+        <v>0.84996470000000002</v>
       </c>
       <c r="G39" s="326">
-        <v>0.89452370000000003</v>
+        <v>0.89357200000000003</v>
       </c>
     </row>
     <row r="40">
@@ -15463,22 +15463,22 @@
         <v>36</v>
       </c>
       <c r="B40" s="329">
-        <v>0.52355189999999996</v>
+        <v>0.52396120000000002</v>
       </c>
       <c r="C40" s="330">
-        <v>0.074685000000000001</v>
+        <v>0.074733300000000003</v>
       </c>
       <c r="D40" s="331">
-        <v>-4.54</v>
+        <v>-4.5300000000000002</v>
       </c>
       <c r="E40" s="332">
         <v>0</v>
       </c>
       <c r="F40" s="333">
-        <v>0.39585429999999999</v>
+        <v>0.3961787</v>
       </c>
       <c r="G40" s="334">
-        <v>0.69244320000000004</v>
+        <v>0.69295839999999998</v>
       </c>
     </row>
     <row r="41">
@@ -15486,22 +15486,22 @@
         <v>37</v>
       </c>
       <c r="B41" s="337">
-        <v>0.83361940000000001</v>
+        <v>0.83459309999999998</v>
       </c>
       <c r="C41" s="338">
-        <v>0.058167999999999998</v>
+        <v>0.058200700000000001</v>
       </c>
       <c r="D41" s="339">
-        <v>-2.6099999999999999</v>
+        <v>-2.5899999999999999</v>
       </c>
       <c r="E41" s="340">
-        <v>0.0089999999999999993</v>
+        <v>0.01</v>
       </c>
       <c r="F41" s="341">
-        <v>0.7270645</v>
+        <v>0.72797400000000001</v>
       </c>
       <c r="G41" s="342">
-        <v>0.95579049999999999</v>
+        <v>0.9568276</v>
       </c>
     </row>
     <row r="42">
@@ -15509,22 +15509,22 @@
         <v>38</v>
       </c>
       <c r="B42" s="345">
-        <v>0.78871279999999999</v>
+        <v>0.79076880000000005</v>
       </c>
       <c r="C42" s="346">
-        <v>0.1000423</v>
+        <v>0.1002459</v>
       </c>
       <c r="D42" s="347">
-        <v>-1.8700000000000001</v>
+        <v>-1.8500000000000001</v>
       </c>
       <c r="E42" s="348">
-        <v>0.060999999999999999</v>
+        <v>0.064000000000000001</v>
       </c>
       <c r="F42" s="349">
-        <v>0.61510659999999995</v>
+        <v>0.6167975</v>
       </c>
       <c r="G42" s="350">
-        <v>1.011317</v>
+        <v>1.0138100000000001</v>
       </c>
     </row>
     <row r="43">
@@ -15532,22 +15532,22 @@
         <v>39</v>
       </c>
       <c r="B43" s="353">
-        <v>0.74126910000000001</v>
+        <v>0.74163869999999999</v>
       </c>
       <c r="C43" s="354">
-        <v>0.068133899999999997</v>
+        <v>0.068152199999999996</v>
       </c>
       <c r="D43" s="355">
-        <v>-3.2599999999999998</v>
+        <v>-3.25</v>
       </c>
       <c r="E43" s="356">
         <v>0.001</v>
       </c>
       <c r="F43" s="357">
-        <v>0.61906680000000003</v>
+        <v>0.61940110000000004</v>
       </c>
       <c r="G43" s="358">
-        <v>0.88759390000000005</v>
+        <v>0.8879996</v>
       </c>
     </row>
     <row r="44">
@@ -15555,22 +15555,22 @@
         <v>40</v>
       </c>
       <c r="B44" s="361">
-        <v>0.97204000000000002</v>
+        <v>0.97441639999999996</v>
       </c>
       <c r="C44" s="362">
-        <v>0.087967000000000004</v>
+        <v>0.088131500000000002</v>
       </c>
       <c r="D44" s="363">
-        <v>-0.31</v>
+        <v>-0.28999999999999998</v>
       </c>
       <c r="E44" s="364">
-        <v>0.754</v>
+        <v>0.77400000000000002</v>
       </c>
       <c r="F44" s="365">
-        <v>0.81405300000000003</v>
+        <v>0.81612620000000002</v>
       </c>
       <c r="G44" s="366">
-        <v>1.160688</v>
+        <v>1.1634070000000001</v>
       </c>
     </row>
     <row r="45">
@@ -15578,22 +15578,22 @@
         <v>41</v>
       </c>
       <c r="B45" s="369">
-        <v>0.92738969999999998</v>
+        <v>0.91880759999999995</v>
       </c>
       <c r="C45" s="370">
-        <v>0.53840969999999999</v>
+        <v>0.53262620000000005</v>
       </c>
       <c r="D45" s="371">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="E45" s="372">
-        <v>0.89700000000000002</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="F45" s="373">
-        <v>0.29722460000000001</v>
+        <v>0.29497760000000001</v>
       </c>
       <c r="G45" s="374">
-        <v>2.8936090000000001</v>
+        <v>2.8619370000000002</v>
       </c>
     </row>
     <row r="46">
@@ -15601,22 +15601,22 @@
         <v>42</v>
       </c>
       <c r="B46" s="377">
-        <v>1.094854</v>
+        <v>1.09328</v>
       </c>
       <c r="C46" s="378">
-        <v>0.043226000000000001</v>
+        <v>0.043152799999999998</v>
       </c>
       <c r="D46" s="379">
-        <v>2.2999999999999998</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="E46" s="380">
-        <v>0.021999999999999999</v>
+        <v>0.024</v>
       </c>
       <c r="F46" s="381">
-        <v>1.013328</v>
+        <v>1.0118910000000001</v>
       </c>
       <c r="G46" s="382">
-        <v>1.1829400000000001</v>
+        <v>1.1812149999999999</v>
       </c>
     </row>
     <row r="47">
@@ -15624,22 +15624,22 @@
         <v>43</v>
       </c>
       <c r="B47" s="385">
-        <v>0.95155009999999996</v>
+        <v>0.95077999999999996</v>
       </c>
       <c r="C47" s="386">
-        <v>0.0248541</v>
+        <v>0.024815299999999999</v>
       </c>
       <c r="D47" s="387">
-        <v>-1.8999999999999999</v>
+        <v>-1.9299999999999999</v>
       </c>
       <c r="E47" s="388">
-        <v>0.057000000000000002</v>
+        <v>0.052999999999999999</v>
       </c>
       <c r="F47" s="389">
-        <v>0.9040629</v>
+        <v>0.903366</v>
       </c>
       <c r="G47" s="390">
-        <v>1.0015320000000001</v>
+        <v>1.000683</v>
       </c>
     </row>
     <row r="48">
@@ -15647,22 +15647,22 @@
         <v>44</v>
       </c>
       <c r="B48" s="393">
-        <v>0.80558909999999995</v>
+        <v>0.80775810000000003</v>
       </c>
       <c r="C48" s="394">
-        <v>0.045275200000000002</v>
+        <v>0.045404100000000003</v>
       </c>
       <c r="D48" s="395">
-        <v>-3.8500000000000001</v>
+        <v>-3.7999999999999998</v>
       </c>
       <c r="E48" s="396">
         <v>0</v>
       </c>
       <c r="F48" s="397">
-        <v>0.72156419999999999</v>
+        <v>0.72349450000000004</v>
       </c>
       <c r="G48" s="398">
-        <v>0.8993987</v>
+        <v>0.90183570000000002</v>
       </c>
     </row>
     <row r="49">
@@ -15670,22 +15670,22 @@
         <v>45</v>
       </c>
       <c r="B49" s="401">
-        <v>0.92934450000000002</v>
+        <v>0.93145319999999998</v>
       </c>
       <c r="C49" s="402">
-        <v>0.074740200000000007</v>
+        <v>0.074876799999999993</v>
       </c>
       <c r="D49" s="403">
-        <v>-0.91000000000000003</v>
+        <v>-0.88</v>
       </c>
       <c r="E49" s="404">
-        <v>0.36199999999999999</v>
+        <v>0.377</v>
       </c>
       <c r="F49" s="405">
-        <v>0.79381809999999997</v>
+        <v>0.7956744</v>
       </c>
       <c r="G49" s="406">
-        <v>1.088009</v>
+        <v>1.0904020000000001</v>
       </c>
     </row>
     <row r="50">
@@ -15693,22 +15693,22 @@
         <v>46</v>
       </c>
       <c r="B50" s="409">
-        <v>0.89705299999999999</v>
+        <v>0.89851619999999999</v>
       </c>
       <c r="C50" s="410">
-        <v>0.037905599999999998</v>
+        <v>0.037957100000000001</v>
       </c>
       <c r="D50" s="411">
-        <v>-2.5699999999999999</v>
+        <v>-2.5299999999999998</v>
       </c>
       <c r="E50" s="412">
-        <v>0.01</v>
+        <v>0.010999999999999999</v>
       </c>
       <c r="F50" s="413">
-        <v>0.82575259999999995</v>
+        <v>0.82711820000000003</v>
       </c>
       <c r="G50" s="414">
-        <v>0.97450979999999998</v>
+        <v>0.97607750000000004</v>
       </c>
     </row>
     <row r="51">
@@ -15716,22 +15716,22 @@
         <v>47</v>
       </c>
       <c r="B51" s="417">
-        <v>0.88480959999999997</v>
+        <v>0.88780550000000003</v>
       </c>
       <c r="C51" s="418">
-        <v>0.0841084</v>
+        <v>0.084552299999999997</v>
       </c>
       <c r="D51" s="419">
-        <v>-1.29</v>
+        <v>-1.25</v>
       </c>
       <c r="E51" s="420">
-        <v>0.19800000000000001</v>
+        <v>0.21099999999999999</v>
       </c>
       <c r="F51" s="421">
-        <v>0.73440589999999995</v>
+        <v>0.73663380000000001</v>
       </c>
       <c r="G51" s="422">
-        <v>1.0660149999999999</v>
+        <v>1.070001</v>
       </c>
     </row>
     <row r="52">
@@ -15739,22 +15739,22 @@
         <v>48</v>
       </c>
       <c r="B52" s="425">
-        <v>0.86274779999999995</v>
+        <v>0.8619272</v>
       </c>
       <c r="C52" s="426">
-        <v>0.067236299999999999</v>
+        <v>0.067169300000000001</v>
       </c>
       <c r="D52" s="427">
-        <v>-1.8899999999999999</v>
+        <v>-1.9099999999999999</v>
       </c>
       <c r="E52" s="428">
-        <v>0.058000000000000003</v>
+        <v>0.057000000000000002</v>
       </c>
       <c r="F52" s="429">
-        <v>0.74053809999999998</v>
+        <v>0.73983889999999997</v>
       </c>
       <c r="G52" s="430">
-        <v>1.005126</v>
+        <v>1.0041629999999999</v>
       </c>
     </row>
     <row r="53">
@@ -15762,22 +15762,22 @@
         <v>49</v>
       </c>
       <c r="B53" s="433">
-        <v>0.95653290000000002</v>
+        <v>0.95759669999999997</v>
       </c>
       <c r="C53" s="434">
-        <v>0.038327100000000003</v>
+        <v>0.038366900000000002</v>
       </c>
       <c r="D53" s="435">
-        <v>-1.1100000000000001</v>
+        <v>-1.0800000000000001</v>
       </c>
       <c r="E53" s="436">
-        <v>0.26700000000000002</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F53" s="437">
-        <v>0.88428720000000005</v>
+        <v>0.8852757</v>
       </c>
       <c r="G53" s="438">
-        <v>1.034681</v>
+        <v>1.0358259999999999</v>
       </c>
     </row>
     <row r="54">
@@ -15785,10 +15785,10 @@
         <v>50</v>
       </c>
       <c r="B54" s="441">
-        <v>0.86602460000000003</v>
+        <v>0.86605540000000003</v>
       </c>
       <c r="C54" s="442">
-        <v>0.035971000000000003</v>
+        <v>0.035968399999999998</v>
       </c>
       <c r="D54" s="443">
         <v>-3.46</v>
@@ -15797,10 +15797,10 @@
         <v>0.001</v>
       </c>
       <c r="F54" s="445">
-        <v>0.79831620000000003</v>
+        <v>0.79835160000000005</v>
       </c>
       <c r="G54" s="446">
-        <v>0.93947570000000002</v>
+        <v>0.93950080000000002</v>
       </c>
     </row>
     <row r="55">
@@ -15831,22 +15831,22 @@
         <v>52</v>
       </c>
       <c r="B56" s="457">
-        <v>0.70654819999999996</v>
+        <v>0.70402019999999999</v>
       </c>
       <c r="C56" s="458">
-        <v>0.1207954</v>
+        <v>0.1202532</v>
       </c>
       <c r="D56" s="459">
-        <v>-2.0299999999999998</v>
+        <v>-2.0499999999999998</v>
       </c>
       <c r="E56" s="460">
-        <v>0.042000000000000003</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="F56" s="461">
-        <v>0.50537730000000003</v>
+        <v>0.50372329999999999</v>
       </c>
       <c r="G56" s="462">
-        <v>0.98779740000000005</v>
+        <v>0.9839618</v>
       </c>
     </row>
     <row r="57">
@@ -15854,22 +15854,22 @@
         <v>53</v>
       </c>
       <c r="B57" s="465">
-        <v>0.90027869999999999</v>
+        <v>0.9005706</v>
       </c>
       <c r="C57" s="466">
-        <v>0.1620393</v>
+        <v>0.1619062</v>
       </c>
       <c r="D57" s="467">
         <v>-0.57999999999999996</v>
       </c>
       <c r="E57" s="468">
-        <v>0.55900000000000005</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="F57" s="469">
-        <v>0.63266089999999997</v>
+        <v>0.63312170000000001</v>
       </c>
       <c r="G57" s="470">
-        <v>1.2810999999999999</v>
+        <v>1.2809980000000001</v>
       </c>
     </row>
     <row r="58">
@@ -15877,22 +15877,22 @@
         <v>54</v>
       </c>
       <c r="B58" s="473">
-        <v>0.72033000000000003</v>
+        <v>0.71731509999999998</v>
       </c>
       <c r="C58" s="474">
-        <v>0.1186745</v>
+        <v>0.1180537</v>
       </c>
       <c r="D58" s="475">
-        <v>-1.99</v>
+        <v>-2.02</v>
       </c>
       <c r="E58" s="476">
-        <v>0.045999999999999999</v>
+        <v>0.043999999999999998</v>
       </c>
       <c r="F58" s="477">
-        <v>0.52154990000000001</v>
+        <v>0.51954310000000004</v>
       </c>
       <c r="G58" s="478">
-        <v>0.99487190000000003</v>
+        <v>0.99037200000000003</v>
       </c>
     </row>
     <row r="59">
@@ -15900,22 +15900,22 @@
         <v>55</v>
       </c>
       <c r="B59" s="481">
-        <v>1.1285829999999999</v>
+        <v>1.120144</v>
       </c>
       <c r="C59" s="482">
-        <v>0.18179699999999999</v>
+        <v>0.18025079999999999</v>
       </c>
       <c r="D59" s="483">
-        <v>0.75</v>
+        <v>0.70999999999999997</v>
       </c>
       <c r="E59" s="484">
-        <v>0.45300000000000001</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="F59" s="485">
-        <v>0.82303459999999995</v>
+        <v>0.81714750000000003</v>
       </c>
       <c r="G59" s="486">
-        <v>1.5475639999999999</v>
+        <v>1.53549</v>
       </c>
     </row>
     <row r="60">
@@ -15946,22 +15946,22 @@
         <v>57</v>
       </c>
       <c r="B61" s="497">
-        <v>0.95548180000000005</v>
+        <v>0.95467409999999997</v>
       </c>
       <c r="C61" s="498">
-        <v>0.0582412</v>
+        <v>0.0581939</v>
       </c>
       <c r="D61" s="499">
-        <v>-0.75</v>
+        <v>-0.76000000000000001</v>
       </c>
       <c r="E61" s="500">
-        <v>0.45500000000000002</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="F61" s="501">
-        <v>0.84788629999999998</v>
+        <v>0.84716610000000003</v>
       </c>
       <c r="G61" s="502">
-        <v>1.0767310000000001</v>
+        <v>1.075825</v>
       </c>
     </row>
     <row r="62">
@@ -15969,22 +15969,22 @@
         <v>58</v>
       </c>
       <c r="B62" s="505">
-        <v>1.02119</v>
+        <v>1.017576</v>
       </c>
       <c r="C62" s="506">
-        <v>0.077821799999999997</v>
+        <v>0.077511399999999994</v>
       </c>
       <c r="D62" s="507">
-        <v>0.28000000000000003</v>
+        <v>0.23000000000000001</v>
       </c>
       <c r="E62" s="508">
-        <v>0.78300000000000003</v>
+        <v>0.81899999999999995</v>
       </c>
       <c r="F62" s="509">
-        <v>0.87950640000000002</v>
+        <v>0.87645329999999999</v>
       </c>
       <c r="G62" s="510">
-        <v>1.1856979999999999</v>
+        <v>1.181422</v>
       </c>
     </row>
     <row r="63">
@@ -15992,22 +15992,22 @@
         <v>59</v>
       </c>
       <c r="B63" s="513">
-        <v>0.90837299999999999</v>
+        <v>0.91354270000000004</v>
       </c>
       <c r="C63" s="514">
-        <v>0.052869399999999997</v>
+        <v>0.053155500000000001</v>
       </c>
       <c r="D63" s="515">
-        <v>-1.6499999999999999</v>
+        <v>-1.55</v>
       </c>
       <c r="E63" s="516">
-        <v>0.099000000000000005</v>
+        <v>0.12</v>
       </c>
       <c r="F63" s="517">
-        <v>0.81044260000000001</v>
+        <v>0.8150809</v>
       </c>
       <c r="G63" s="518">
-        <v>1.0181370000000001</v>
+        <v>1.0238989999999999</v>
       </c>
     </row>
     <row r="64">
@@ -16015,22 +16015,22 @@
         <v>60</v>
       </c>
       <c r="B64" s="521">
-        <v>1.4199459999999999</v>
+        <v>1.418258</v>
       </c>
       <c r="C64" s="522">
-        <v>0.2033818</v>
+        <v>0.20303679999999999</v>
       </c>
       <c r="D64" s="523">
-        <v>2.4500000000000002</v>
+        <v>2.44</v>
       </c>
       <c r="E64" s="524">
-        <v>0.014</v>
+        <v>0.014999999999999999</v>
       </c>
       <c r="F64" s="525">
-        <v>1.072389</v>
+        <v>1.071267</v>
       </c>
       <c r="G64" s="526">
-        <v>1.880144</v>
+        <v>1.8776409999999999</v>
       </c>
     </row>
     <row r="65">
@@ -16038,22 +16038,22 @@
         <v>61</v>
       </c>
       <c r="B65" s="529">
-        <v>1.5297449999999999</v>
+        <v>1.521037</v>
       </c>
       <c r="C65" s="530">
-        <v>0.32426319999999997</v>
+        <v>0.32207029999999998</v>
       </c>
       <c r="D65" s="531">
-        <v>2.0099999999999998</v>
+        <v>1.98</v>
       </c>
       <c r="E65" s="532">
-        <v>0.044999999999999998</v>
+        <v>0.048000000000000001</v>
       </c>
       <c r="F65" s="533">
-        <v>1.00969</v>
+        <v>1.004391</v>
       </c>
       <c r="G65" s="534">
-        <v>2.3176610000000002</v>
+        <v>2.3034379999999999</v>
       </c>
     </row>
     <row r="66">
@@ -16061,22 +16061,22 @@
         <v>62</v>
       </c>
       <c r="B66" s="537">
-        <v>0.37475249999999999</v>
+        <v>0.37219269999999999</v>
       </c>
       <c r="C66" s="538">
-        <v>0.57707169999999997</v>
+        <v>0.57274250000000004</v>
       </c>
       <c r="D66" s="539">
         <v>-0.64000000000000001</v>
       </c>
       <c r="E66" s="540">
-        <v>0.52400000000000002</v>
+        <v>0.52100000000000002</v>
       </c>
       <c r="F66" s="541">
-        <v>0.018323200000000001</v>
+        <v>0.0182352</v>
       </c>
       <c r="G66" s="542">
-        <v>7.664568</v>
+        <v>7.5967039999999999</v>
       </c>
     </row>
     <row r="67">
@@ -16084,22 +16084,22 @@
         <v>63</v>
       </c>
       <c r="B67" s="545">
-        <v>0.99886249999999999</v>
+        <v>0.99830490000000005</v>
       </c>
       <c r="C67" s="546">
-        <v>0.086314500000000002</v>
+        <v>0.0862145</v>
       </c>
       <c r="D67" s="547">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="E67" s="548">
-        <v>0.98899999999999999</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="F67" s="549">
-        <v>0.84323959999999998</v>
+        <v>0.84285449999999995</v>
       </c>
       <c r="G67" s="550">
-        <v>1.183206</v>
+        <v>1.1824250000000001</v>
       </c>
     </row>
     <row r="68">
@@ -16107,22 +16107,22 @@
         <v>64</v>
       </c>
       <c r="B68" s="553">
-        <v>1.205918</v>
+        <v>1.206191</v>
       </c>
       <c r="C68" s="554">
-        <v>0.1208795</v>
+        <v>0.1208519</v>
       </c>
       <c r="D68" s="555">
         <v>1.8700000000000001</v>
       </c>
       <c r="E68" s="556">
-        <v>0.062</v>
+        <v>0.060999999999999999</v>
       </c>
       <c r="F68" s="557">
-        <v>0.99081969999999997</v>
+        <v>0.99113280000000004</v>
       </c>
       <c r="G68" s="558">
-        <v>1.467713</v>
+        <v>1.467914</v>
       </c>
     </row>
     <row r="69">
@@ -16130,22 +16130,22 @@
         <v>65</v>
       </c>
       <c r="B69" s="561">
-        <v>1.2827390000000001</v>
+        <v>1.285177</v>
       </c>
       <c r="C69" s="562">
-        <v>0.16728090000000001</v>
+        <v>0.16743810000000001</v>
       </c>
       <c r="D69" s="563">
-        <v>1.9099999999999999</v>
+        <v>1.9299999999999999</v>
       </c>
       <c r="E69" s="564">
-        <v>0.056000000000000001</v>
+        <v>0.053999999999999999</v>
       </c>
       <c r="F69" s="565">
-        <v>0.99342240000000004</v>
+        <v>0.99555439999999995</v>
       </c>
       <c r="G69" s="566">
-        <v>1.656315</v>
+        <v>1.6590560000000001</v>
       </c>
     </row>
     <row r="70">
@@ -16153,22 +16153,22 @@
         <v>66</v>
       </c>
       <c r="B70" s="569">
-        <v>0.48615920000000001</v>
+        <v>0.473719</v>
       </c>
       <c r="C70" s="570">
-        <v>0.32485540000000002</v>
+        <v>0.31612230000000002</v>
       </c>
       <c r="D70" s="571">
-        <v>-1.0800000000000001</v>
+        <v>-1.1200000000000001</v>
       </c>
       <c r="E70" s="572">
-        <v>0.28000000000000003</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="F70" s="573">
-        <v>0.1312197</v>
+        <v>0.12808449999999999</v>
       </c>
       <c r="G70" s="574">
-        <v>1.8011839999999999</v>
+        <v>1.7520439999999999</v>
       </c>
     </row>
     <row r="71">
@@ -16176,22 +16176,22 @@
         <v>67</v>
       </c>
       <c r="B71" s="577">
-        <v>1.67547</v>
+        <v>1.6785460000000001</v>
       </c>
       <c r="C71" s="578">
-        <v>0.31797389999999998</v>
+        <v>0.31821349999999998</v>
       </c>
       <c r="D71" s="579">
-        <v>2.7200000000000002</v>
+        <v>2.73</v>
       </c>
       <c r="E71" s="580">
-        <v>0.0070000000000000001</v>
+        <v>0.0060000000000000001</v>
       </c>
       <c r="F71" s="581">
-        <v>1.1550320000000001</v>
+        <v>1.157618</v>
       </c>
       <c r="G71" s="582">
-        <v>2.4304079999999999</v>
+        <v>2.4338929999999999</v>
       </c>
     </row>
     <row r="72">
@@ -16199,22 +16199,22 @@
         <v>68</v>
       </c>
       <c r="B72" s="585">
-        <v>0.94634989999999997</v>
+        <v>0.9431737</v>
       </c>
       <c r="C72" s="586">
-        <v>0.25296960000000002</v>
+        <v>0.25205640000000001</v>
       </c>
       <c r="D72" s="587">
-        <v>-0.20999999999999999</v>
+        <v>-0.22</v>
       </c>
       <c r="E72" s="588">
-        <v>0.83699999999999997</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="F72" s="589">
-        <v>0.56042349999999996</v>
+        <v>0.55861700000000003</v>
       </c>
       <c r="G72" s="590">
-        <v>1.5980380000000001</v>
+        <v>1.592462</v>
       </c>
     </row>
     <row r="73">
@@ -16222,22 +16222,22 @@
         <v>69</v>
       </c>
       <c r="B73" s="593">
-        <v>0.94726089999999996</v>
+        <v>0.94853109999999996</v>
       </c>
       <c r="C73" s="594">
-        <v>0.112485</v>
+        <v>0.1124882</v>
       </c>
       <c r="D73" s="595">
-        <v>-0.46000000000000002</v>
+        <v>-0.45000000000000001</v>
       </c>
       <c r="E73" s="596">
-        <v>0.64800000000000002</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="F73" s="597">
-        <v>0.75057030000000002</v>
+        <v>0.75180630000000004</v>
       </c>
       <c r="G73" s="598">
-        <v>1.195495</v>
+        <v>1.196733</v>
       </c>
     </row>
     <row r="74">
@@ -16245,22 +16245,22 @@
         <v>70</v>
       </c>
       <c r="B74" s="601">
-        <v>1.0879509999999999</v>
+        <v>1.095502</v>
       </c>
       <c r="C74" s="602">
-        <v>0.1827858</v>
+        <v>0.18395639999999999</v>
       </c>
       <c r="D74" s="603">
-        <v>0.5</v>
+        <v>0.54000000000000004</v>
       </c>
       <c r="E74" s="604">
-        <v>0.61599999999999999</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="F74" s="605">
-        <v>0.78270799999999996</v>
+        <v>0.78827789999999998</v>
       </c>
       <c r="G74" s="606">
-        <v>1.512235</v>
+        <v>1.5224629999999999</v>
       </c>
     </row>
     <row r="75">
@@ -16268,22 +16268,22 @@
         <v>71</v>
       </c>
       <c r="B75" s="609">
-        <v>0.96328389999999997</v>
+        <v>0.94975560000000003</v>
       </c>
       <c r="C75" s="610">
-        <v>0.057050799999999999</v>
+        <v>0.056081699999999998</v>
       </c>
       <c r="D75" s="611">
-        <v>-0.63</v>
+        <v>-0.87</v>
       </c>
       <c r="E75" s="612">
-        <v>0.52800000000000002</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="F75" s="613">
-        <v>0.85771229999999998</v>
+        <v>0.84595969999999998</v>
       </c>
       <c r="G75" s="614">
-        <v>1.08185</v>
+        <v>1.066287</v>
       </c>
     </row>
     <row r="76">
@@ -16291,22 +16291,22 @@
         <v>72</v>
       </c>
       <c r="B76" s="617">
-        <v>1.508187</v>
+        <v>1.465876</v>
       </c>
       <c r="C76" s="618">
-        <v>0.23993809999999999</v>
+        <v>0.23221339999999999</v>
       </c>
       <c r="D76" s="619">
-        <v>2.5800000000000001</v>
+        <v>2.4100000000000001</v>
       </c>
       <c r="E76" s="620">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="F76" s="621">
-        <v>1.1041730000000001</v>
+        <v>1.0746230000000001</v>
       </c>
       <c r="G76" s="622">
-        <v>2.0600290000000001</v>
+        <v>1.9995780000000001</v>
       </c>
     </row>
     <row r="77">
@@ -16314,22 +16314,22 @@
         <v>73</v>
       </c>
       <c r="B77" s="625">
-        <v>1.108001</v>
+        <v>1.1174980000000001</v>
       </c>
       <c r="C77" s="626">
-        <v>0.089749999999999997</v>
+        <v>0.0904552</v>
       </c>
       <c r="D77" s="627">
-        <v>1.27</v>
+        <v>1.3700000000000001</v>
       </c>
       <c r="E77" s="628">
-        <v>0.20499999999999999</v>
+        <v>0.17000000000000001</v>
       </c>
       <c r="F77" s="629">
-        <v>0.9453471</v>
+        <v>0.95355749999999995</v>
       </c>
       <c r="G77" s="630">
-        <v>1.29864</v>
+        <v>1.309625</v>
       </c>
     </row>
     <row r="78">
@@ -16337,22 +16337,22 @@
         <v>74</v>
       </c>
       <c r="B78" s="633">
-        <v>1.4318150000000001</v>
+        <v>1.4227160000000001</v>
       </c>
       <c r="C78" s="634">
-        <v>0.37345810000000002</v>
+        <v>0.37109320000000001</v>
       </c>
       <c r="D78" s="635">
-        <v>1.3799999999999999</v>
+        <v>1.3500000000000001</v>
       </c>
       <c r="E78" s="636">
-        <v>0.16900000000000001</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="F78" s="637">
-        <v>0.85875489999999999</v>
+        <v>0.85328839999999995</v>
       </c>
       <c r="G78" s="638">
-        <v>2.387286</v>
+        <v>2.3721429999999999</v>
       </c>
     </row>
     <row r="79">
@@ -16406,22 +16406,22 @@
         <v>1</v>
       </c>
       <c r="B81" s="657">
-        <v>0.68046130000000005</v>
+        <v>37600000</v>
       </c>
       <c r="C81" s="658">
-        <v>0.17001649999999999</v>
+        <v>2510000000</v>
       </c>
       <c r="D81" s="659">
-        <v>-1.54</v>
+        <v>0.26000000000000001</v>
       </c>
       <c r="E81" s="660">
-        <v>0.123</v>
+        <v>0.79400000000000004</v>
       </c>
       <c r="F81" s="661">
-        <v>0.416991</v>
+        <v>6.1600000000000003e-50</v>
       </c>
       <c r="G81" s="662">
-        <v>1.1104019999999999</v>
+        <v>2.3e+64</v>
       </c>
     </row>
     <row r="82">
@@ -16475,22 +16475,22 @@
         <v>1</v>
       </c>
       <c r="B84" s="681">
-        <v>6.0548960000000003</v>
+        <v>7.81907</v>
       </c>
       <c r="C84" s="682">
-        <v>4.9696559999999996</v>
+        <v>6.244726</v>
       </c>
       <c r="D84" s="683">
-        <v>2.19</v>
+        <v>2.5800000000000001</v>
       </c>
       <c r="E84" s="684">
-        <v>0.028000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F84" s="685">
-        <v>1.2119059999999999</v>
+        <v>1.6343319999999999</v>
       </c>
       <c r="G84" s="686">
-        <v>30.251329999999999</v>
+        <v>37.408479999999997</v>
       </c>
     </row>
     <row r="85">
@@ -16544,22 +16544,22 @@
         <v>1</v>
       </c>
       <c r="B87" s="705">
-        <v>0.82965630000000001</v>
+        <v>2.85e-08</v>
       </c>
       <c r="C87" s="706">
-        <v>0.20293990000000001</v>
+        <v>1.9e-06</v>
       </c>
       <c r="D87" s="707">
-        <v>-0.76000000000000001</v>
+        <v>-0.26000000000000001</v>
       </c>
       <c r="E87" s="708">
-        <v>0.44500000000000001</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="F87" s="709">
-        <v>0.51367479999999999</v>
+        <v>4.6699999999999997e-65</v>
       </c>
       <c r="G87" s="710">
-        <v>1.3400099999999999</v>
+        <v>1.7400000000000001e+49</v>
       </c>
     </row>
     <row r="88">
@@ -16613,22 +16613,22 @@
         <v>1</v>
       </c>
       <c r="B90" s="729">
-        <v>1.516319</v>
+        <v>1.9546349999999999</v>
       </c>
       <c r="C90" s="730">
-        <v>0.35964249999999998</v>
+        <v>0.28353010000000001</v>
       </c>
       <c r="D90" s="731">
-        <v>1.76</v>
+        <v>4.6200000000000001</v>
       </c>
       <c r="E90" s="732">
-        <v>0.079000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F90" s="733">
-        <v>0.95257999999999998</v>
+        <v>1.4709380000000001</v>
       </c>
       <c r="G90" s="734">
-        <v>2.4136799999999998</v>
+        <v>2.5973890000000002</v>
       </c>
     </row>
     <row r="91">
@@ -16682,22 +16682,22 @@
         <v>1</v>
       </c>
       <c r="B93" s="753">
-        <v>1.8507450000000001</v>
+        <v>2.320986</v>
       </c>
       <c r="C93" s="754">
-        <v>0.95050809999999997</v>
+        <v>1.1111530000000001</v>
       </c>
       <c r="D93" s="755">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="E93" s="756">
-        <v>0.23100000000000001</v>
+        <v>0.079000000000000001</v>
       </c>
       <c r="F93" s="757">
-        <v>0.67637170000000002</v>
+        <v>0.9081688</v>
       </c>
       <c r="G93" s="758">
-        <v>5.064165</v>
+        <v>5.9316890000000004</v>
       </c>
     </row>
     <row r="94">
@@ -16751,22 +16751,22 @@
         <v>1</v>
       </c>
       <c r="B96" s="777">
-        <v>3.670512</v>
+        <v>4.824872</v>
       </c>
       <c r="C96" s="778">
-        <v>1.078945</v>
+        <v>1.1034919999999999</v>
       </c>
       <c r="D96" s="779">
-        <v>4.4199999999999999</v>
+        <v>6.8799999999999999</v>
       </c>
       <c r="E96" s="780">
         <v>0</v>
       </c>
       <c r="F96" s="781">
-        <v>2.0630820000000001</v>
+        <v>3.0818270000000001</v>
       </c>
       <c r="G96" s="782">
-        <v>6.5303570000000004</v>
+        <v>7.5537619999999999</v>
       </c>
     </row>
     <row r="97">
@@ -16820,22 +16820,22 @@
         <v>1</v>
       </c>
       <c r="B99" s="801">
-        <v>2.2813940000000001</v>
+        <v>3.019215</v>
       </c>
       <c r="C99" s="802">
-        <v>1.2395259999999999</v>
+        <v>1.5417730000000001</v>
       </c>
       <c r="D99" s="803">
-        <v>1.52</v>
+        <v>2.1600000000000001</v>
       </c>
       <c r="E99" s="804">
-        <v>0.129</v>
+        <v>0.029999999999999999</v>
       </c>
       <c r="F99" s="805">
-        <v>0.78654939999999996</v>
+        <v>1.1097490000000001</v>
       </c>
       <c r="G99" s="806">
-        <v>6.6172079999999998</v>
+        <v>8.2141610000000007</v>
       </c>
     </row>
     <row r="100">
@@ -16889,22 +16889,22 @@
         <v>1</v>
       </c>
       <c r="B102" s="825">
-        <v>1.305895</v>
+        <v>1.687975</v>
       </c>
       <c r="C102" s="826">
-        <v>1.25553</v>
+        <v>1.594128</v>
       </c>
       <c r="D102" s="827">
-        <v>0.28000000000000003</v>
+        <v>0.55000000000000005</v>
       </c>
       <c r="E102" s="828">
-        <v>0.78100000000000003</v>
+        <v>0.57899999999999996</v>
       </c>
       <c r="F102" s="829">
-        <v>0.1983972</v>
+        <v>0.2651482</v>
       </c>
       <c r="G102" s="830">
-        <v>8.5956960000000002</v>
+        <v>10.74591</v>
       </c>
     </row>
     <row r="103">
@@ -17027,22 +17027,22 @@
         <v>1</v>
       </c>
       <c r="B108" s="873">
-        <v>15.3744</v>
+        <v>19.998190000000001</v>
       </c>
       <c r="C108" s="874">
-        <v>26.068850000000001</v>
+        <v>33.69294</v>
       </c>
       <c r="D108" s="875">
-        <v>1.6100000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="E108" s="876">
-        <v>0.107</v>
+        <v>0.074999999999999997</v>
       </c>
       <c r="F108" s="877">
-        <v>0.55398749999999997</v>
+        <v>0.73601620000000001</v>
       </c>
       <c r="G108" s="878">
-        <v>426.67419999999999</v>
+        <v>543.3682</v>
       </c>
     </row>
     <row r="109">
@@ -17096,22 +17096,22 @@
         <v>1</v>
       </c>
       <c r="B111" s="897">
-        <v>0.3662707</v>
+        <v>0.47235709999999998</v>
       </c>
       <c r="C111" s="898">
-        <v>0.40698889999999999</v>
+        <v>0.51732929999999999</v>
       </c>
       <c r="D111" s="899">
-        <v>-0.90000000000000002</v>
+        <v>-0.68000000000000005</v>
       </c>
       <c r="E111" s="900">
-        <v>0.36599999999999999</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="F111" s="901">
-        <v>0.041492800000000003</v>
+        <v>0.055211299999999998</v>
       </c>
       <c r="G111" s="902">
-        <v>3.2331919999999999</v>
+        <v>4.0412270000000001</v>
       </c>
     </row>
     <row r="112">
@@ -17165,22 +17165,22 @@
         <v>1</v>
       </c>
       <c r="B114" s="921">
-        <v>0.3361133</v>
+        <v>0.43328719999999998</v>
       </c>
       <c r="C114" s="922">
-        <v>1.3072429999999999</v>
+        <v>1.682042</v>
       </c>
       <c r="D114" s="923">
-        <v>-0.28000000000000003</v>
+        <v>-0.22</v>
       </c>
       <c r="E114" s="924">
-        <v>0.77900000000000003</v>
+        <v>0.82899999999999996</v>
       </c>
       <c r="F114" s="925">
-        <v>0.00016440000000000001</v>
+        <v>0.000215</v>
       </c>
       <c r="G114" s="926">
-        <v>687.15769999999998</v>
+        <v>873.33479999999997</v>
       </c>
     </row>
     <row r="115">
@@ -17211,22 +17211,22 @@
         <v>88</v>
       </c>
       <c r="B116" s="944">
-        <v>96.123270000000005</v>
+        <v>171.6</v>
       </c>
       <c r="C116" s="945">
-        <v>67.488169999999997</v>
+        <v>112.3506</v>
       </c>
       <c r="D116" s="946">
-        <v>6.5</v>
+        <v>7.8600000000000003</v>
       </c>
       <c r="E116" s="947">
         <v>0</v>
       </c>
       <c r="F116" s="948">
-        <v>24.277259999999998</v>
+        <v>47.557079999999999</v>
       </c>
       <c r="G116" s="949">
-        <v>380.58999999999998</v>
+        <v>619.18330000000003</v>
       </c>
     </row>
   </sheetData>

--- a/progression_odds_only_pdl1.xlsx
+++ b/progression_odds_only_pdl1.xlsx
@@ -14589,22 +14589,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="25">
-        <v>1.382166</v>
+        <v>1.95103</v>
       </c>
       <c r="C2" s="26">
-        <v>1.263261</v>
+        <v>0.53916050000000004</v>
       </c>
       <c r="D2" s="27">
-        <v>0.34999999999999998</v>
+        <v>2.4199999999999999</v>
       </c>
       <c r="E2" s="28">
-        <v>0.72299999999999998</v>
+        <v>0.016</v>
       </c>
       <c r="F2" s="29">
-        <v>0.23045499999999999</v>
+        <v>1.135108</v>
       </c>
       <c r="G2" s="30">
-        <v>8.2896180000000008</v>
+        <v>3.35344</v>
       </c>
     </row>
     <row r="3">
@@ -14612,22 +14612,22 @@
         <v>8</v>
       </c>
       <c r="B3" s="33">
-        <v>0.80735849999999998</v>
+        <v>1.4164969999999999</v>
       </c>
       <c r="C3" s="34">
-        <v>0.078483899999999995</v>
+        <v>0.37657069999999998</v>
       </c>
       <c r="D3" s="35">
-        <v>-2.2000000000000002</v>
+        <v>1.3100000000000001</v>
       </c>
       <c r="E3" s="36">
-        <v>0.028000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="F3" s="37">
-        <v>0.66729910000000003</v>
+        <v>0.84125360000000005</v>
       </c>
       <c r="G3" s="38">
-        <v>0.97681499999999999</v>
+        <v>2.3850889999999998</v>
       </c>
     </row>
     <row r="4">
@@ -14635,22 +14635,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="41">
-        <v>1.1661189999999999</v>
+        <v>2.0536750000000001</v>
       </c>
       <c r="C4" s="42">
-        <v>0.25204680000000002</v>
+        <v>0.6765622</v>
       </c>
       <c r="D4" s="43">
-        <v>0.70999999999999997</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="E4" s="44">
-        <v>0.47699999999999998</v>
+        <v>0.029000000000000001</v>
       </c>
       <c r="F4" s="45">
-        <v>0.76341870000000001</v>
+        <v>1.0767439999999999</v>
       </c>
       <c r="G4" s="46">
-        <v>1.781242</v>
+        <v>3.9169800000000001</v>
       </c>
     </row>
     <row r="5">
@@ -14658,22 +14658,22 @@
         <v>10</v>
       </c>
       <c r="B5" s="49">
-        <v>0.81775690000000001</v>
+        <v>1.2889120000000001</v>
       </c>
       <c r="C5" s="50">
-        <v>0.093204899999999993</v>
+        <v>0.32879140000000001</v>
       </c>
       <c r="D5" s="51">
-        <v>-1.77</v>
+        <v>0.98999999999999999</v>
       </c>
       <c r="E5" s="52">
-        <v>0.078</v>
+        <v>0.32000000000000001</v>
       </c>
       <c r="F5" s="53">
-        <v>0.65404459999999998</v>
+        <v>0.78178650000000005</v>
       </c>
       <c r="G5" s="54">
-        <v>1.0224470000000001</v>
+        <v>2.1249959999999999</v>
       </c>
     </row>
     <row r="6">
@@ -14681,22 +14681,22 @@
         <v>11</v>
       </c>
       <c r="B6" s="57">
-        <v>0.54097660000000003</v>
+        <v>1.3094539999999999</v>
       </c>
       <c r="C6" s="58">
-        <v>0.49216959999999999</v>
+        <v>0.35046290000000002</v>
       </c>
       <c r="D6" s="59">
-        <v>-0.68000000000000005</v>
+        <v>1.01</v>
       </c>
       <c r="E6" s="60">
-        <v>0.499</v>
+        <v>0.314</v>
       </c>
       <c r="F6" s="61">
-        <v>0.090943700000000002</v>
+        <v>0.77495099999999995</v>
       </c>
       <c r="G6" s="62">
-        <v>3.2179880000000001</v>
+        <v>2.2126169999999998</v>
       </c>
     </row>
     <row r="7">
@@ -14704,22 +14704,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="65">
-        <v>0.9453722</v>
+        <v>1.6326989999999999</v>
       </c>
       <c r="C7" s="66">
-        <v>0.45216279999999998</v>
+        <v>0.87593840000000001</v>
       </c>
       <c r="D7" s="67">
-        <v>-0.12</v>
+        <v>0.91000000000000003</v>
       </c>
       <c r="E7" s="68">
-        <v>0.90700000000000003</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="F7" s="69">
-        <v>0.37023800000000001</v>
+        <v>0.57047769999999998</v>
       </c>
       <c r="G7" s="70">
-        <v>2.4139300000000001</v>
+        <v>4.672758</v>
       </c>
     </row>
     <row r="8">
@@ -14750,22 +14750,22 @@
         <v>15</v>
       </c>
       <c r="B9" s="81">
-        <v>0.2238726</v>
+        <v>0.4009491</v>
       </c>
       <c r="C9" s="82">
-        <v>0.22839609999999999</v>
+        <v>0.4216895</v>
       </c>
       <c r="D9" s="83">
-        <v>-1.47</v>
+        <v>-0.87</v>
       </c>
       <c r="E9" s="84">
-        <v>0.14199999999999999</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="F9" s="85">
-        <v>0.030311000000000001</v>
+        <v>0.051033599999999999</v>
       </c>
       <c r="G9" s="86">
-        <v>1.6534899999999999</v>
+        <v>3.150083</v>
       </c>
     </row>
     <row r="10">
@@ -14773,22 +14773,22 @@
         <v>16</v>
       </c>
       <c r="B10" s="89">
-        <v>0.98913600000000002</v>
+        <v>1.739045</v>
       </c>
       <c r="C10" s="90">
-        <v>0.52160209999999996</v>
+        <v>1.013164</v>
       </c>
       <c r="D10" s="91">
-        <v>-0.02</v>
+        <v>0.94999999999999996</v>
       </c>
       <c r="E10" s="92">
-        <v>0.98299999999999999</v>
+        <v>0.34200000000000003</v>
       </c>
       <c r="F10" s="93">
-        <v>0.3518771</v>
+        <v>0.55513999999999997</v>
       </c>
       <c r="G10" s="94">
-        <v>2.7804880000000001</v>
+        <v>5.4477729999999998</v>
       </c>
     </row>
     <row r="11">
@@ -14796,22 +14796,22 @@
         <v>17</v>
       </c>
       <c r="B11" s="97">
-        <v>0.36105399999999999</v>
+        <v>0.63797990000000004</v>
       </c>
       <c r="C11" s="98">
-        <v>0.37251489999999998</v>
+        <v>0.67715590000000003</v>
       </c>
       <c r="D11" s="99">
-        <v>-0.98999999999999999</v>
+        <v>-0.41999999999999999</v>
       </c>
       <c r="E11" s="100">
-        <v>0.32300000000000001</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="F11" s="101">
-        <v>0.047791500000000001</v>
+        <v>0.079677600000000001</v>
       </c>
       <c r="G11" s="102">
-        <v>2.7276790000000002</v>
+        <v>5.1083160000000003</v>
       </c>
     </row>
     <row r="12">
@@ -14865,22 +14865,22 @@
         <v>19</v>
       </c>
       <c r="B14" s="121">
-        <v>0.54264800000000002</v>
+        <v>0.54199909999999996</v>
       </c>
       <c r="C14" s="122">
-        <v>0.1005233</v>
+        <v>0.1003496</v>
       </c>
       <c r="D14" s="123">
-        <v>-3.2999999999999998</v>
+        <v>-3.3100000000000001</v>
       </c>
       <c r="E14" s="124">
         <v>0.001</v>
       </c>
       <c r="F14" s="125">
-        <v>0.37743009999999999</v>
+        <v>0.37705169999999999</v>
       </c>
       <c r="G14" s="126">
-        <v>0.78018900000000002</v>
+        <v>0.7791053</v>
       </c>
     </row>
     <row r="15">
@@ -14888,22 +14888,22 @@
         <v>20</v>
       </c>
       <c r="B15" s="129">
-        <v>1.5850839999999999</v>
+        <v>2.7959610000000001</v>
       </c>
       <c r="C15" s="130">
-        <v>1.8509329999999999</v>
+        <v>3.3364910000000001</v>
       </c>
       <c r="D15" s="131">
-        <v>0.39000000000000001</v>
+        <v>0.85999999999999999</v>
       </c>
       <c r="E15" s="132">
-        <v>0.69299999999999995</v>
+        <v>0.38900000000000001</v>
       </c>
       <c r="F15" s="133">
-        <v>0.1607267</v>
+        <v>0.26963179999999998</v>
       </c>
       <c r="G15" s="134">
-        <v>15.63208</v>
+        <v>28.99287</v>
       </c>
     </row>
     <row r="16">
@@ -14911,22 +14911,22 @@
         <v>21</v>
       </c>
       <c r="B16" s="137">
-        <v>0.23096449999999999</v>
+        <v>0.39306029999999997</v>
       </c>
       <c r="C16" s="138">
-        <v>0.056233400000000003</v>
+        <v>0.13349440000000001</v>
       </c>
       <c r="D16" s="139">
-        <v>-6.0199999999999996</v>
+        <v>-2.75</v>
       </c>
       <c r="E16" s="140">
-        <v>0</v>
+        <v>0.0060000000000000001</v>
       </c>
       <c r="F16" s="141">
-        <v>0.14331830000000001</v>
+        <v>0.2020073</v>
       </c>
       <c r="G16" s="142">
-        <v>0.37221080000000001</v>
+        <v>0.76480610000000004</v>
       </c>
     </row>
     <row r="17">
@@ -14980,22 +14980,22 @@
         <v>19</v>
       </c>
       <c r="B19" s="161">
-        <v>0.91699489999999995</v>
+        <v>0.92039289999999996</v>
       </c>
       <c r="C19" s="162">
-        <v>0.087200299999999995</v>
+        <v>0.0875388</v>
       </c>
       <c r="D19" s="163">
-        <v>-0.91000000000000003</v>
+        <v>-0.87</v>
       </c>
       <c r="E19" s="164">
-        <v>0.36199999999999999</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="F19" s="165">
-        <v>0.76106739999999995</v>
+        <v>0.76386259999999995</v>
       </c>
       <c r="G19" s="166">
-        <v>1.1048690000000001</v>
+        <v>1.1089990000000001</v>
       </c>
     </row>
     <row r="20">
@@ -15003,22 +15003,22 @@
         <v>20</v>
       </c>
       <c r="B20" s="169">
-        <v>1.3639600000000001</v>
+        <v>2.3840219999999999</v>
       </c>
       <c r="C20" s="170">
-        <v>0.4448011</v>
+        <v>0.97508399999999995</v>
       </c>
       <c r="D20" s="171">
-        <v>0.94999999999999996</v>
+        <v>2.1200000000000001</v>
       </c>
       <c r="E20" s="172">
-        <v>0.34100000000000003</v>
+        <v>0.034000000000000002</v>
       </c>
       <c r="F20" s="173">
-        <v>0.71980739999999999</v>
+        <v>1.0694539999999999</v>
       </c>
       <c r="G20" s="174">
-        <v>2.5845630000000002</v>
+        <v>5.3144520000000002</v>
       </c>
     </row>
     <row r="21">
@@ -15026,22 +15026,22 @@
         <v>21</v>
       </c>
       <c r="B21" s="177">
-        <v>0.3089806</v>
+        <v>0.53668380000000005</v>
       </c>
       <c r="C21" s="178">
-        <v>0.033144399999999998</v>
+        <v>0.14266029999999999</v>
       </c>
       <c r="D21" s="179">
-        <v>-10.949999999999999</v>
+        <v>-2.3399999999999999</v>
       </c>
       <c r="E21" s="180">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="F21" s="181">
-        <v>0.25039329999999999</v>
+        <v>0.3187526</v>
       </c>
       <c r="G21" s="182">
-        <v>0.38127630000000001</v>
+        <v>0.90361469999999999</v>
       </c>
     </row>
     <row r="22">
@@ -15095,22 +15095,22 @@
         <v>19</v>
       </c>
       <c r="B24" s="201">
-        <v>0.98608200000000001</v>
+        <v>0.99318770000000001</v>
       </c>
       <c r="C24" s="202">
-        <v>0.2765571</v>
+        <v>0.27861570000000002</v>
       </c>
       <c r="D24" s="203">
-        <v>-0.050000000000000003</v>
+        <v>-0.02</v>
       </c>
       <c r="E24" s="204">
-        <v>0.95999999999999997</v>
+        <v>0.98099999999999998</v>
       </c>
       <c r="F24" s="205">
-        <v>0.56909480000000001</v>
+        <v>0.5731214</v>
       </c>
       <c r="G24" s="206">
-        <v>1.708604</v>
+        <v>1.7211399999999999</v>
       </c>
     </row>
     <row r="25">
@@ -15118,22 +15118,22 @@
         <v>20</v>
       </c>
       <c r="B25" s="209">
-        <v>1.0772200000000001</v>
+        <v>1.844848</v>
       </c>
       <c r="C25" s="210">
-        <v>0.34881190000000001</v>
+        <v>0.73904119999999995</v>
       </c>
       <c r="D25" s="211">
-        <v>0.23000000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="E25" s="212">
-        <v>0.81799999999999995</v>
+        <v>0.126</v>
       </c>
       <c r="F25" s="213">
-        <v>0.57105680000000003</v>
+        <v>0.84134030000000004</v>
       </c>
       <c r="G25" s="214">
-        <v>2.0320290000000001</v>
+        <v>4.0452899999999996</v>
       </c>
     </row>
     <row r="26">
@@ -15141,22 +15141,22 @@
         <v>21</v>
       </c>
       <c r="B26" s="217">
-        <v>0.48528159999999998</v>
+        <v>0.85454399999999997</v>
       </c>
       <c r="C26" s="218">
-        <v>0.18200669999999999</v>
+        <v>0.3854108</v>
       </c>
       <c r="D26" s="219">
-        <v>-1.9299999999999999</v>
+        <v>-0.34999999999999998</v>
       </c>
       <c r="E26" s="220">
-        <v>0.053999999999999999</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="F26" s="221">
-        <v>0.23267379999999999</v>
+        <v>0.35304580000000002</v>
       </c>
       <c r="G26" s="222">
-        <v>1.0121389999999999</v>
+        <v>2.0684149999999999</v>
       </c>
     </row>
     <row r="27">
@@ -15187,22 +15187,22 @@
         <v>24</v>
       </c>
       <c r="B28" s="233">
-        <v>0.92869219999999997</v>
+        <v>0.92954309999999996</v>
       </c>
       <c r="C28" s="234">
-        <v>0.091844200000000001</v>
+        <v>0.091952099999999995</v>
       </c>
       <c r="D28" s="235">
-        <v>-0.75</v>
+        <v>-0.73999999999999999</v>
       </c>
       <c r="E28" s="236">
-        <v>0.45400000000000001</v>
+        <v>0.46000000000000002</v>
       </c>
       <c r="F28" s="237">
-        <v>0.76505230000000002</v>
+        <v>0.76571489999999998</v>
       </c>
       <c r="G28" s="238">
-        <v>1.1273340000000001</v>
+        <v>1.128423</v>
       </c>
     </row>
     <row r="29">
@@ -15210,22 +15210,22 @@
         <v>25</v>
       </c>
       <c r="B29" s="241">
-        <v>1.1205909999999999</v>
+        <v>1.120093</v>
       </c>
       <c r="C29" s="242">
-        <v>0.0595877</v>
+        <v>0.059580500000000002</v>
       </c>
       <c r="D29" s="243">
-        <v>2.1400000000000001</v>
+        <v>2.1299999999999999</v>
       </c>
       <c r="E29" s="244">
-        <v>0.032000000000000001</v>
+        <v>0.033000000000000002</v>
       </c>
       <c r="F29" s="245">
-        <v>1.009682</v>
+        <v>1.009199</v>
       </c>
       <c r="G29" s="246">
-        <v>1.243684</v>
+        <v>1.2431730000000001</v>
       </c>
     </row>
     <row r="30">
@@ -15233,22 +15233,22 @@
         <v>26</v>
       </c>
       <c r="B30" s="249">
-        <v>0.55215820000000004</v>
+        <v>0.55220499999999995</v>
       </c>
       <c r="C30" s="250">
-        <v>0.0399932</v>
+        <v>0.040018499999999999</v>
       </c>
       <c r="D30" s="251">
-        <v>-8.1999999999999993</v>
+        <v>-8.1899999999999995</v>
       </c>
       <c r="E30" s="252">
         <v>0</v>
       </c>
       <c r="F30" s="253">
-        <v>0.47908260000000003</v>
+        <v>0.47908590000000001</v>
       </c>
       <c r="G30" s="254">
-        <v>0.63638019999999995</v>
+        <v>0.63648369999999999</v>
       </c>
     </row>
     <row r="31">
@@ -15256,22 +15256,22 @@
         <v>27</v>
       </c>
       <c r="B31" s="257">
-        <v>0.83079329999999996</v>
+        <v>0.8283239</v>
       </c>
       <c r="C31" s="258">
-        <v>0.054820599999999997</v>
+        <v>0.054681899999999999</v>
       </c>
       <c r="D31" s="259">
-        <v>-2.8100000000000001</v>
+        <v>-2.8500000000000001</v>
       </c>
       <c r="E31" s="260">
-        <v>0.0050000000000000001</v>
+        <v>0.0040000000000000001</v>
       </c>
       <c r="F31" s="261">
-        <v>0.73000489999999996</v>
+        <v>0.72779320000000003</v>
       </c>
       <c r="G31" s="262">
-        <v>0.94549720000000004</v>
+        <v>0.9427411</v>
       </c>
     </row>
     <row r="32">
@@ -15279,22 +15279,22 @@
         <v>28</v>
       </c>
       <c r="B32" s="265">
-        <v>1.24654</v>
+        <v>1.2435970000000001</v>
       </c>
       <c r="C32" s="266">
-        <v>0.090324100000000004</v>
+        <v>0.090160000000000004</v>
       </c>
       <c r="D32" s="267">
-        <v>3.04</v>
+        <v>3.0099999999999998</v>
       </c>
       <c r="E32" s="268">
-        <v>0.002</v>
+        <v>0.0030000000000000001</v>
       </c>
       <c r="F32" s="269">
-        <v>1.081504</v>
+        <v>1.078867</v>
       </c>
       <c r="G32" s="270">
-        <v>1.4367589999999999</v>
+        <v>1.433478</v>
       </c>
     </row>
     <row r="33">
@@ -15302,22 +15302,22 @@
         <v>29</v>
       </c>
       <c r="B33" s="273">
-        <v>1.7720100000000001</v>
+        <v>1.7659419999999999</v>
       </c>
       <c r="C33" s="274">
-        <v>0.14898049999999999</v>
+        <v>0.1485541</v>
       </c>
       <c r="D33" s="275">
-        <v>6.7999999999999998</v>
+        <v>6.7599999999999998</v>
       </c>
       <c r="E33" s="276">
         <v>0</v>
       </c>
       <c r="F33" s="277">
-        <v>1.502802</v>
+        <v>1.4975179999999999</v>
       </c>
       <c r="G33" s="278">
-        <v>2.089442</v>
+        <v>2.082481</v>
       </c>
     </row>
     <row r="34">
@@ -15325,22 +15325,22 @@
         <v>30</v>
       </c>
       <c r="B34" s="281">
-        <v>2.0435569999999999</v>
+        <v>2.0145599999999999</v>
       </c>
       <c r="C34" s="282">
-        <v>0.37689070000000002</v>
+        <v>0.37138139999999997</v>
       </c>
       <c r="D34" s="283">
-        <v>3.8799999999999999</v>
+        <v>3.7999999999999998</v>
       </c>
       <c r="E34" s="284">
         <v>0</v>
       </c>
       <c r="F34" s="285">
-        <v>1.4236420000000001</v>
+        <v>1.403662</v>
       </c>
       <c r="G34" s="286">
-        <v>2.9334099999999999</v>
+        <v>2.8913329999999999</v>
       </c>
     </row>
     <row r="35">
@@ -15348,22 +15348,22 @@
         <v>31</v>
       </c>
       <c r="B35" s="289">
-        <v>0.92847939999999996</v>
+        <v>0.92437480000000005</v>
       </c>
       <c r="C35" s="290">
-        <v>0.1064005</v>
+        <v>0.1059585</v>
       </c>
       <c r="D35" s="291">
-        <v>-0.65000000000000002</v>
+        <v>-0.68999999999999995</v>
       </c>
       <c r="E35" s="292">
-        <v>0.51700000000000002</v>
+        <v>0.49299999999999999</v>
       </c>
       <c r="F35" s="293">
-        <v>0.74169879999999999</v>
+        <v>0.73837540000000002</v>
       </c>
       <c r="G35" s="294">
-        <v>1.1622969999999999</v>
+        <v>1.1572279999999999</v>
       </c>
     </row>
     <row r="36">
@@ -15371,22 +15371,22 @@
         <v>32</v>
       </c>
       <c r="B36" s="297">
-        <v>0.74097690000000005</v>
+        <v>0.74031279999999999</v>
       </c>
       <c r="C36" s="298">
-        <v>0.080496899999999996</v>
+        <v>0.080440999999999999</v>
       </c>
       <c r="D36" s="299">
-        <v>-2.7599999999999998</v>
+        <v>-2.77</v>
       </c>
       <c r="E36" s="300">
         <v>0.0060000000000000001</v>
       </c>
       <c r="F36" s="301">
-        <v>0.59887120000000005</v>
+        <v>0.59830859999999997</v>
       </c>
       <c r="G36" s="302">
-        <v>0.91680289999999998</v>
+        <v>0.91602059999999996</v>
       </c>
     </row>
     <row r="37">
@@ -15394,22 +15394,22 @@
         <v>33</v>
       </c>
       <c r="B37" s="305">
-        <v>0.3597784</v>
+        <v>0.46468860000000001</v>
       </c>
       <c r="C37" s="306">
-        <v>0.038785800000000002</v>
+        <v>0.1008443</v>
       </c>
       <c r="D37" s="307">
-        <v>-9.4800000000000004</v>
+        <v>-3.5299999999999998</v>
       </c>
       <c r="E37" s="308">
         <v>0</v>
       </c>
       <c r="F37" s="309">
-        <v>0.29125380000000001</v>
+        <v>0.30369570000000001</v>
       </c>
       <c r="G37" s="310">
-        <v>0.44442510000000002</v>
+        <v>0.71102569999999998</v>
       </c>
     </row>
     <row r="38">
@@ -15417,22 +15417,22 @@
         <v>34</v>
       </c>
       <c r="B38" s="313">
-        <v>0.86714659999999999</v>
+        <v>0.86745280000000002</v>
       </c>
       <c r="C38" s="314">
-        <v>0.094197199999999995</v>
+        <v>0.094178399999999996</v>
       </c>
       <c r="D38" s="315">
         <v>-1.3100000000000001</v>
       </c>
       <c r="E38" s="316">
-        <v>0.189</v>
+        <v>0.19</v>
       </c>
       <c r="F38" s="317">
-        <v>0.70085379999999997</v>
+        <v>0.70118369999999997</v>
       </c>
       <c r="G38" s="318">
-        <v>1.0728960000000001</v>
+        <v>1.0731489999999999</v>
       </c>
     </row>
     <row r="39">
@@ -15440,22 +15440,22 @@
         <v>35</v>
       </c>
       <c r="B39" s="321">
-        <v>0.87149569999999999</v>
+        <v>0.8724073</v>
       </c>
       <c r="C39" s="322">
-        <v>0.0111234</v>
+        <v>0.011143399999999999</v>
       </c>
       <c r="D39" s="323">
-        <v>-10.779999999999999</v>
+        <v>-10.69</v>
       </c>
       <c r="E39" s="324">
         <v>0</v>
       </c>
       <c r="F39" s="325">
-        <v>0.84996470000000002</v>
+        <v>0.85083759999999997</v>
       </c>
       <c r="G39" s="326">
-        <v>0.89357200000000003</v>
+        <v>0.89452370000000003</v>
       </c>
     </row>
     <row r="40">
@@ -15463,22 +15463,22 @@
         <v>36</v>
       </c>
       <c r="B40" s="329">
-        <v>0.52396120000000002</v>
+        <v>0.52355189999999996</v>
       </c>
       <c r="C40" s="330">
-        <v>0.074733300000000003</v>
+        <v>0.074685000000000001</v>
       </c>
       <c r="D40" s="331">
-        <v>-4.5300000000000002</v>
+        <v>-4.54</v>
       </c>
       <c r="E40" s="332">
         <v>0</v>
       </c>
       <c r="F40" s="333">
-        <v>0.3961787</v>
+        <v>0.39585429999999999</v>
       </c>
       <c r="G40" s="334">
-        <v>0.69295839999999998</v>
+        <v>0.69244320000000004</v>
       </c>
     </row>
     <row r="41">
@@ -15486,22 +15486,22 @@
         <v>37</v>
       </c>
       <c r="B41" s="337">
-        <v>0.83459309999999998</v>
+        <v>0.83361940000000001</v>
       </c>
       <c r="C41" s="338">
-        <v>0.058200700000000001</v>
+        <v>0.058167999999999998</v>
       </c>
       <c r="D41" s="339">
-        <v>-2.5899999999999999</v>
+        <v>-2.6099999999999999</v>
       </c>
       <c r="E41" s="340">
-        <v>0.01</v>
+        <v>0.0089999999999999993</v>
       </c>
       <c r="F41" s="341">
-        <v>0.72797400000000001</v>
+        <v>0.7270645</v>
       </c>
       <c r="G41" s="342">
-        <v>0.9568276</v>
+        <v>0.95579049999999999</v>
       </c>
     </row>
     <row r="42">
@@ -15509,22 +15509,22 @@
         <v>38</v>
       </c>
       <c r="B42" s="345">
-        <v>0.79076880000000005</v>
+        <v>0.78871279999999999</v>
       </c>
       <c r="C42" s="346">
-        <v>0.1002459</v>
+        <v>0.1000423</v>
       </c>
       <c r="D42" s="347">
-        <v>-1.8500000000000001</v>
+        <v>-1.8700000000000001</v>
       </c>
       <c r="E42" s="348">
-        <v>0.064000000000000001</v>
+        <v>0.060999999999999999</v>
       </c>
       <c r="F42" s="349">
-        <v>0.6167975</v>
+        <v>0.61510659999999995</v>
       </c>
       <c r="G42" s="350">
-        <v>1.0138100000000001</v>
+        <v>1.011317</v>
       </c>
     </row>
     <row r="43">
@@ -15532,22 +15532,22 @@
         <v>39</v>
       </c>
       <c r="B43" s="353">
-        <v>0.74163869999999999</v>
+        <v>0.74126910000000001</v>
       </c>
       <c r="C43" s="354">
-        <v>0.068152199999999996</v>
+        <v>0.068133899999999997</v>
       </c>
       <c r="D43" s="355">
-        <v>-3.25</v>
+        <v>-3.2599999999999998</v>
       </c>
       <c r="E43" s="356">
         <v>0.001</v>
       </c>
       <c r="F43" s="357">
-        <v>0.61940110000000004</v>
+        <v>0.61906680000000003</v>
       </c>
       <c r="G43" s="358">
-        <v>0.8879996</v>
+        <v>0.88759390000000005</v>
       </c>
     </row>
     <row r="44">
@@ -15555,22 +15555,22 @@
         <v>40</v>
       </c>
       <c r="B44" s="361">
-        <v>0.97441639999999996</v>
+        <v>0.97204000000000002</v>
       </c>
       <c r="C44" s="362">
-        <v>0.088131500000000002</v>
+        <v>0.087967000000000004</v>
       </c>
       <c r="D44" s="363">
-        <v>-0.28999999999999998</v>
+        <v>-0.31</v>
       </c>
       <c r="E44" s="364">
-        <v>0.77400000000000002</v>
+        <v>0.754</v>
       </c>
       <c r="F44" s="365">
-        <v>0.81612620000000002</v>
+        <v>0.81405300000000003</v>
       </c>
       <c r="G44" s="366">
-        <v>1.1634070000000001</v>
+        <v>1.160688</v>
       </c>
     </row>
     <row r="45">
@@ -15578,22 +15578,22 @@
         <v>41</v>
       </c>
       <c r="B45" s="369">
-        <v>0.91880759999999995</v>
+        <v>0.92738969999999998</v>
       </c>
       <c r="C45" s="370">
-        <v>0.53262620000000005</v>
+        <v>0.53840969999999999</v>
       </c>
       <c r="D45" s="371">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="E45" s="372">
-        <v>0.88400000000000001</v>
+        <v>0.89700000000000002</v>
       </c>
       <c r="F45" s="373">
-        <v>0.29497760000000001</v>
+        <v>0.29722460000000001</v>
       </c>
       <c r="G45" s="374">
-        <v>2.8619370000000002</v>
+        <v>2.8936090000000001</v>
       </c>
     </row>
     <row r="46">
@@ -15601,22 +15601,22 @@
         <v>42</v>
       </c>
       <c r="B46" s="377">
-        <v>1.09328</v>
+        <v>1.094854</v>
       </c>
       <c r="C46" s="378">
-        <v>0.043152799999999998</v>
+        <v>0.043226000000000001</v>
       </c>
       <c r="D46" s="379">
-        <v>2.2599999999999998</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E46" s="380">
-        <v>0.024</v>
+        <v>0.021999999999999999</v>
       </c>
       <c r="F46" s="381">
-        <v>1.0118910000000001</v>
+        <v>1.013328</v>
       </c>
       <c r="G46" s="382">
-        <v>1.1812149999999999</v>
+        <v>1.1829400000000001</v>
       </c>
     </row>
     <row r="47">
@@ -15624,22 +15624,22 @@
         <v>43</v>
       </c>
       <c r="B47" s="385">
-        <v>0.95077999999999996</v>
+        <v>0.95155009999999996</v>
       </c>
       <c r="C47" s="386">
-        <v>0.024815299999999999</v>
+        <v>0.0248541</v>
       </c>
       <c r="D47" s="387">
-        <v>-1.9299999999999999</v>
+        <v>-1.8999999999999999</v>
       </c>
       <c r="E47" s="388">
-        <v>0.052999999999999999</v>
+        <v>0.057000000000000002</v>
       </c>
       <c r="F47" s="389">
-        <v>0.903366</v>
+        <v>0.9040629</v>
       </c>
       <c r="G47" s="390">
-        <v>1.000683</v>
+        <v>1.0015320000000001</v>
       </c>
     </row>
     <row r="48">
@@ -15647,22 +15647,22 @@
         <v>44</v>
       </c>
       <c r="B48" s="393">
-        <v>0.80775810000000003</v>
+        <v>0.80558909999999995</v>
       </c>
       <c r="C48" s="394">
-        <v>0.045404100000000003</v>
+        <v>0.045275200000000002</v>
       </c>
       <c r="D48" s="395">
-        <v>-3.7999999999999998</v>
+        <v>-3.8500000000000001</v>
       </c>
       <c r="E48" s="396">
         <v>0</v>
       </c>
       <c r="F48" s="397">
-        <v>0.72349450000000004</v>
+        <v>0.72156419999999999</v>
       </c>
       <c r="G48" s="398">
-        <v>0.90183570000000002</v>
+        <v>0.8993987</v>
       </c>
     </row>
     <row r="49">
@@ -15670,22 +15670,22 @@
         <v>45</v>
       </c>
       <c r="B49" s="401">
-        <v>0.93145319999999998</v>
+        <v>0.92934450000000002</v>
       </c>
       <c r="C49" s="402">
-        <v>0.074876799999999993</v>
+        <v>0.074740200000000007</v>
       </c>
       <c r="D49" s="403">
-        <v>-0.88</v>
+        <v>-0.91000000000000003</v>
       </c>
       <c r="E49" s="404">
-        <v>0.377</v>
+        <v>0.36199999999999999</v>
       </c>
       <c r="F49" s="405">
-        <v>0.7956744</v>
+        <v>0.79381809999999997</v>
       </c>
       <c r="G49" s="406">
-        <v>1.0904020000000001</v>
+        <v>1.088009</v>
       </c>
     </row>
     <row r="50">
@@ -15693,22 +15693,22 @@
         <v>46</v>
       </c>
       <c r="B50" s="409">
-        <v>0.89851619999999999</v>
+        <v>0.89705299999999999</v>
       </c>
       <c r="C50" s="410">
-        <v>0.037957100000000001</v>
+        <v>0.037905599999999998</v>
       </c>
       <c r="D50" s="411">
-        <v>-2.5299999999999998</v>
+        <v>-2.5699999999999999</v>
       </c>
       <c r="E50" s="412">
-        <v>0.010999999999999999</v>
+        <v>0.01</v>
       </c>
       <c r="F50" s="413">
-        <v>0.82711820000000003</v>
+        <v>0.82575259999999995</v>
       </c>
       <c r="G50" s="414">
-        <v>0.97607750000000004</v>
+        <v>0.97450979999999998</v>
       </c>
     </row>
     <row r="51">
@@ -15716,22 +15716,22 @@
         <v>47</v>
       </c>
       <c r="B51" s="417">
-        <v>0.88780550000000003</v>
+        <v>0.88480959999999997</v>
       </c>
       <c r="C51" s="418">
-        <v>0.084552299999999997</v>
+        <v>0.0841084</v>
       </c>
       <c r="D51" s="419">
-        <v>-1.25</v>
+        <v>-1.29</v>
       </c>
       <c r="E51" s="420">
-        <v>0.21099999999999999</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="F51" s="421">
-        <v>0.73663380000000001</v>
+        <v>0.73440589999999995</v>
       </c>
       <c r="G51" s="422">
-        <v>1.070001</v>
+        <v>1.0660149999999999</v>
       </c>
     </row>
     <row r="52">
@@ -15739,22 +15739,22 @@
         <v>48</v>
       </c>
       <c r="B52" s="425">
-        <v>0.8619272</v>
+        <v>0.86274779999999995</v>
       </c>
       <c r="C52" s="426">
-        <v>0.067169300000000001</v>
+        <v>0.067236299999999999</v>
       </c>
       <c r="D52" s="427">
-        <v>-1.9099999999999999</v>
+        <v>-1.8899999999999999</v>
       </c>
       <c r="E52" s="428">
-        <v>0.057000000000000002</v>
+        <v>0.058000000000000003</v>
       </c>
       <c r="F52" s="429">
-        <v>0.73983889999999997</v>
+        <v>0.74053809999999998</v>
       </c>
       <c r="G52" s="430">
-        <v>1.0041629999999999</v>
+        <v>1.005126</v>
       </c>
     </row>
     <row r="53">
@@ -15762,22 +15762,22 @@
         <v>49</v>
       </c>
       <c r="B53" s="433">
-        <v>0.95759669999999997</v>
+        <v>0.95653290000000002</v>
       </c>
       <c r="C53" s="434">
-        <v>0.038366900000000002</v>
+        <v>0.038327100000000003</v>
       </c>
       <c r="D53" s="435">
-        <v>-1.0800000000000001</v>
+        <v>-1.1100000000000001</v>
       </c>
       <c r="E53" s="436">
-        <v>0.28000000000000003</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="F53" s="437">
-        <v>0.8852757</v>
+        <v>0.88428720000000005</v>
       </c>
       <c r="G53" s="438">
-        <v>1.0358259999999999</v>
+        <v>1.034681</v>
       </c>
     </row>
     <row r="54">
@@ -15785,10 +15785,10 @@
         <v>50</v>
       </c>
       <c r="B54" s="441">
-        <v>0.86605540000000003</v>
+        <v>0.86602460000000003</v>
       </c>
       <c r="C54" s="442">
-        <v>0.035968399999999998</v>
+        <v>0.035971000000000003</v>
       </c>
       <c r="D54" s="443">
         <v>-3.46</v>
@@ -15797,10 +15797,10 @@
         <v>0.001</v>
       </c>
       <c r="F54" s="445">
-        <v>0.79835160000000005</v>
+        <v>0.79831620000000003</v>
       </c>
       <c r="G54" s="446">
-        <v>0.93950080000000002</v>
+        <v>0.93947570000000002</v>
       </c>
     </row>
     <row r="55">
@@ -15831,22 +15831,22 @@
         <v>52</v>
       </c>
       <c r="B56" s="457">
-        <v>0.70402019999999999</v>
+        <v>0.70654819999999996</v>
       </c>
       <c r="C56" s="458">
-        <v>0.1202532</v>
+        <v>0.1207954</v>
       </c>
       <c r="D56" s="459">
-        <v>-2.0499999999999998</v>
+        <v>-2.0299999999999998</v>
       </c>
       <c r="E56" s="460">
-        <v>0.040000000000000001</v>
+        <v>0.042000000000000003</v>
       </c>
       <c r="F56" s="461">
-        <v>0.50372329999999999</v>
+        <v>0.50537730000000003</v>
       </c>
       <c r="G56" s="462">
-        <v>0.9839618</v>
+        <v>0.98779740000000005</v>
       </c>
     </row>
     <row r="57">
@@ -15854,22 +15854,22 @@
         <v>53</v>
       </c>
       <c r="B57" s="465">
-        <v>0.9005706</v>
+        <v>0.90027869999999999</v>
       </c>
       <c r="C57" s="466">
-        <v>0.1619062</v>
+        <v>0.1620393</v>
       </c>
       <c r="D57" s="467">
         <v>-0.57999999999999996</v>
       </c>
       <c r="E57" s="468">
-        <v>0.56000000000000005</v>
+        <v>0.55900000000000005</v>
       </c>
       <c r="F57" s="469">
-        <v>0.63312170000000001</v>
+        <v>0.63266089999999997</v>
       </c>
       <c r="G57" s="470">
-        <v>1.2809980000000001</v>
+        <v>1.2810999999999999</v>
       </c>
     </row>
     <row r="58">
@@ -15877,22 +15877,22 @@
         <v>54</v>
       </c>
       <c r="B58" s="473">
-        <v>0.71731509999999998</v>
+        <v>0.72033000000000003</v>
       </c>
       <c r="C58" s="474">
-        <v>0.1180537</v>
+        <v>0.1186745</v>
       </c>
       <c r="D58" s="475">
-        <v>-2.02</v>
+        <v>-1.99</v>
       </c>
       <c r="E58" s="476">
-        <v>0.043999999999999998</v>
+        <v>0.045999999999999999</v>
       </c>
       <c r="F58" s="477">
-        <v>0.51954310000000004</v>
+        <v>0.52154990000000001</v>
       </c>
       <c r="G58" s="478">
-        <v>0.99037200000000003</v>
+        <v>0.99487190000000003</v>
       </c>
     </row>
     <row r="59">
@@ -15900,22 +15900,22 @@
         <v>55</v>
       </c>
       <c r="B59" s="481">
-        <v>1.120144</v>
+        <v>1.1285829999999999</v>
       </c>
       <c r="C59" s="482">
-        <v>0.18025079999999999</v>
+        <v>0.18179699999999999</v>
       </c>
       <c r="D59" s="483">
-        <v>0.70999999999999997</v>
+        <v>0.75</v>
       </c>
       <c r="E59" s="484">
-        <v>0.48099999999999998</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="F59" s="485">
-        <v>0.81714750000000003</v>
+        <v>0.82303459999999995</v>
       </c>
       <c r="G59" s="486">
-        <v>1.53549</v>
+        <v>1.5475639999999999</v>
       </c>
     </row>
     <row r="60">
@@ -15946,22 +15946,22 @@
         <v>57</v>
       </c>
       <c r="B61" s="497">
-        <v>0.95467409999999997</v>
+        <v>0.95548180000000005</v>
       </c>
       <c r="C61" s="498">
-        <v>0.0581939</v>
+        <v>0.0582412</v>
       </c>
       <c r="D61" s="499">
-        <v>-0.76000000000000001</v>
+        <v>-0.75</v>
       </c>
       <c r="E61" s="500">
-        <v>0.44700000000000001</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="F61" s="501">
-        <v>0.84716610000000003</v>
+        <v>0.84788629999999998</v>
       </c>
       <c r="G61" s="502">
-        <v>1.075825</v>
+        <v>1.0767310000000001</v>
       </c>
     </row>
     <row r="62">
@@ -15969,22 +15969,22 @@
         <v>58</v>
       </c>
       <c r="B62" s="505">
-        <v>1.017576</v>
+        <v>1.02119</v>
       </c>
       <c r="C62" s="506">
-        <v>0.077511399999999994</v>
+        <v>0.077821799999999997</v>
       </c>
       <c r="D62" s="507">
-        <v>0.23000000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E62" s="508">
-        <v>0.81899999999999995</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="F62" s="509">
-        <v>0.87645329999999999</v>
+        <v>0.87950640000000002</v>
       </c>
       <c r="G62" s="510">
-        <v>1.181422</v>
+        <v>1.1856979999999999</v>
       </c>
     </row>
     <row r="63">
@@ -15992,22 +15992,22 @@
         <v>59</v>
       </c>
       <c r="B63" s="513">
-        <v>0.91354270000000004</v>
+        <v>0.90837299999999999</v>
       </c>
       <c r="C63" s="514">
-        <v>0.053155500000000001</v>
+        <v>0.052869399999999997</v>
       </c>
       <c r="D63" s="515">
-        <v>-1.55</v>
+        <v>-1.6499999999999999</v>
       </c>
       <c r="E63" s="516">
-        <v>0.12</v>
+        <v>0.099000000000000005</v>
       </c>
       <c r="F63" s="517">
-        <v>0.8150809</v>
+        <v>0.81044260000000001</v>
       </c>
       <c r="G63" s="518">
-        <v>1.0238989999999999</v>
+        <v>1.0181370000000001</v>
       </c>
     </row>
     <row r="64">
@@ -16015,22 +16015,22 @@
         <v>60</v>
       </c>
       <c r="B64" s="521">
-        <v>1.418258</v>
+        <v>1.4199459999999999</v>
       </c>
       <c r="C64" s="522">
-        <v>0.20303679999999999</v>
+        <v>0.2033818</v>
       </c>
       <c r="D64" s="523">
-        <v>2.44</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="E64" s="524">
-        <v>0.014999999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="F64" s="525">
-        <v>1.071267</v>
+        <v>1.072389</v>
       </c>
       <c r="G64" s="526">
-        <v>1.8776409999999999</v>
+        <v>1.880144</v>
       </c>
     </row>
     <row r="65">
@@ -16038,22 +16038,22 @@
         <v>61</v>
       </c>
       <c r="B65" s="529">
-        <v>1.521037</v>
+        <v>1.5297449999999999</v>
       </c>
       <c r="C65" s="530">
-        <v>0.32207029999999998</v>
+        <v>0.32426319999999997</v>
       </c>
       <c r="D65" s="531">
-        <v>1.98</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="E65" s="532">
-        <v>0.048000000000000001</v>
+        <v>0.044999999999999998</v>
       </c>
       <c r="F65" s="533">
-        <v>1.004391</v>
+        <v>1.00969</v>
       </c>
       <c r="G65" s="534">
-        <v>2.3034379999999999</v>
+        <v>2.3176610000000002</v>
       </c>
     </row>
     <row r="66">
@@ -16061,22 +16061,22 @@
         <v>62</v>
       </c>
       <c r="B66" s="537">
-        <v>0.37219269999999999</v>
+        <v>0.37475249999999999</v>
       </c>
       <c r="C66" s="538">
-        <v>0.57274250000000004</v>
+        <v>0.57707169999999997</v>
       </c>
       <c r="D66" s="539">
         <v>-0.64000000000000001</v>
       </c>
       <c r="E66" s="540">
-        <v>0.52100000000000002</v>
+        <v>0.52400000000000002</v>
       </c>
       <c r="F66" s="541">
-        <v>0.0182352</v>
+        <v>0.018323200000000001</v>
       </c>
       <c r="G66" s="542">
-        <v>7.5967039999999999</v>
+        <v>7.664568</v>
       </c>
     </row>
     <row r="67">
@@ -16084,22 +16084,22 @@
         <v>63</v>
       </c>
       <c r="B67" s="545">
-        <v>0.99830490000000005</v>
+        <v>0.99886249999999999</v>
       </c>
       <c r="C67" s="546">
-        <v>0.0862145</v>
+        <v>0.086314500000000002</v>
       </c>
       <c r="D67" s="547">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="E67" s="548">
-        <v>0.98399999999999999</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="F67" s="549">
-        <v>0.84285449999999995</v>
+        <v>0.84323959999999998</v>
       </c>
       <c r="G67" s="550">
-        <v>1.1824250000000001</v>
+        <v>1.183206</v>
       </c>
     </row>
     <row r="68">
@@ -16107,22 +16107,22 @@
         <v>64</v>
       </c>
       <c r="B68" s="553">
-        <v>1.206191</v>
+        <v>1.205918</v>
       </c>
       <c r="C68" s="554">
-        <v>0.1208519</v>
+        <v>0.1208795</v>
       </c>
       <c r="D68" s="555">
         <v>1.8700000000000001</v>
       </c>
       <c r="E68" s="556">
-        <v>0.060999999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="F68" s="557">
-        <v>0.99113280000000004</v>
+        <v>0.99081969999999997</v>
       </c>
       <c r="G68" s="558">
-        <v>1.467914</v>
+        <v>1.467713</v>
       </c>
     </row>
     <row r="69">
@@ -16130,22 +16130,22 @@
         <v>65</v>
       </c>
       <c r="B69" s="561">
-        <v>1.285177</v>
+        <v>1.2827390000000001</v>
       </c>
       <c r="C69" s="562">
-        <v>0.16743810000000001</v>
+        <v>0.16728090000000001</v>
       </c>
       <c r="D69" s="563">
-        <v>1.9299999999999999</v>
+        <v>1.9099999999999999</v>
       </c>
       <c r="E69" s="564">
-        <v>0.053999999999999999</v>
+        <v>0.056000000000000001</v>
       </c>
       <c r="F69" s="565">
-        <v>0.99555439999999995</v>
+        <v>0.99342240000000004</v>
       </c>
       <c r="G69" s="566">
-        <v>1.6590560000000001</v>
+        <v>1.656315</v>
       </c>
     </row>
     <row r="70">
@@ -16153,22 +16153,22 @@
         <v>66</v>
       </c>
       <c r="B70" s="569">
-        <v>0.473719</v>
+        <v>0.48615920000000001</v>
       </c>
       <c r="C70" s="570">
-        <v>0.31612230000000002</v>
+        <v>0.32485540000000002</v>
       </c>
       <c r="D70" s="571">
-        <v>-1.1200000000000001</v>
+        <v>-1.0800000000000001</v>
       </c>
       <c r="E70" s="572">
-        <v>0.26300000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="F70" s="573">
-        <v>0.12808449999999999</v>
+        <v>0.1312197</v>
       </c>
       <c r="G70" s="574">
-        <v>1.7520439999999999</v>
+        <v>1.8011839999999999</v>
       </c>
     </row>
     <row r="71">
@@ -16176,22 +16176,22 @@
         <v>67</v>
       </c>
       <c r="B71" s="577">
-        <v>1.6785460000000001</v>
+        <v>1.67547</v>
       </c>
       <c r="C71" s="578">
-        <v>0.31821349999999998</v>
+        <v>0.31797389999999998</v>
       </c>
       <c r="D71" s="579">
-        <v>2.73</v>
+        <v>2.7200000000000002</v>
       </c>
       <c r="E71" s="580">
-        <v>0.0060000000000000001</v>
+        <v>0.0070000000000000001</v>
       </c>
       <c r="F71" s="581">
-        <v>1.157618</v>
+        <v>1.1550320000000001</v>
       </c>
       <c r="G71" s="582">
-        <v>2.4338929999999999</v>
+        <v>2.4304079999999999</v>
       </c>
     </row>
     <row r="72">
@@ -16199,22 +16199,22 @@
         <v>68</v>
       </c>
       <c r="B72" s="585">
-        <v>0.9431737</v>
+        <v>0.94634989999999997</v>
       </c>
       <c r="C72" s="586">
-        <v>0.25205640000000001</v>
+        <v>0.25296960000000002</v>
       </c>
       <c r="D72" s="587">
-        <v>-0.22</v>
+        <v>-0.20999999999999999</v>
       </c>
       <c r="E72" s="588">
-        <v>0.82699999999999996</v>
+        <v>0.83699999999999997</v>
       </c>
       <c r="F72" s="589">
-        <v>0.55861700000000003</v>
+        <v>0.56042349999999996</v>
       </c>
       <c r="G72" s="590">
-        <v>1.592462</v>
+        <v>1.5980380000000001</v>
       </c>
     </row>
     <row r="73">
@@ -16222,22 +16222,22 @@
         <v>69</v>
       </c>
       <c r="B73" s="593">
-        <v>0.94853109999999996</v>
+        <v>0.94726089999999996</v>
       </c>
       <c r="C73" s="594">
-        <v>0.1124882</v>
+        <v>0.112485</v>
       </c>
       <c r="D73" s="595">
-        <v>-0.45000000000000001</v>
+        <v>-0.46000000000000002</v>
       </c>
       <c r="E73" s="596">
-        <v>0.65600000000000003</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="F73" s="597">
-        <v>0.75180630000000004</v>
+        <v>0.75057030000000002</v>
       </c>
       <c r="G73" s="598">
-        <v>1.196733</v>
+        <v>1.195495</v>
       </c>
     </row>
     <row r="74">
@@ -16245,22 +16245,22 @@
         <v>70</v>
       </c>
       <c r="B74" s="601">
-        <v>1.095502</v>
+        <v>1.0879509999999999</v>
       </c>
       <c r="C74" s="602">
-        <v>0.18395639999999999</v>
+        <v>0.1827858</v>
       </c>
       <c r="D74" s="603">
-        <v>0.54000000000000004</v>
+        <v>0.5</v>
       </c>
       <c r="E74" s="604">
-        <v>0.58699999999999997</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="F74" s="605">
-        <v>0.78827789999999998</v>
+        <v>0.78270799999999996</v>
       </c>
       <c r="G74" s="606">
-        <v>1.5224629999999999</v>
+        <v>1.512235</v>
       </c>
     </row>
     <row r="75">
@@ -16268,22 +16268,22 @@
         <v>71</v>
       </c>
       <c r="B75" s="609">
-        <v>0.94975560000000003</v>
+        <v>0.96328389999999997</v>
       </c>
       <c r="C75" s="610">
-        <v>0.056081699999999998</v>
+        <v>0.057050799999999999</v>
       </c>
       <c r="D75" s="611">
-        <v>-0.87</v>
+        <v>-0.63</v>
       </c>
       <c r="E75" s="612">
-        <v>0.38300000000000001</v>
+        <v>0.52800000000000002</v>
       </c>
       <c r="F75" s="613">
-        <v>0.84595969999999998</v>
+        <v>0.85771229999999998</v>
       </c>
       <c r="G75" s="614">
-        <v>1.066287</v>
+        <v>1.08185</v>
       </c>
     </row>
     <row r="76">
@@ -16291,22 +16291,22 @@
         <v>72</v>
       </c>
       <c r="B76" s="617">
-        <v>1.465876</v>
+        <v>1.508187</v>
       </c>
       <c r="C76" s="618">
-        <v>0.23221339999999999</v>
+        <v>0.23993809999999999</v>
       </c>
       <c r="D76" s="619">
-        <v>2.4100000000000001</v>
+        <v>2.5800000000000001</v>
       </c>
       <c r="E76" s="620">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="F76" s="621">
-        <v>1.0746230000000001</v>
+        <v>1.1041730000000001</v>
       </c>
       <c r="G76" s="622">
-        <v>1.9995780000000001</v>
+        <v>2.0600290000000001</v>
       </c>
     </row>
     <row r="77">
@@ -16314,22 +16314,22 @@
         <v>73</v>
       </c>
       <c r="B77" s="625">
-        <v>1.1174980000000001</v>
+        <v>1.108001</v>
       </c>
       <c r="C77" s="626">
-        <v>0.0904552</v>
+        <v>0.089749999999999997</v>
       </c>
       <c r="D77" s="627">
-        <v>1.3700000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="E77" s="628">
-        <v>0.17000000000000001</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="F77" s="629">
-        <v>0.95355749999999995</v>
+        <v>0.9453471</v>
       </c>
       <c r="G77" s="630">
-        <v>1.309625</v>
+        <v>1.29864</v>
       </c>
     </row>
     <row r="78">
@@ -16337,22 +16337,22 @@
         <v>74</v>
       </c>
       <c r="B78" s="633">
-        <v>1.4227160000000001</v>
+        <v>1.4318150000000001</v>
       </c>
       <c r="C78" s="634">
-        <v>0.37109320000000001</v>
+        <v>0.37345810000000002</v>
       </c>
       <c r="D78" s="635">
-        <v>1.3500000000000001</v>
+        <v>1.3799999999999999</v>
       </c>
       <c r="E78" s="636">
-        <v>0.17599999999999999</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="F78" s="637">
-        <v>0.85328839999999995</v>
+        <v>0.85875489999999999</v>
       </c>
       <c r="G78" s="638">
-        <v>2.3721429999999999</v>
+        <v>2.387286</v>
       </c>
     </row>
     <row r="79">
@@ -16406,22 +16406,22 @@
         <v>1</v>
       </c>
       <c r="B81" s="657">
-        <v>37600000</v>
+        <v>0.68046130000000005</v>
       </c>
       <c r="C81" s="658">
-        <v>2510000000</v>
+        <v>0.17001649999999999</v>
       </c>
       <c r="D81" s="659">
-        <v>0.26000000000000001</v>
+        <v>-1.54</v>
       </c>
       <c r="E81" s="660">
-        <v>0.79400000000000004</v>
+        <v>0.123</v>
       </c>
       <c r="F81" s="661">
-        <v>6.1600000000000003e-50</v>
+        <v>0.416991</v>
       </c>
       <c r="G81" s="662">
-        <v>2.3e+64</v>
+        <v>1.1104019999999999</v>
       </c>
     </row>
     <row r="82">
@@ -16475,22 +16475,22 @@
         <v>1</v>
       </c>
       <c r="B84" s="681">
-        <v>7.81907</v>
+        <v>6.0548960000000003</v>
       </c>
       <c r="C84" s="682">
-        <v>6.244726</v>
+        <v>4.9696559999999996</v>
       </c>
       <c r="D84" s="683">
-        <v>2.5800000000000001</v>
+        <v>2.19</v>
       </c>
       <c r="E84" s="684">
-        <v>0.01</v>
+        <v>0.028000000000000001</v>
       </c>
       <c r="F84" s="685">
-        <v>1.6343319999999999</v>
+        <v>1.2119059999999999</v>
       </c>
       <c r="G84" s="686">
-        <v>37.408479999999997</v>
+        <v>30.251329999999999</v>
       </c>
     </row>
     <row r="85">
@@ -16544,22 +16544,22 @@
         <v>1</v>
       </c>
       <c r="B87" s="705">
-        <v>2.85e-08</v>
+        <v>0.82965630000000001</v>
       </c>
       <c r="C87" s="706">
-        <v>1.9e-06</v>
+        <v>0.20293990000000001</v>
       </c>
       <c r="D87" s="707">
-        <v>-0.26000000000000001</v>
+        <v>-0.76000000000000001</v>
       </c>
       <c r="E87" s="708">
-        <v>0.79500000000000004</v>
+        <v>0.44500000000000001</v>
       </c>
       <c r="F87" s="709">
-        <v>4.6699999999999997e-65</v>
+        <v>0.51367479999999999</v>
       </c>
       <c r="G87" s="710">
-        <v>1.7400000000000001e+49</v>
+        <v>1.3400099999999999</v>
       </c>
     </row>
     <row r="88">
@@ -16613,22 +16613,22 @@
         <v>1</v>
       </c>
       <c r="B90" s="729">
-        <v>1.9546349999999999</v>
+        <v>1.516319</v>
       </c>
       <c r="C90" s="730">
-        <v>0.28353010000000001</v>
+        <v>0.35964249999999998</v>
       </c>
       <c r="D90" s="731">
-        <v>4.6200000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="E90" s="732">
-        <v>0</v>
+        <v>0.079000000000000001</v>
       </c>
       <c r="F90" s="733">
-        <v>1.4709380000000001</v>
+        <v>0.95257999999999998</v>
       </c>
       <c r="G90" s="734">
-        <v>2.5973890000000002</v>
+        <v>2.4136799999999998</v>
       </c>
     </row>
     <row r="91">
@@ -16682,22 +16682,22 @@
         <v>1</v>
       </c>
       <c r="B93" s="753">
-        <v>2.320986</v>
+        <v>1.8507450000000001</v>
       </c>
       <c r="C93" s="754">
-        <v>1.1111530000000001</v>
+        <v>0.95050809999999997</v>
       </c>
       <c r="D93" s="755">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="E93" s="756">
-        <v>0.079000000000000001</v>
+        <v>0.23100000000000001</v>
       </c>
       <c r="F93" s="757">
-        <v>0.9081688</v>
+        <v>0.67637170000000002</v>
       </c>
       <c r="G93" s="758">
-        <v>5.9316890000000004</v>
+        <v>5.064165</v>
       </c>
     </row>
     <row r="94">
@@ -16751,22 +16751,22 @@
         <v>1</v>
       </c>
       <c r="B96" s="777">
-        <v>4.824872</v>
+        <v>3.670512</v>
       </c>
       <c r="C96" s="778">
-        <v>1.1034919999999999</v>
+        <v>1.078945</v>
       </c>
       <c r="D96" s="779">
-        <v>6.8799999999999999</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="E96" s="780">
         <v>0</v>
       </c>
       <c r="F96" s="781">
-        <v>3.0818270000000001</v>
+        <v>2.0630820000000001</v>
       </c>
       <c r="G96" s="782">
-        <v>7.5537619999999999</v>
+        <v>6.5303570000000004</v>
       </c>
     </row>
     <row r="97">
@@ -16820,22 +16820,22 @@
         <v>1</v>
       </c>
       <c r="B99" s="801">
-        <v>3.019215</v>
+        <v>2.2813940000000001</v>
       </c>
       <c r="C99" s="802">
-        <v>1.5417730000000001</v>
+        <v>1.2395259999999999</v>
       </c>
       <c r="D99" s="803">
-        <v>2.1600000000000001</v>
+        <v>1.52</v>
       </c>
       <c r="E99" s="804">
-        <v>0.029999999999999999</v>
+        <v>0.129</v>
       </c>
       <c r="F99" s="805">
-        <v>1.1097490000000001</v>
+        <v>0.78654939999999996</v>
       </c>
       <c r="G99" s="806">
-        <v>8.2141610000000007</v>
+        <v>6.6172079999999998</v>
       </c>
     </row>
     <row r="100">
@@ -16889,22 +16889,22 @@
         <v>1</v>
       </c>
       <c r="B102" s="825">
-        <v>1.687975</v>
+        <v>1.305895</v>
       </c>
       <c r="C102" s="826">
-        <v>1.594128</v>
+        <v>1.25553</v>
       </c>
       <c r="D102" s="827">
-        <v>0.55000000000000005</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E102" s="828">
-        <v>0.57899999999999996</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="F102" s="829">
-        <v>0.2651482</v>
+        <v>0.1983972</v>
       </c>
       <c r="G102" s="830">
-        <v>10.74591</v>
+        <v>8.5956960000000002</v>
       </c>
     </row>
     <row r="103">
@@ -17027,22 +17027,22 @@
         <v>1</v>
       </c>
       <c r="B108" s="873">
-        <v>19.998190000000001</v>
+        <v>15.3744</v>
       </c>
       <c r="C108" s="874">
-        <v>33.69294</v>
+        <v>26.068850000000001</v>
       </c>
       <c r="D108" s="875">
-        <v>1.78</v>
+        <v>1.6100000000000001</v>
       </c>
       <c r="E108" s="876">
-        <v>0.074999999999999997</v>
+        <v>0.107</v>
       </c>
       <c r="F108" s="877">
-        <v>0.73601620000000001</v>
+        <v>0.55398749999999997</v>
       </c>
       <c r="G108" s="878">
-        <v>543.3682</v>
+        <v>426.67419999999999</v>
       </c>
     </row>
     <row r="109">
@@ -17096,22 +17096,22 @@
         <v>1</v>
       </c>
       <c r="B111" s="897">
-        <v>0.47235709999999998</v>
+        <v>0.3662707</v>
       </c>
       <c r="C111" s="898">
-        <v>0.51732929999999999</v>
+        <v>0.40698889999999999</v>
       </c>
       <c r="D111" s="899">
-        <v>-0.68000000000000005</v>
+        <v>-0.90000000000000002</v>
       </c>
       <c r="E111" s="900">
-        <v>0.49299999999999999</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="F111" s="901">
-        <v>0.055211299999999998</v>
+        <v>0.041492800000000003</v>
       </c>
       <c r="G111" s="902">
-        <v>4.0412270000000001</v>
+        <v>3.2331919999999999</v>
       </c>
     </row>
     <row r="112">
@@ -17165,22 +17165,22 @@
         <v>1</v>
       </c>
       <c r="B114" s="921">
-        <v>0.43328719999999998</v>
+        <v>0.3361133</v>
       </c>
       <c r="C114" s="922">
-        <v>1.682042</v>
+        <v>1.3072429999999999</v>
       </c>
       <c r="D114" s="923">
-        <v>-0.22</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="E114" s="924">
-        <v>0.82899999999999996</v>
+        <v>0.77900000000000003</v>
       </c>
       <c r="F114" s="925">
-        <v>0.000215</v>
+        <v>0.00016440000000000001</v>
       </c>
       <c r="G114" s="926">
-        <v>873.33479999999997</v>
+        <v>687.15769999999998</v>
       </c>
     </row>
     <row r="115">
@@ -17211,22 +17211,22 @@
         <v>88</v>
       </c>
       <c r="B116" s="944">
-        <v>171.6</v>
+        <v>96.123270000000005</v>
       </c>
       <c r="C116" s="945">
-        <v>112.3506</v>
+        <v>67.488169999999997</v>
       </c>
       <c r="D116" s="946">
-        <v>7.8600000000000003</v>
+        <v>6.5</v>
       </c>
       <c r="E116" s="947">
         <v>0</v>
       </c>
       <c r="F116" s="948">
-        <v>47.557079999999999</v>
+        <v>24.277259999999998</v>
       </c>
       <c r="G116" s="949">
-        <v>619.18330000000003</v>
+        <v>380.58999999999998</v>
       </c>
     </row>
   </sheetData>
